--- a/input/Test_Positioning document.xlsx
+++ b/input/Test_Positioning document.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Products India\Campaign Management\Google\Setup\KW classification\for claude working\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\keywords classifier google\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69D85E2-0576-40F6-8834-81029BF10E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D5A43C-B5CF-4615-8AFF-3875B271D361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4668" yWindow="1776" windowWidth="17280" windowHeight="10464" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Focus products" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -487,13 +485,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Indulekha Hair oil 
-Baidyanath- Mahabhringaraj Tel
-Kottakal-Nilibhringadi Kerathailam 
-Shesha Ayurveda
-Kesh King </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">BGR-34 
 Himalaya Diabecon 
@@ -1028,6 +1019,22 @@
 Mild laxative 
 Tonic for maintaining colon health 
 Constipation, sluggish digestion, bloating, irregular bowel movements, weak gut motility, dependency on laxatives, acidity, poor nutrient absorption, gut discomfort.indigestion, sluggish metabolism.</t>
+  </si>
+  <si>
+    <t>Indulekha Hair oil 
+Indulekha bhringa oil
+Indulekha
+Baidyanath- Mahabhringaraj Tel
+Kottakal-Nilibhringadi Kerathailam 
+Shesha Ayurveda
+Kesh King 
+Sesha ayurveda
+vedix
+avp
+kalans
+dabur vatika
+dabur amla
+trichup</t>
   </si>
 </sst>
 </file>
@@ -1833,20 +1840,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L991"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="2" width="44.28515625" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
-    <col min="4" max="4" width="66.85546875" customWidth="1"/>
-    <col min="5" max="5" width="51.28515625" customWidth="1"/>
-    <col min="6" max="6" width="59.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="44.33203125" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="4" max="4" width="66.88671875" customWidth="1"/>
+    <col min="5" max="5" width="51.33203125" customWidth="1"/>
+    <col min="6" max="6" width="59.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="13.2" x14ac:dyDescent="0.25">
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1857,7 +1864,7 @@
         <v>107</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>2</v>
@@ -1866,7 +1873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="151.80000000000001" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
@@ -1877,14 +1884,14 @@
         <v>5</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="36" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
@@ -1895,14 +1902,14 @@
         <v>7</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="37" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
@@ -1913,14 +1920,14 @@
         <v>9</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="38" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -1931,14 +1938,14 @@
         <v>11</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="38" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="69" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
@@ -1949,13 +1956,13 @@
         <v>14</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
@@ -1963,17 +1970,17 @@
         <v>72</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E8" s="44"/>
       <c r="F8" s="42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>16</v>
       </c>
@@ -1984,14 +1991,14 @@
         <v>17</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>18</v>
       </c>
@@ -1999,17 +2006,17 @@
         <v>74</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="43" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
@@ -2017,17 +2024,17 @@
         <v>75</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E11" s="48"/>
       <c r="F11" s="42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -2035,17 +2042,17 @@
         <v>76</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>21</v>
       </c>
@@ -2056,14 +2063,14 @@
         <v>22</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" s="48"/>
       <c r="F13" s="42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>23</v>
       </c>
@@ -2071,16 +2078,16 @@
         <v>78</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>25</v>
       </c>
@@ -2091,14 +2098,14 @@
         <v>26</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="42" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>27</v>
       </c>
@@ -2109,14 +2116,14 @@
         <v>28</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="42" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>29</v>
       </c>
@@ -2127,14 +2134,14 @@
         <v>30</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E17" s="48"/>
       <c r="F17" s="42" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>31</v>
       </c>
@@ -2142,16 +2149,16 @@
         <v>82</v>
       </c>
       <c r="C18" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="D18" s="49" t="s">
-        <v>145</v>
-      </c>
       <c r="F18" s="42" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>32</v>
       </c>
@@ -2159,17 +2166,17 @@
         <v>83</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="42" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>33</v>
       </c>
@@ -2177,17 +2184,17 @@
         <v>84</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="42" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>34</v>
       </c>
@@ -2195,17 +2202,17 @@
         <v>85</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="42" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>35</v>
       </c>
@@ -2216,10 +2223,10 @@
         <v>36</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>37</v>
       </c>
@@ -2227,13 +2234,13 @@
         <v>87</v>
       </c>
       <c r="C23" s="46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
@@ -2242,7 +2249,7 @@
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
     </row>
-    <row r="24" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>38</v>
       </c>
@@ -2264,7 +2271,7 @@
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
     </row>
-    <row r="25" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>41</v>
       </c>
@@ -2275,11 +2282,11 @@
         <v>42</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
@@ -2288,7 +2295,7 @@
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
     </row>
-    <row r="26" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>43</v>
       </c>
@@ -2299,7 +2306,7 @@
         <v>44</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F26" s="13"/>
       <c r="G26" s="18"/>
@@ -2309,7 +2316,7 @@
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
     </row>
-    <row r="27" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
         <v>45</v>
       </c>
@@ -2317,10 +2324,10 @@
         <v>91</v>
       </c>
       <c r="C27" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="50" t="s">
         <v>150</v>
-      </c>
-      <c r="D27" s="50" t="s">
-        <v>151</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="13"/>
@@ -2331,7 +2338,7 @@
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
     </row>
-    <row r="28" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>46</v>
       </c>
@@ -2342,7 +2349,7 @@
         <v>47</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E28" s="9"/>
       <c r="G28" s="18"/>
@@ -2352,7 +2359,7 @@
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
     </row>
-    <row r="29" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>48</v>
       </c>
@@ -2363,7 +2370,7 @@
         <v>49</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E29" s="9"/>
       <c r="G29" s="18"/>
@@ -2373,7 +2380,7 @@
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
     </row>
-    <row r="30" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>50</v>
       </c>
@@ -2394,7 +2401,7 @@
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
     </row>
-    <row r="31" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>52</v>
       </c>
@@ -2405,7 +2412,7 @@
         <v>53</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E31" s="9"/>
       <c r="G31" s="18"/>
@@ -2415,7 +2422,7 @@
       <c r="K31" s="18"/>
       <c r="L31" s="18"/>
     </row>
-    <row r="32" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>54</v>
       </c>
@@ -2426,7 +2433,7 @@
         <v>55</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G32" s="18"/>
       <c r="H32" s="18"/>
@@ -2435,7 +2442,7 @@
       <c r="K32" s="18"/>
       <c r="L32" s="18"/>
     </row>
-    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>56</v>
       </c>
@@ -2443,10 +2450,10 @@
         <v>97</v>
       </c>
       <c r="C33" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E33" s="32"/>
       <c r="F33" s="23"/>
@@ -2457,7 +2464,7 @@
       <c r="K33" s="18"/>
       <c r="L33" s="18"/>
     </row>
-    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
         <v>57</v>
       </c>
@@ -2468,7 +2475,7 @@
         <v>59</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E34" s="30"/>
       <c r="F34" s="40" t="s">
@@ -2481,7 +2488,7 @@
       <c r="K34" s="18"/>
       <c r="L34" s="18"/>
     </row>
-    <row r="35" spans="1:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
         <v>60</v>
       </c>
@@ -2492,14 +2499,14 @@
         <v>61</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E35" s="31"/>
       <c r="F35" s="40" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
         <v>62</v>
       </c>
@@ -2510,14 +2517,14 @@
         <v>63</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E36" s="31"/>
       <c r="F36" s="41" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>64</v>
       </c>
@@ -2528,14 +2535,14 @@
         <v>65</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
         <v>66</v>
       </c>
@@ -2546,14 +2553,14 @@
         <v>67</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E38" s="52"/>
       <c r="F38" s="40" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26"/>
       <c r="B39" s="27"/>
       <c r="C39" s="24"/>
@@ -2561,7 +2568,7 @@
       <c r="E39" s="24"/>
       <c r="F39" s="25"/>
     </row>
-    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26"/>
       <c r="B40" s="27"/>
       <c r="C40" s="24"/>
@@ -2569,7 +2576,7 @@
       <c r="E40" s="24"/>
       <c r="F40" s="25"/>
     </row>
-    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="26"/>
       <c r="B41" s="27"/>
       <c r="C41" s="24"/>
@@ -2577,7 +2584,7 @@
       <c r="E41" s="24"/>
       <c r="F41" s="25"/>
     </row>
-    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="26"/>
       <c r="B42" s="27"/>
       <c r="C42" s="24"/>
@@ -2585,7 +2592,7 @@
       <c r="E42" s="24"/>
       <c r="F42" s="25"/>
     </row>
-    <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="26"/>
       <c r="B43" s="27"/>
       <c r="C43" s="24"/>
@@ -2593,7 +2600,7 @@
       <c r="E43" s="24"/>
       <c r="F43" s="25"/>
     </row>
-    <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="26"/>
       <c r="B44" s="27"/>
       <c r="C44" s="24"/>
@@ -2601,7 +2608,7 @@
       <c r="E44" s="24"/>
       <c r="F44" s="25"/>
     </row>
-    <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="26"/>
       <c r="B45" s="27"/>
       <c r="C45" s="24"/>
@@ -2609,7 +2616,7 @@
       <c r="E45" s="24"/>
       <c r="F45" s="25"/>
     </row>
-    <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26"/>
       <c r="B46" s="27"/>
       <c r="C46" s="24"/>
@@ -2617,7 +2624,7 @@
       <c r="E46" s="24"/>
       <c r="F46" s="25"/>
     </row>
-    <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="26"/>
       <c r="B47" s="27"/>
       <c r="C47" s="24"/>
@@ -2625,7 +2632,7 @@
       <c r="E47" s="24"/>
       <c r="F47" s="25"/>
     </row>
-    <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="26"/>
       <c r="B48" s="27"/>
       <c r="C48" s="24"/>
@@ -2633,7 +2640,7 @@
       <c r="E48" s="24"/>
       <c r="F48" s="25"/>
     </row>
-    <row r="49" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26"/>
       <c r="B49" s="27"/>
       <c r="C49" s="24"/>
@@ -2641,7 +2648,7 @@
       <c r="E49" s="24"/>
       <c r="F49" s="25"/>
     </row>
-    <row r="50" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="27"/>
       <c r="C50" s="24"/>
@@ -2649,7 +2656,7 @@
       <c r="E50" s="24"/>
       <c r="F50" s="25"/>
     </row>
-    <row r="51" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26"/>
       <c r="B51" s="27"/>
       <c r="C51" s="24"/>
@@ -2657,7 +2664,7 @@
       <c r="E51" s="24"/>
       <c r="F51" s="25"/>
     </row>
-    <row r="52" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26"/>
       <c r="B52" s="27"/>
       <c r="C52" s="24"/>
@@ -2665,7 +2672,7 @@
       <c r="E52" s="24"/>
       <c r="F52" s="25"/>
     </row>
-    <row r="53" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
       <c r="B53" s="27"/>
       <c r="C53" s="24"/>
@@ -2673,7 +2680,7 @@
       <c r="E53" s="24"/>
       <c r="F53" s="25"/>
     </row>
-    <row r="54" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26"/>
       <c r="B54" s="27"/>
       <c r="C54" s="24"/>
@@ -2681,7 +2688,7 @@
       <c r="E54" s="24"/>
       <c r="F54" s="25"/>
     </row>
-    <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26"/>
       <c r="B55" s="27"/>
       <c r="C55" s="24"/>
@@ -2689,7 +2696,7 @@
       <c r="E55" s="24"/>
       <c r="F55" s="25"/>
     </row>
-    <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26"/>
       <c r="B56" s="27"/>
       <c r="C56" s="24"/>
@@ -2697,7 +2704,7 @@
       <c r="E56" s="24"/>
       <c r="F56" s="25"/>
     </row>
-    <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26"/>
       <c r="B57" s="27"/>
       <c r="C57" s="24"/>
@@ -2705,7 +2712,7 @@
       <c r="E57" s="24"/>
       <c r="F57" s="25"/>
     </row>
-    <row r="58" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="26"/>
       <c r="B58" s="27"/>
       <c r="C58" s="24"/>
@@ -2713,7 +2720,7 @@
       <c r="E58" s="24"/>
       <c r="F58" s="25"/>
     </row>
-    <row r="59" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="B59" s="27"/>
       <c r="C59" s="24"/>
@@ -2721,7 +2728,7 @@
       <c r="E59" s="24"/>
       <c r="F59" s="25"/>
     </row>
-    <row r="60" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="27"/>
       <c r="C60" s="24"/>
@@ -2729,7 +2736,7 @@
       <c r="E60" s="24"/>
       <c r="F60" s="25"/>
     </row>
-    <row r="61" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="26"/>
       <c r="B61" s="27"/>
       <c r="C61" s="24"/>
@@ -2737,7 +2744,7 @@
       <c r="E61" s="24"/>
       <c r="F61" s="25"/>
     </row>
-    <row r="62" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="26"/>
       <c r="B62" s="27"/>
       <c r="C62" s="24"/>
@@ -2745,7 +2752,7 @@
       <c r="E62" s="24"/>
       <c r="F62" s="25"/>
     </row>
-    <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="26"/>
       <c r="B63" s="27"/>
       <c r="C63" s="24"/>
@@ -2753,7 +2760,7 @@
       <c r="E63" s="24"/>
       <c r="F63" s="25"/>
     </row>
-    <row r="64" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26"/>
       <c r="B64" s="27"/>
       <c r="C64" s="24"/>
@@ -2761,7 +2768,7 @@
       <c r="E64" s="24"/>
       <c r="F64" s="25"/>
     </row>
-    <row r="65" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26"/>
       <c r="B65" s="27"/>
       <c r="C65" s="24"/>
@@ -2769,7 +2776,7 @@
       <c r="E65" s="24"/>
       <c r="F65" s="25"/>
     </row>
-    <row r="66" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26"/>
       <c r="B66" s="27"/>
       <c r="C66" s="24"/>
@@ -2777,7 +2784,7 @@
       <c r="E66" s="24"/>
       <c r="F66" s="25"/>
     </row>
-    <row r="67" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26"/>
       <c r="B67" s="27"/>
       <c r="C67" s="24"/>
@@ -2785,7 +2792,7 @@
       <c r="E67" s="24"/>
       <c r="F67" s="25"/>
     </row>
-    <row r="68" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="26"/>
       <c r="B68" s="27"/>
       <c r="C68" s="24"/>
@@ -2793,7 +2800,7 @@
       <c r="E68" s="24"/>
       <c r="F68" s="25"/>
     </row>
-    <row r="69" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="26"/>
       <c r="B69" s="27"/>
       <c r="C69" s="24"/>
@@ -2801,7 +2808,7 @@
       <c r="E69" s="24"/>
       <c r="F69" s="25"/>
     </row>
-    <row r="70" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26"/>
       <c r="B70" s="27"/>
       <c r="C70" s="24"/>
@@ -2809,7 +2816,7 @@
       <c r="E70" s="24"/>
       <c r="F70" s="25"/>
     </row>
-    <row r="71" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="26"/>
       <c r="B71" s="27"/>
       <c r="C71" s="24"/>
@@ -2817,7 +2824,7 @@
       <c r="E71" s="24"/>
       <c r="F71" s="25"/>
     </row>
-    <row r="72" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="26"/>
       <c r="B72" s="27"/>
       <c r="C72" s="24"/>
@@ -2825,7 +2832,7 @@
       <c r="E72" s="24"/>
       <c r="F72" s="25"/>
     </row>
-    <row r="73" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="26"/>
       <c r="B73" s="27"/>
       <c r="C73" s="24"/>
@@ -2833,7 +2840,7 @@
       <c r="E73" s="24"/>
       <c r="F73" s="25"/>
     </row>
-    <row r="74" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="26"/>
       <c r="B74" s="27"/>
       <c r="C74" s="24"/>
@@ -2841,7 +2848,7 @@
       <c r="E74" s="24"/>
       <c r="F74" s="25"/>
     </row>
-    <row r="75" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="26"/>
       <c r="B75" s="27"/>
       <c r="C75" s="24"/>
@@ -2849,7 +2856,7 @@
       <c r="E75" s="24"/>
       <c r="F75" s="25"/>
     </row>
-    <row r="76" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="26"/>
       <c r="B76" s="27"/>
       <c r="C76" s="24"/>
@@ -2857,7 +2864,7 @@
       <c r="E76" s="24"/>
       <c r="F76" s="25"/>
     </row>
-    <row r="77" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="26"/>
       <c r="B77" s="27"/>
       <c r="C77" s="24"/>
@@ -2865,7 +2872,7 @@
       <c r="E77" s="24"/>
       <c r="F77" s="25"/>
     </row>
-    <row r="78" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="26"/>
       <c r="B78" s="27"/>
       <c r="C78" s="24"/>
@@ -2873,7 +2880,7 @@
       <c r="E78" s="24"/>
       <c r="F78" s="25"/>
     </row>
-    <row r="79" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="26"/>
       <c r="B79" s="27"/>
       <c r="C79" s="24"/>
@@ -2881,7 +2888,7 @@
       <c r="E79" s="24"/>
       <c r="F79" s="25"/>
     </row>
-    <row r="80" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="26"/>
       <c r="B80" s="27"/>
       <c r="C80" s="24"/>
@@ -2889,7 +2896,7 @@
       <c r="E80" s="24"/>
       <c r="F80" s="25"/>
     </row>
-    <row r="81" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="26"/>
       <c r="B81" s="27"/>
       <c r="C81" s="24"/>
@@ -2897,7 +2904,7 @@
       <c r="E81" s="24"/>
       <c r="F81" s="25"/>
     </row>
-    <row r="82" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="26"/>
       <c r="B82" s="27"/>
       <c r="C82" s="24"/>
@@ -2905,7 +2912,7 @@
       <c r="E82" s="24"/>
       <c r="F82" s="25"/>
     </row>
-    <row r="83" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="26"/>
       <c r="B83" s="27"/>
       <c r="C83" s="24"/>
@@ -2913,7 +2920,7 @@
       <c r="E83" s="24"/>
       <c r="F83" s="25"/>
     </row>
-    <row r="84" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="26"/>
       <c r="B84" s="27"/>
       <c r="C84" s="24"/>
@@ -2921,7 +2928,7 @@
       <c r="E84" s="24"/>
       <c r="F84" s="25"/>
     </row>
-    <row r="85" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="26"/>
       <c r="B85" s="27"/>
       <c r="C85" s="24"/>
@@ -2929,7 +2936,7 @@
       <c r="E85" s="24"/>
       <c r="F85" s="25"/>
     </row>
-    <row r="86" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="26"/>
       <c r="B86" s="27"/>
       <c r="C86" s="24"/>
@@ -2937,7 +2944,7 @@
       <c r="E86" s="24"/>
       <c r="F86" s="25"/>
     </row>
-    <row r="87" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="26"/>
       <c r="B87" s="27"/>
       <c r="C87" s="24"/>
@@ -2945,7 +2952,7 @@
       <c r="E87" s="24"/>
       <c r="F87" s="25"/>
     </row>
-    <row r="88" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="26"/>
       <c r="B88" s="27"/>
       <c r="C88" s="24"/>
@@ -2953,7 +2960,7 @@
       <c r="E88" s="24"/>
       <c r="F88" s="25"/>
     </row>
-    <row r="89" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="26"/>
       <c r="B89" s="27"/>
       <c r="C89" s="24"/>
@@ -2961,7 +2968,7 @@
       <c r="E89" s="24"/>
       <c r="F89" s="25"/>
     </row>
-    <row r="90" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="26"/>
       <c r="B90" s="27"/>
       <c r="C90" s="24"/>
@@ -2969,7 +2976,7 @@
       <c r="E90" s="24"/>
       <c r="F90" s="25"/>
     </row>
-    <row r="91" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="26"/>
       <c r="B91" s="27"/>
       <c r="C91" s="24"/>
@@ -2977,7 +2984,7 @@
       <c r="E91" s="24"/>
       <c r="F91" s="25"/>
     </row>
-    <row r="92" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="26"/>
       <c r="B92" s="27"/>
       <c r="C92" s="24"/>
@@ -2985,7 +2992,7 @@
       <c r="E92" s="24"/>
       <c r="F92" s="25"/>
     </row>
-    <row r="93" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="26"/>
       <c r="B93" s="27"/>
       <c r="C93" s="24"/>
@@ -2993,7 +3000,7 @@
       <c r="E93" s="24"/>
       <c r="F93" s="25"/>
     </row>
-    <row r="94" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="26"/>
       <c r="B94" s="27"/>
       <c r="C94" s="24"/>
@@ -3001,7 +3008,7 @@
       <c r="E94" s="24"/>
       <c r="F94" s="25"/>
     </row>
-    <row r="95" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="26"/>
       <c r="B95" s="27"/>
       <c r="C95" s="24"/>
@@ -3009,7 +3016,7 @@
       <c r="E95" s="24"/>
       <c r="F95" s="25"/>
     </row>
-    <row r="96" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="26"/>
       <c r="B96" s="27"/>
       <c r="C96" s="24"/>
@@ -3017,7 +3024,7 @@
       <c r="E96" s="24"/>
       <c r="F96" s="25"/>
     </row>
-    <row r="97" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="26"/>
       <c r="B97" s="27"/>
       <c r="C97" s="24"/>
@@ -3025,7 +3032,7 @@
       <c r="E97" s="24"/>
       <c r="F97" s="25"/>
     </row>
-    <row r="98" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="26"/>
       <c r="B98" s="27"/>
       <c r="C98" s="24"/>
@@ -3033,7 +3040,7 @@
       <c r="E98" s="24"/>
       <c r="F98" s="25"/>
     </row>
-    <row r="99" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="26"/>
       <c r="B99" s="27"/>
       <c r="C99" s="24"/>
@@ -3041,7 +3048,7 @@
       <c r="E99" s="24"/>
       <c r="F99" s="25"/>
     </row>
-    <row r="100" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="26"/>
       <c r="B100" s="27"/>
       <c r="C100" s="24"/>
@@ -3049,7 +3056,7 @@
       <c r="E100" s="24"/>
       <c r="F100" s="25"/>
     </row>
-    <row r="101" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="26"/>
       <c r="B101" s="27"/>
       <c r="C101" s="24"/>
@@ -3057,7 +3064,7 @@
       <c r="E101" s="24"/>
       <c r="F101" s="25"/>
     </row>
-    <row r="102" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="26"/>
       <c r="B102" s="27"/>
       <c r="C102" s="24"/>
@@ -3065,7 +3072,7 @@
       <c r="E102" s="24"/>
       <c r="F102" s="25"/>
     </row>
-    <row r="103" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="26"/>
       <c r="B103" s="27"/>
       <c r="C103" s="24"/>
@@ -3073,7 +3080,7 @@
       <c r="E103" s="24"/>
       <c r="F103" s="25"/>
     </row>
-    <row r="104" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="26"/>
       <c r="B104" s="27"/>
       <c r="C104" s="24"/>
@@ -3081,7 +3088,7 @@
       <c r="E104" s="24"/>
       <c r="F104" s="25"/>
     </row>
-    <row r="105" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="26"/>
       <c r="B105" s="27"/>
       <c r="C105" s="24"/>
@@ -3089,7 +3096,7 @@
       <c r="E105" s="24"/>
       <c r="F105" s="25"/>
     </row>
-    <row r="106" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26"/>
       <c r="B106" s="27"/>
       <c r="C106" s="24"/>
@@ -3097,7 +3104,7 @@
       <c r="E106" s="24"/>
       <c r="F106" s="25"/>
     </row>
-    <row r="107" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="26"/>
       <c r="B107" s="27"/>
       <c r="C107" s="24"/>
@@ -3105,7 +3112,7 @@
       <c r="E107" s="24"/>
       <c r="F107" s="25"/>
     </row>
-    <row r="108" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="26"/>
       <c r="B108" s="27"/>
       <c r="C108" s="24"/>
@@ -3113,7 +3120,7 @@
       <c r="E108" s="24"/>
       <c r="F108" s="25"/>
     </row>
-    <row r="109" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="26"/>
       <c r="B109" s="27"/>
       <c r="C109" s="24"/>
@@ -3121,7 +3128,7 @@
       <c r="E109" s="24"/>
       <c r="F109" s="25"/>
     </row>
-    <row r="110" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="26"/>
       <c r="B110" s="27"/>
       <c r="C110" s="24"/>
@@ -3129,7 +3136,7 @@
       <c r="E110" s="24"/>
       <c r="F110" s="25"/>
     </row>
-    <row r="111" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="26"/>
       <c r="B111" s="27"/>
       <c r="C111" s="24"/>
@@ -3137,7 +3144,7 @@
       <c r="E111" s="24"/>
       <c r="F111" s="25"/>
     </row>
-    <row r="112" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="26"/>
       <c r="B112" s="27"/>
       <c r="C112" s="24"/>
@@ -3145,7 +3152,7 @@
       <c r="E112" s="24"/>
       <c r="F112" s="25"/>
     </row>
-    <row r="113" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="26"/>
       <c r="B113" s="27"/>
       <c r="C113" s="24"/>
@@ -3153,7 +3160,7 @@
       <c r="E113" s="24"/>
       <c r="F113" s="25"/>
     </row>
-    <row r="114" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="26"/>
       <c r="B114" s="27"/>
       <c r="C114" s="24"/>
@@ -3161,7 +3168,7 @@
       <c r="E114" s="24"/>
       <c r="F114" s="25"/>
     </row>
-    <row r="115" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="26"/>
       <c r="B115" s="27"/>
       <c r="C115" s="24"/>
@@ -3169,7 +3176,7 @@
       <c r="E115" s="24"/>
       <c r="F115" s="25"/>
     </row>
-    <row r="116" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="26"/>
       <c r="B116" s="27"/>
       <c r="C116" s="24"/>
@@ -3177,7 +3184,7 @@
       <c r="E116" s="24"/>
       <c r="F116" s="25"/>
     </row>
-    <row r="117" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="26"/>
       <c r="B117" s="27"/>
       <c r="C117" s="24"/>
@@ -3185,7 +3192,7 @@
       <c r="E117" s="24"/>
       <c r="F117" s="25"/>
     </row>
-    <row r="118" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="26"/>
       <c r="B118" s="27"/>
       <c r="C118" s="24"/>
@@ -3193,7 +3200,7 @@
       <c r="E118" s="24"/>
       <c r="F118" s="25"/>
     </row>
-    <row r="119" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="26"/>
       <c r="B119" s="27"/>
       <c r="C119" s="24"/>
@@ -3201,7 +3208,7 @@
       <c r="E119" s="24"/>
       <c r="F119" s="25"/>
     </row>
-    <row r="120" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="26"/>
       <c r="B120" s="27"/>
       <c r="C120" s="24"/>
@@ -3209,7 +3216,7 @@
       <c r="E120" s="24"/>
       <c r="F120" s="25"/>
     </row>
-    <row r="121" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="26"/>
       <c r="B121" s="27"/>
       <c r="C121" s="24"/>
@@ -3217,7 +3224,7 @@
       <c r="E121" s="24"/>
       <c r="F121" s="25"/>
     </row>
-    <row r="122" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="26"/>
       <c r="B122" s="27"/>
       <c r="C122" s="24"/>
@@ -3225,7 +3232,7 @@
       <c r="E122" s="24"/>
       <c r="F122" s="25"/>
     </row>
-    <row r="123" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="26"/>
       <c r="B123" s="27"/>
       <c r="C123" s="24"/>
@@ -3233,7 +3240,7 @@
       <c r="E123" s="24"/>
       <c r="F123" s="25"/>
     </row>
-    <row r="124" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="26"/>
       <c r="B124" s="27"/>
       <c r="C124" s="24"/>
@@ -3241,7 +3248,7 @@
       <c r="E124" s="24"/>
       <c r="F124" s="25"/>
     </row>
-    <row r="125" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="26"/>
       <c r="B125" s="27"/>
       <c r="C125" s="24"/>
@@ -3249,7 +3256,7 @@
       <c r="E125" s="24"/>
       <c r="F125" s="25"/>
     </row>
-    <row r="126" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="26"/>
       <c r="B126" s="27"/>
       <c r="C126" s="24"/>
@@ -3257,7 +3264,7 @@
       <c r="E126" s="24"/>
       <c r="F126" s="25"/>
     </row>
-    <row r="127" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="26"/>
       <c r="B127" s="27"/>
       <c r="C127" s="24"/>
@@ -3265,7 +3272,7 @@
       <c r="E127" s="24"/>
       <c r="F127" s="25"/>
     </row>
-    <row r="128" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="26"/>
       <c r="B128" s="27"/>
       <c r="C128" s="24"/>
@@ -3273,7 +3280,7 @@
       <c r="E128" s="24"/>
       <c r="F128" s="25"/>
     </row>
-    <row r="129" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="26"/>
       <c r="B129" s="27"/>
       <c r="C129" s="24"/>
@@ -3281,7 +3288,7 @@
       <c r="E129" s="24"/>
       <c r="F129" s="25"/>
     </row>
-    <row r="130" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="26"/>
       <c r="B130" s="27"/>
       <c r="C130" s="24"/>
@@ -3289,7 +3296,7 @@
       <c r="E130" s="24"/>
       <c r="F130" s="25"/>
     </row>
-    <row r="131" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="26"/>
       <c r="B131" s="27"/>
       <c r="C131" s="24"/>
@@ -3297,7 +3304,7 @@
       <c r="E131" s="24"/>
       <c r="F131" s="25"/>
     </row>
-    <row r="132" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="26"/>
       <c r="B132" s="27"/>
       <c r="C132" s="24"/>
@@ -3305,7 +3312,7 @@
       <c r="E132" s="24"/>
       <c r="F132" s="25"/>
     </row>
-    <row r="133" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="26"/>
       <c r="B133" s="27"/>
       <c r="C133" s="24"/>
@@ -3313,7 +3320,7 @@
       <c r="E133" s="24"/>
       <c r="F133" s="25"/>
     </row>
-    <row r="134" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="26"/>
       <c r="B134" s="27"/>
       <c r="C134" s="24"/>
@@ -3321,7 +3328,7 @@
       <c r="E134" s="24"/>
       <c r="F134" s="25"/>
     </row>
-    <row r="135" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="26"/>
       <c r="B135" s="27"/>
       <c r="C135" s="24"/>
@@ -3329,7 +3336,7 @@
       <c r="E135" s="24"/>
       <c r="F135" s="25"/>
     </row>
-    <row r="136" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="26"/>
       <c r="B136" s="27"/>
       <c r="C136" s="24"/>
@@ -3337,7 +3344,7 @@
       <c r="E136" s="24"/>
       <c r="F136" s="25"/>
     </row>
-    <row r="137" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="26"/>
       <c r="B137" s="27"/>
       <c r="C137" s="24"/>
@@ -3345,7 +3352,7 @@
       <c r="E137" s="24"/>
       <c r="F137" s="25"/>
     </row>
-    <row r="138" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="26"/>
       <c r="B138" s="27"/>
       <c r="C138" s="24"/>
@@ -3353,7 +3360,7 @@
       <c r="E138" s="24"/>
       <c r="F138" s="25"/>
     </row>
-    <row r="139" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="26"/>
       <c r="B139" s="27"/>
       <c r="C139" s="24"/>
@@ -3361,7 +3368,7 @@
       <c r="E139" s="24"/>
       <c r="F139" s="25"/>
     </row>
-    <row r="140" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="26"/>
       <c r="B140" s="27"/>
       <c r="C140" s="24"/>
@@ -3369,7 +3376,7 @@
       <c r="E140" s="24"/>
       <c r="F140" s="25"/>
     </row>
-    <row r="141" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="26"/>
       <c r="B141" s="27"/>
       <c r="C141" s="24"/>
@@ -3377,7 +3384,7 @@
       <c r="E141" s="24"/>
       <c r="F141" s="25"/>
     </row>
-    <row r="142" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="26"/>
       <c r="B142" s="27"/>
       <c r="C142" s="24"/>
@@ -3385,7 +3392,7 @@
       <c r="E142" s="24"/>
       <c r="F142" s="25"/>
     </row>
-    <row r="143" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="26"/>
       <c r="B143" s="27"/>
       <c r="C143" s="24"/>
@@ -3393,7 +3400,7 @@
       <c r="E143" s="24"/>
       <c r="F143" s="25"/>
     </row>
-    <row r="144" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="26"/>
       <c r="B144" s="27"/>
       <c r="C144" s="24"/>
@@ -3401,7 +3408,7 @@
       <c r="E144" s="24"/>
       <c r="F144" s="25"/>
     </row>
-    <row r="145" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="26"/>
       <c r="B145" s="27"/>
       <c r="C145" s="24"/>
@@ -3409,7 +3416,7 @@
       <c r="E145" s="24"/>
       <c r="F145" s="25"/>
     </row>
-    <row r="146" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="26"/>
       <c r="B146" s="27"/>
       <c r="C146" s="24"/>
@@ -3417,7 +3424,7 @@
       <c r="E146" s="24"/>
       <c r="F146" s="25"/>
     </row>
-    <row r="147" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="26"/>
       <c r="B147" s="27"/>
       <c r="C147" s="24"/>
@@ -3425,7 +3432,7 @@
       <c r="E147" s="24"/>
       <c r="F147" s="25"/>
     </row>
-    <row r="148" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="26"/>
       <c r="B148" s="27"/>
       <c r="C148" s="24"/>
@@ -3433,7 +3440,7 @@
       <c r="E148" s="24"/>
       <c r="F148" s="25"/>
     </row>
-    <row r="149" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="26"/>
       <c r="B149" s="27"/>
       <c r="C149" s="24"/>
@@ -3441,7 +3448,7 @@
       <c r="E149" s="24"/>
       <c r="F149" s="25"/>
     </row>
-    <row r="150" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="26"/>
       <c r="B150" s="27"/>
       <c r="C150" s="24"/>
@@ -3449,7 +3456,7 @@
       <c r="E150" s="24"/>
       <c r="F150" s="25"/>
     </row>
-    <row r="151" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="26"/>
       <c r="B151" s="27"/>
       <c r="C151" s="24"/>
@@ -3457,7 +3464,7 @@
       <c r="E151" s="24"/>
       <c r="F151" s="25"/>
     </row>
-    <row r="152" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="26"/>
       <c r="B152" s="27"/>
       <c r="C152" s="24"/>
@@ -3465,7 +3472,7 @@
       <c r="E152" s="24"/>
       <c r="F152" s="25"/>
     </row>
-    <row r="153" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="26"/>
       <c r="B153" s="27"/>
       <c r="C153" s="24"/>
@@ -3473,7 +3480,7 @@
       <c r="E153" s="24"/>
       <c r="F153" s="25"/>
     </row>
-    <row r="154" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="26"/>
       <c r="B154" s="27"/>
       <c r="C154" s="24"/>
@@ -3481,7 +3488,7 @@
       <c r="E154" s="24"/>
       <c r="F154" s="25"/>
     </row>
-    <row r="155" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="26"/>
       <c r="B155" s="27"/>
       <c r="C155" s="24"/>
@@ -3489,7 +3496,7 @@
       <c r="E155" s="24"/>
       <c r="F155" s="25"/>
     </row>
-    <row r="156" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="26"/>
       <c r="B156" s="27"/>
       <c r="C156" s="24"/>
@@ -3497,7 +3504,7 @@
       <c r="E156" s="24"/>
       <c r="F156" s="25"/>
     </row>
-    <row r="157" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="26"/>
       <c r="B157" s="27"/>
       <c r="C157" s="24"/>
@@ -3505,7 +3512,7 @@
       <c r="E157" s="24"/>
       <c r="F157" s="25"/>
     </row>
-    <row r="158" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="26"/>
       <c r="B158" s="27"/>
       <c r="C158" s="24"/>
@@ -3513,7 +3520,7 @@
       <c r="E158" s="24"/>
       <c r="F158" s="25"/>
     </row>
-    <row r="159" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="26"/>
       <c r="B159" s="27"/>
       <c r="C159" s="24"/>
@@ -3521,7 +3528,7 @@
       <c r="E159" s="24"/>
       <c r="F159" s="25"/>
     </row>
-    <row r="160" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="26"/>
       <c r="B160" s="27"/>
       <c r="C160" s="24"/>
@@ -3529,7 +3536,7 @@
       <c r="E160" s="24"/>
       <c r="F160" s="25"/>
     </row>
-    <row r="161" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="26"/>
       <c r="B161" s="27"/>
       <c r="C161" s="24"/>
@@ -3537,7 +3544,7 @@
       <c r="E161" s="24"/>
       <c r="F161" s="25"/>
     </row>
-    <row r="162" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="26"/>
       <c r="B162" s="27"/>
       <c r="C162" s="24"/>
@@ -3545,7 +3552,7 @@
       <c r="E162" s="24"/>
       <c r="F162" s="25"/>
     </row>
-    <row r="163" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="26"/>
       <c r="B163" s="27"/>
       <c r="C163" s="24"/>
@@ -3553,7 +3560,7 @@
       <c r="E163" s="24"/>
       <c r="F163" s="25"/>
     </row>
-    <row r="164" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="26"/>
       <c r="B164" s="27"/>
       <c r="C164" s="24"/>
@@ -3561,7 +3568,7 @@
       <c r="E164" s="24"/>
       <c r="F164" s="25"/>
     </row>
-    <row r="165" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="26"/>
       <c r="B165" s="27"/>
       <c r="C165" s="24"/>
@@ -3569,7 +3576,7 @@
       <c r="E165" s="24"/>
       <c r="F165" s="25"/>
     </row>
-    <row r="166" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="26"/>
       <c r="B166" s="27"/>
       <c r="C166" s="24"/>
@@ -3577,7 +3584,7 @@
       <c r="E166" s="24"/>
       <c r="F166" s="25"/>
     </row>
-    <row r="167" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="26"/>
       <c r="B167" s="27"/>
       <c r="C167" s="24"/>
@@ -3585,7 +3592,7 @@
       <c r="E167" s="24"/>
       <c r="F167" s="25"/>
     </row>
-    <row r="168" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="26"/>
       <c r="B168" s="27"/>
       <c r="C168" s="24"/>
@@ -3593,7 +3600,7 @@
       <c r="E168" s="24"/>
       <c r="F168" s="25"/>
     </row>
-    <row r="169" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="26"/>
       <c r="B169" s="27"/>
       <c r="C169" s="24"/>
@@ -3601,7 +3608,7 @@
       <c r="E169" s="24"/>
       <c r="F169" s="25"/>
     </row>
-    <row r="170" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="26"/>
       <c r="B170" s="27"/>
       <c r="C170" s="24"/>
@@ -3609,7 +3616,7 @@
       <c r="E170" s="24"/>
       <c r="F170" s="25"/>
     </row>
-    <row r="171" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="26"/>
       <c r="B171" s="27"/>
       <c r="C171" s="24"/>
@@ -3617,7 +3624,7 @@
       <c r="E171" s="24"/>
       <c r="F171" s="25"/>
     </row>
-    <row r="172" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="26"/>
       <c r="B172" s="27"/>
       <c r="C172" s="24"/>
@@ -3625,7 +3632,7 @@
       <c r="E172" s="24"/>
       <c r="F172" s="25"/>
     </row>
-    <row r="173" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="26"/>
       <c r="B173" s="27"/>
       <c r="C173" s="24"/>
@@ -3633,7 +3640,7 @@
       <c r="E173" s="24"/>
       <c r="F173" s="25"/>
     </row>
-    <row r="174" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="26"/>
       <c r="B174" s="27"/>
       <c r="C174" s="24"/>
@@ -3641,7 +3648,7 @@
       <c r="E174" s="24"/>
       <c r="F174" s="25"/>
     </row>
-    <row r="175" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="26"/>
       <c r="B175" s="27"/>
       <c r="C175" s="24"/>
@@ -3649,7 +3656,7 @@
       <c r="E175" s="24"/>
       <c r="F175" s="25"/>
     </row>
-    <row r="176" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="26"/>
       <c r="B176" s="27"/>
       <c r="C176" s="24"/>
@@ -3657,7 +3664,7 @@
       <c r="E176" s="24"/>
       <c r="F176" s="25"/>
     </row>
-    <row r="177" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="26"/>
       <c r="B177" s="27"/>
       <c r="C177" s="24"/>
@@ -3665,7 +3672,7 @@
       <c r="E177" s="24"/>
       <c r="F177" s="25"/>
     </row>
-    <row r="178" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="26"/>
       <c r="B178" s="27"/>
       <c r="C178" s="24"/>
@@ -3673,7 +3680,7 @@
       <c r="E178" s="24"/>
       <c r="F178" s="25"/>
     </row>
-    <row r="179" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="26"/>
       <c r="B179" s="27"/>
       <c r="C179" s="24"/>
@@ -3681,7 +3688,7 @@
       <c r="E179" s="24"/>
       <c r="F179" s="25"/>
     </row>
-    <row r="180" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="26"/>
       <c r="B180" s="27"/>
       <c r="C180" s="24"/>
@@ -3689,7 +3696,7 @@
       <c r="E180" s="24"/>
       <c r="F180" s="25"/>
     </row>
-    <row r="181" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="26"/>
       <c r="B181" s="27"/>
       <c r="C181" s="24"/>
@@ -3697,7 +3704,7 @@
       <c r="E181" s="24"/>
       <c r="F181" s="25"/>
     </row>
-    <row r="182" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="26"/>
       <c r="B182" s="27"/>
       <c r="C182" s="24"/>
@@ -3705,7 +3712,7 @@
       <c r="E182" s="24"/>
       <c r="F182" s="25"/>
     </row>
-    <row r="183" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="26"/>
       <c r="B183" s="27"/>
       <c r="C183" s="24"/>
@@ -3713,7 +3720,7 @@
       <c r="E183" s="24"/>
       <c r="F183" s="25"/>
     </row>
-    <row r="184" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="26"/>
       <c r="B184" s="27"/>
       <c r="C184" s="24"/>
@@ -3721,7 +3728,7 @@
       <c r="E184" s="24"/>
       <c r="F184" s="25"/>
     </row>
-    <row r="185" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="26"/>
       <c r="B185" s="27"/>
       <c r="C185" s="24"/>
@@ -3729,7 +3736,7 @@
       <c r="E185" s="24"/>
       <c r="F185" s="25"/>
     </row>
-    <row r="186" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="26"/>
       <c r="B186" s="27"/>
       <c r="C186" s="24"/>
@@ -3737,7 +3744,7 @@
       <c r="E186" s="24"/>
       <c r="F186" s="25"/>
     </row>
-    <row r="187" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="26"/>
       <c r="B187" s="27"/>
       <c r="C187" s="24"/>
@@ -3745,7 +3752,7 @@
       <c r="E187" s="24"/>
       <c r="F187" s="25"/>
     </row>
-    <row r="188" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="26"/>
       <c r="B188" s="27"/>
       <c r="C188" s="24"/>
@@ -3753,7 +3760,7 @@
       <c r="E188" s="24"/>
       <c r="F188" s="25"/>
     </row>
-    <row r="189" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="26"/>
       <c r="B189" s="27"/>
       <c r="C189" s="24"/>
@@ -3761,7 +3768,7 @@
       <c r="E189" s="24"/>
       <c r="F189" s="25"/>
     </row>
-    <row r="190" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="26"/>
       <c r="B190" s="27"/>
       <c r="C190" s="24"/>
@@ -3769,7 +3776,7 @@
       <c r="E190" s="24"/>
       <c r="F190" s="25"/>
     </row>
-    <row r="191" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="26"/>
       <c r="B191" s="27"/>
       <c r="C191" s="24"/>
@@ -3777,7 +3784,7 @@
       <c r="E191" s="24"/>
       <c r="F191" s="25"/>
     </row>
-    <row r="192" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="26"/>
       <c r="B192" s="27"/>
       <c r="C192" s="24"/>
@@ -3785,7 +3792,7 @@
       <c r="E192" s="24"/>
       <c r="F192" s="25"/>
     </row>
-    <row r="193" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="26"/>
       <c r="B193" s="27"/>
       <c r="C193" s="24"/>
@@ -3793,7 +3800,7 @@
       <c r="E193" s="24"/>
       <c r="F193" s="25"/>
     </row>
-    <row r="194" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="26"/>
       <c r="B194" s="27"/>
       <c r="C194" s="24"/>
@@ -3801,7 +3808,7 @@
       <c r="E194" s="24"/>
       <c r="F194" s="25"/>
     </row>
-    <row r="195" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="26"/>
       <c r="B195" s="27"/>
       <c r="C195" s="24"/>
@@ -3809,7 +3816,7 @@
       <c r="E195" s="24"/>
       <c r="F195" s="25"/>
     </row>
-    <row r="196" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="26"/>
       <c r="B196" s="27"/>
       <c r="C196" s="24"/>
@@ -3817,7 +3824,7 @@
       <c r="E196" s="24"/>
       <c r="F196" s="25"/>
     </row>
-    <row r="197" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="26"/>
       <c r="B197" s="27"/>
       <c r="C197" s="24"/>
@@ -3825,7 +3832,7 @@
       <c r="E197" s="24"/>
       <c r="F197" s="25"/>
     </row>
-    <row r="198" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="26"/>
       <c r="B198" s="27"/>
       <c r="C198" s="24"/>
@@ -3833,7 +3840,7 @@
       <c r="E198" s="24"/>
       <c r="F198" s="25"/>
     </row>
-    <row r="199" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="26"/>
       <c r="B199" s="27"/>
       <c r="C199" s="24"/>
@@ -3841,7 +3848,7 @@
       <c r="E199" s="24"/>
       <c r="F199" s="25"/>
     </row>
-    <row r="200" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="26"/>
       <c r="B200" s="27"/>
       <c r="C200" s="24"/>
@@ -3849,7 +3856,7 @@
       <c r="E200" s="24"/>
       <c r="F200" s="25"/>
     </row>
-    <row r="201" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="26"/>
       <c r="B201" s="27"/>
       <c r="C201" s="24"/>
@@ -3857,7 +3864,7 @@
       <c r="E201" s="24"/>
       <c r="F201" s="25"/>
     </row>
-    <row r="202" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="26"/>
       <c r="B202" s="27"/>
       <c r="C202" s="24"/>
@@ -3865,7 +3872,7 @@
       <c r="E202" s="24"/>
       <c r="F202" s="25"/>
     </row>
-    <row r="203" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="26"/>
       <c r="B203" s="27"/>
       <c r="C203" s="24"/>
@@ -3873,7 +3880,7 @@
       <c r="E203" s="24"/>
       <c r="F203" s="25"/>
     </row>
-    <row r="204" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="26"/>
       <c r="B204" s="27"/>
       <c r="C204" s="24"/>
@@ -3881,7 +3888,7 @@
       <c r="E204" s="24"/>
       <c r="F204" s="25"/>
     </row>
-    <row r="205" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="26"/>
       <c r="B205" s="27"/>
       <c r="C205" s="24"/>
@@ -3889,7 +3896,7 @@
       <c r="E205" s="24"/>
       <c r="F205" s="25"/>
     </row>
-    <row r="206" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="26"/>
       <c r="B206" s="27"/>
       <c r="C206" s="24"/>
@@ -3897,7 +3904,7 @@
       <c r="E206" s="24"/>
       <c r="F206" s="25"/>
     </row>
-    <row r="207" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="26"/>
       <c r="B207" s="27"/>
       <c r="C207" s="24"/>
@@ -3905,7 +3912,7 @@
       <c r="E207" s="24"/>
       <c r="F207" s="25"/>
     </row>
-    <row r="208" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="26"/>
       <c r="B208" s="27"/>
       <c r="C208" s="24"/>
@@ -3913,7 +3920,7 @@
       <c r="E208" s="24"/>
       <c r="F208" s="25"/>
     </row>
-    <row r="209" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="26"/>
       <c r="B209" s="27"/>
       <c r="C209" s="24"/>
@@ -3921,7 +3928,7 @@
       <c r="E209" s="24"/>
       <c r="F209" s="25"/>
     </row>
-    <row r="210" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="26"/>
       <c r="B210" s="27"/>
       <c r="C210" s="24"/>
@@ -3929,7 +3936,7 @@
       <c r="E210" s="24"/>
       <c r="F210" s="25"/>
     </row>
-    <row r="211" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="26"/>
       <c r="B211" s="27"/>
       <c r="C211" s="24"/>
@@ -3937,7 +3944,7 @@
       <c r="E211" s="24"/>
       <c r="F211" s="25"/>
     </row>
-    <row r="212" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="26"/>
       <c r="B212" s="27"/>
       <c r="C212" s="24"/>
@@ -3945,7 +3952,7 @@
       <c r="E212" s="24"/>
       <c r="F212" s="25"/>
     </row>
-    <row r="213" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="26"/>
       <c r="B213" s="27"/>
       <c r="C213" s="24"/>
@@ -3953,7 +3960,7 @@
       <c r="E213" s="24"/>
       <c r="F213" s="25"/>
     </row>
-    <row r="214" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="26"/>
       <c r="B214" s="27"/>
       <c r="C214" s="24"/>
@@ -3961,7 +3968,7 @@
       <c r="E214" s="24"/>
       <c r="F214" s="25"/>
     </row>
-    <row r="215" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="26"/>
       <c r="B215" s="27"/>
       <c r="C215" s="24"/>
@@ -3969,7 +3976,7 @@
       <c r="E215" s="24"/>
       <c r="F215" s="25"/>
     </row>
-    <row r="216" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="26"/>
       <c r="B216" s="27"/>
       <c r="C216" s="24"/>
@@ -3977,7 +3984,7 @@
       <c r="E216" s="24"/>
       <c r="F216" s="25"/>
     </row>
-    <row r="217" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="26"/>
       <c r="B217" s="27"/>
       <c r="C217" s="24"/>
@@ -3985,7 +3992,7 @@
       <c r="E217" s="24"/>
       <c r="F217" s="25"/>
     </row>
-    <row r="218" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="26"/>
       <c r="B218" s="27"/>
       <c r="C218" s="24"/>
@@ -3993,7 +4000,7 @@
       <c r="E218" s="24"/>
       <c r="F218" s="25"/>
     </row>
-    <row r="219" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="26"/>
       <c r="B219" s="27"/>
       <c r="C219" s="24"/>
@@ -4001,7 +4008,7 @@
       <c r="E219" s="24"/>
       <c r="F219" s="25"/>
     </row>
-    <row r="220" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="26"/>
       <c r="B220" s="27"/>
       <c r="C220" s="24"/>
@@ -4009,7 +4016,7 @@
       <c r="E220" s="24"/>
       <c r="F220" s="25"/>
     </row>
-    <row r="221" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="26"/>
       <c r="B221" s="27"/>
       <c r="C221" s="24"/>
@@ -4017,7 +4024,7 @@
       <c r="E221" s="24"/>
       <c r="F221" s="25"/>
     </row>
-    <row r="222" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="26"/>
       <c r="B222" s="27"/>
       <c r="C222" s="24"/>
@@ -4025,7 +4032,7 @@
       <c r="E222" s="24"/>
       <c r="F222" s="25"/>
     </row>
-    <row r="223" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="26"/>
       <c r="B223" s="27"/>
       <c r="C223" s="24"/>
@@ -4033,7 +4040,7 @@
       <c r="E223" s="24"/>
       <c r="F223" s="25"/>
     </row>
-    <row r="224" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="26"/>
       <c r="B224" s="27"/>
       <c r="C224" s="24"/>
@@ -4041,7 +4048,7 @@
       <c r="E224" s="24"/>
       <c r="F224" s="25"/>
     </row>
-    <row r="225" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="26"/>
       <c r="B225" s="27"/>
       <c r="C225" s="24"/>
@@ -4049,7 +4056,7 @@
       <c r="E225" s="24"/>
       <c r="F225" s="25"/>
     </row>
-    <row r="226" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="26"/>
       <c r="B226" s="27"/>
       <c r="C226" s="24"/>
@@ -4057,7 +4064,7 @@
       <c r="E226" s="24"/>
       <c r="F226" s="25"/>
     </row>
-    <row r="227" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="26"/>
       <c r="B227" s="27"/>
       <c r="C227" s="24"/>
@@ -4065,7 +4072,7 @@
       <c r="E227" s="24"/>
       <c r="F227" s="25"/>
     </row>
-    <row r="228" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="26"/>
       <c r="B228" s="27"/>
       <c r="C228" s="24"/>
@@ -4073,7 +4080,7 @@
       <c r="E228" s="24"/>
       <c r="F228" s="25"/>
     </row>
-    <row r="229" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="26"/>
       <c r="B229" s="27"/>
       <c r="C229" s="24"/>
@@ -4081,7 +4088,7 @@
       <c r="E229" s="24"/>
       <c r="F229" s="25"/>
     </row>
-    <row r="230" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="26"/>
       <c r="B230" s="27"/>
       <c r="C230" s="24"/>
@@ -4089,7 +4096,7 @@
       <c r="E230" s="24"/>
       <c r="F230" s="25"/>
     </row>
-    <row r="231" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="26"/>
       <c r="B231" s="27"/>
       <c r="C231" s="24"/>
@@ -4097,7 +4104,7 @@
       <c r="E231" s="24"/>
       <c r="F231" s="25"/>
     </row>
-    <row r="232" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="26"/>
       <c r="B232" s="27"/>
       <c r="C232" s="24"/>
@@ -4105,7 +4112,7 @@
       <c r="E232" s="24"/>
       <c r="F232" s="25"/>
     </row>
-    <row r="233" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="26"/>
       <c r="B233" s="27"/>
       <c r="C233" s="24"/>
@@ -4113,7 +4120,7 @@
       <c r="E233" s="24"/>
       <c r="F233" s="25"/>
     </row>
-    <row r="234" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="26"/>
       <c r="B234" s="27"/>
       <c r="C234" s="24"/>
@@ -4121,7 +4128,7 @@
       <c r="E234" s="24"/>
       <c r="F234" s="25"/>
     </row>
-    <row r="235" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="26"/>
       <c r="B235" s="27"/>
       <c r="C235" s="24"/>
@@ -4129,7 +4136,7 @@
       <c r="E235" s="24"/>
       <c r="F235" s="25"/>
     </row>
-    <row r="236" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="26"/>
       <c r="B236" s="27"/>
       <c r="C236" s="24"/>
@@ -4137,7 +4144,7 @@
       <c r="E236" s="24"/>
       <c r="F236" s="25"/>
     </row>
-    <row r="237" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="26"/>
       <c r="B237" s="27"/>
       <c r="C237" s="24"/>
@@ -4145,7 +4152,7 @@
       <c r="E237" s="24"/>
       <c r="F237" s="25"/>
     </row>
-    <row r="238" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="26"/>
       <c r="B238" s="27"/>
       <c r="C238" s="24"/>
@@ -4153,7 +4160,7 @@
       <c r="E238" s="24"/>
       <c r="F238" s="25"/>
     </row>
-    <row r="239" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="26"/>
       <c r="B239" s="27"/>
       <c r="C239" s="24"/>
@@ -4161,7 +4168,7 @@
       <c r="E239" s="24"/>
       <c r="F239" s="25"/>
     </row>
-    <row r="240" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="26"/>
       <c r="B240" s="27"/>
       <c r="C240" s="24"/>
@@ -4169,7 +4176,7 @@
       <c r="E240" s="24"/>
       <c r="F240" s="25"/>
     </row>
-    <row r="241" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="26"/>
       <c r="B241" s="27"/>
       <c r="C241" s="24"/>
@@ -4177,7 +4184,7 @@
       <c r="E241" s="24"/>
       <c r="F241" s="25"/>
     </row>
-    <row r="242" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="26"/>
       <c r="B242" s="27"/>
       <c r="C242" s="24"/>
@@ -4185,7 +4192,7 @@
       <c r="E242" s="24"/>
       <c r="F242" s="25"/>
     </row>
-    <row r="243" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="26"/>
       <c r="B243" s="27"/>
       <c r="C243" s="24"/>
@@ -4193,7 +4200,7 @@
       <c r="E243" s="24"/>
       <c r="F243" s="25"/>
     </row>
-    <row r="244" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="26"/>
       <c r="B244" s="27"/>
       <c r="C244" s="24"/>
@@ -4201,7 +4208,7 @@
       <c r="E244" s="24"/>
       <c r="F244" s="25"/>
     </row>
-    <row r="245" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="26"/>
       <c r="B245" s="27"/>
       <c r="C245" s="24"/>
@@ -4209,7 +4216,7 @@
       <c r="E245" s="24"/>
       <c r="F245" s="25"/>
     </row>
-    <row r="246" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="26"/>
       <c r="B246" s="27"/>
       <c r="C246" s="24"/>
@@ -4217,7 +4224,7 @@
       <c r="E246" s="24"/>
       <c r="F246" s="25"/>
     </row>
-    <row r="247" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="26"/>
       <c r="B247" s="27"/>
       <c r="C247" s="24"/>
@@ -4225,7 +4232,7 @@
       <c r="E247" s="24"/>
       <c r="F247" s="25"/>
     </row>
-    <row r="248" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="26"/>
       <c r="B248" s="27"/>
       <c r="C248" s="24"/>
@@ -4233,7 +4240,7 @@
       <c r="E248" s="24"/>
       <c r="F248" s="25"/>
     </row>
-    <row r="249" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="26"/>
       <c r="B249" s="27"/>
       <c r="C249" s="24"/>
@@ -4241,7 +4248,7 @@
       <c r="E249" s="24"/>
       <c r="F249" s="25"/>
     </row>
-    <row r="250" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="26"/>
       <c r="B250" s="27"/>
       <c r="C250" s="24"/>
@@ -4249,7 +4256,7 @@
       <c r="E250" s="24"/>
       <c r="F250" s="25"/>
     </row>
-    <row r="251" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="26"/>
       <c r="B251" s="27"/>
       <c r="C251" s="24"/>
@@ -4257,7 +4264,7 @@
       <c r="E251" s="24"/>
       <c r="F251" s="25"/>
     </row>
-    <row r="252" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="26"/>
       <c r="B252" s="27"/>
       <c r="C252" s="24"/>
@@ -4265,7 +4272,7 @@
       <c r="E252" s="24"/>
       <c r="F252" s="25"/>
     </row>
-    <row r="253" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="26"/>
       <c r="B253" s="27"/>
       <c r="C253" s="24"/>
@@ -4273,7 +4280,7 @@
       <c r="E253" s="24"/>
       <c r="F253" s="25"/>
     </row>
-    <row r="254" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="26"/>
       <c r="B254" s="27"/>
       <c r="C254" s="24"/>
@@ -4281,7 +4288,7 @@
       <c r="E254" s="24"/>
       <c r="F254" s="25"/>
     </row>
-    <row r="255" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="26"/>
       <c r="B255" s="27"/>
       <c r="C255" s="24"/>
@@ -4289,7 +4296,7 @@
       <c r="E255" s="24"/>
       <c r="F255" s="25"/>
     </row>
-    <row r="256" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="26"/>
       <c r="B256" s="27"/>
       <c r="C256" s="24"/>
@@ -4297,7 +4304,7 @@
       <c r="E256" s="24"/>
       <c r="F256" s="25"/>
     </row>
-    <row r="257" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="26"/>
       <c r="B257" s="27"/>
       <c r="C257" s="24"/>
@@ -4305,7 +4312,7 @@
       <c r="E257" s="24"/>
       <c r="F257" s="25"/>
     </row>
-    <row r="258" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="26"/>
       <c r="B258" s="27"/>
       <c r="C258" s="24"/>
@@ -4313,7 +4320,7 @@
       <c r="E258" s="24"/>
       <c r="F258" s="25"/>
     </row>
-    <row r="259" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="26"/>
       <c r="B259" s="27"/>
       <c r="C259" s="24"/>
@@ -4321,7 +4328,7 @@
       <c r="E259" s="24"/>
       <c r="F259" s="25"/>
     </row>
-    <row r="260" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="26"/>
       <c r="B260" s="27"/>
       <c r="C260" s="24"/>
@@ -4329,7 +4336,7 @@
       <c r="E260" s="24"/>
       <c r="F260" s="25"/>
     </row>
-    <row r="261" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="26"/>
       <c r="B261" s="27"/>
       <c r="C261" s="24"/>
@@ -4337,7 +4344,7 @@
       <c r="E261" s="24"/>
       <c r="F261" s="25"/>
     </row>
-    <row r="262" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="26"/>
       <c r="B262" s="27"/>
       <c r="C262" s="24"/>
@@ -4345,7 +4352,7 @@
       <c r="E262" s="24"/>
       <c r="F262" s="25"/>
     </row>
-    <row r="263" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="26"/>
       <c r="B263" s="27"/>
       <c r="C263" s="24"/>
@@ -4353,7 +4360,7 @@
       <c r="E263" s="24"/>
       <c r="F263" s="25"/>
     </row>
-    <row r="264" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="26"/>
       <c r="B264" s="27"/>
       <c r="C264" s="24"/>
@@ -4361,7 +4368,7 @@
       <c r="E264" s="24"/>
       <c r="F264" s="25"/>
     </row>
-    <row r="265" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="26"/>
       <c r="B265" s="27"/>
       <c r="C265" s="24"/>
@@ -4369,7 +4376,7 @@
       <c r="E265" s="24"/>
       <c r="F265" s="25"/>
     </row>
-    <row r="266" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="26"/>
       <c r="B266" s="27"/>
       <c r="C266" s="24"/>
@@ -4377,7 +4384,7 @@
       <c r="E266" s="24"/>
       <c r="F266" s="25"/>
     </row>
-    <row r="267" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="26"/>
       <c r="B267" s="27"/>
       <c r="C267" s="24"/>
@@ -4385,7 +4392,7 @@
       <c r="E267" s="24"/>
       <c r="F267" s="25"/>
     </row>
-    <row r="268" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="26"/>
       <c r="B268" s="27"/>
       <c r="C268" s="24"/>
@@ -4393,7 +4400,7 @@
       <c r="E268" s="24"/>
       <c r="F268" s="25"/>
     </row>
-    <row r="269" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="26"/>
       <c r="B269" s="27"/>
       <c r="C269" s="24"/>
@@ -4401,7 +4408,7 @@
       <c r="E269" s="24"/>
       <c r="F269" s="25"/>
     </row>
-    <row r="270" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="26"/>
       <c r="B270" s="27"/>
       <c r="C270" s="24"/>
@@ -4409,7 +4416,7 @@
       <c r="E270" s="24"/>
       <c r="F270" s="25"/>
     </row>
-    <row r="271" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="26"/>
       <c r="B271" s="27"/>
       <c r="C271" s="24"/>
@@ -4417,7 +4424,7 @@
       <c r="E271" s="24"/>
       <c r="F271" s="25"/>
     </row>
-    <row r="272" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="26"/>
       <c r="B272" s="27"/>
       <c r="C272" s="24"/>
@@ -4425,7 +4432,7 @@
       <c r="E272" s="24"/>
       <c r="F272" s="25"/>
     </row>
-    <row r="273" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="26"/>
       <c r="B273" s="27"/>
       <c r="C273" s="24"/>
@@ -4433,7 +4440,7 @@
       <c r="E273" s="24"/>
       <c r="F273" s="25"/>
     </row>
-    <row r="274" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="26"/>
       <c r="B274" s="27"/>
       <c r="C274" s="24"/>
@@ -4441,7 +4448,7 @@
       <c r="E274" s="24"/>
       <c r="F274" s="25"/>
     </row>
-    <row r="275" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="26"/>
       <c r="B275" s="27"/>
       <c r="C275" s="24"/>
@@ -4449,7 +4456,7 @@
       <c r="E275" s="24"/>
       <c r="F275" s="25"/>
     </row>
-    <row r="276" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="26"/>
       <c r="B276" s="27"/>
       <c r="C276" s="24"/>
@@ -4457,7 +4464,7 @@
       <c r="E276" s="24"/>
       <c r="F276" s="25"/>
     </row>
-    <row r="277" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="26"/>
       <c r="B277" s="27"/>
       <c r="C277" s="24"/>
@@ -4465,7 +4472,7 @@
       <c r="E277" s="24"/>
       <c r="F277" s="25"/>
     </row>
-    <row r="278" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="26"/>
       <c r="B278" s="27"/>
       <c r="C278" s="24"/>
@@ -4473,7 +4480,7 @@
       <c r="E278" s="24"/>
       <c r="F278" s="25"/>
     </row>
-    <row r="279" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="26"/>
       <c r="B279" s="27"/>
       <c r="C279" s="24"/>
@@ -4481,7 +4488,7 @@
       <c r="E279" s="24"/>
       <c r="F279" s="25"/>
     </row>
-    <row r="280" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="26"/>
       <c r="B280" s="27"/>
       <c r="C280" s="24"/>
@@ -4489,7 +4496,7 @@
       <c r="E280" s="24"/>
       <c r="F280" s="25"/>
     </row>
-    <row r="281" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="26"/>
       <c r="B281" s="27"/>
       <c r="C281" s="24"/>
@@ -4497,7 +4504,7 @@
       <c r="E281" s="24"/>
       <c r="F281" s="25"/>
     </row>
-    <row r="282" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="26"/>
       <c r="B282" s="27"/>
       <c r="C282" s="24"/>
@@ -4505,7 +4512,7 @@
       <c r="E282" s="24"/>
       <c r="F282" s="25"/>
     </row>
-    <row r="283" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="26"/>
       <c r="B283" s="27"/>
       <c r="C283" s="24"/>
@@ -4513,7 +4520,7 @@
       <c r="E283" s="24"/>
       <c r="F283" s="25"/>
     </row>
-    <row r="284" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="26"/>
       <c r="B284" s="27"/>
       <c r="C284" s="24"/>
@@ -4521,7 +4528,7 @@
       <c r="E284" s="24"/>
       <c r="F284" s="25"/>
     </row>
-    <row r="285" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="26"/>
       <c r="B285" s="27"/>
       <c r="C285" s="24"/>
@@ -4529,7 +4536,7 @@
       <c r="E285" s="24"/>
       <c r="F285" s="25"/>
     </row>
-    <row r="286" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="26"/>
       <c r="B286" s="27"/>
       <c r="C286" s="24"/>
@@ -4537,7 +4544,7 @@
       <c r="E286" s="24"/>
       <c r="F286" s="25"/>
     </row>
-    <row r="287" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="26"/>
       <c r="B287" s="27"/>
       <c r="C287" s="24"/>
@@ -4545,7 +4552,7 @@
       <c r="E287" s="24"/>
       <c r="F287" s="25"/>
     </row>
-    <row r="288" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="26"/>
       <c r="B288" s="27"/>
       <c r="C288" s="24"/>
@@ -4553,7 +4560,7 @@
       <c r="E288" s="24"/>
       <c r="F288" s="25"/>
     </row>
-    <row r="289" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="26"/>
       <c r="B289" s="27"/>
       <c r="C289" s="24"/>
@@ -4561,7 +4568,7 @@
       <c r="E289" s="24"/>
       <c r="F289" s="25"/>
     </row>
-    <row r="290" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="26"/>
       <c r="B290" s="27"/>
       <c r="C290" s="24"/>
@@ -4569,7 +4576,7 @@
       <c r="E290" s="24"/>
       <c r="F290" s="25"/>
     </row>
-    <row r="291" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="26"/>
       <c r="B291" s="27"/>
       <c r="C291" s="24"/>
@@ -4577,7 +4584,7 @@
       <c r="E291" s="24"/>
       <c r="F291" s="25"/>
     </row>
-    <row r="292" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="26"/>
       <c r="B292" s="27"/>
       <c r="C292" s="24"/>
@@ -4585,7 +4592,7 @@
       <c r="E292" s="24"/>
       <c r="F292" s="25"/>
     </row>
-    <row r="293" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="26"/>
       <c r="B293" s="27"/>
       <c r="C293" s="24"/>
@@ -4593,7 +4600,7 @@
       <c r="E293" s="24"/>
       <c r="F293" s="25"/>
     </row>
-    <row r="294" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="26"/>
       <c r="B294" s="27"/>
       <c r="C294" s="24"/>
@@ -4601,7 +4608,7 @@
       <c r="E294" s="24"/>
       <c r="F294" s="25"/>
     </row>
-    <row r="295" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="26"/>
       <c r="B295" s="27"/>
       <c r="C295" s="24"/>
@@ -4609,7 +4616,7 @@
       <c r="E295" s="24"/>
       <c r="F295" s="25"/>
     </row>
-    <row r="296" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="26"/>
       <c r="B296" s="27"/>
       <c r="C296" s="24"/>
@@ -4617,7 +4624,7 @@
       <c r="E296" s="24"/>
       <c r="F296" s="25"/>
     </row>
-    <row r="297" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="26"/>
       <c r="B297" s="27"/>
       <c r="C297" s="24"/>
@@ -4625,7 +4632,7 @@
       <c r="E297" s="24"/>
       <c r="F297" s="25"/>
     </row>
-    <row r="298" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="26"/>
       <c r="B298" s="27"/>
       <c r="C298" s="24"/>
@@ -4633,7 +4640,7 @@
       <c r="E298" s="24"/>
       <c r="F298" s="25"/>
     </row>
-    <row r="299" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="26"/>
       <c r="B299" s="27"/>
       <c r="C299" s="24"/>
@@ -4641,7 +4648,7 @@
       <c r="E299" s="24"/>
       <c r="F299" s="25"/>
     </row>
-    <row r="300" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="26"/>
       <c r="B300" s="27"/>
       <c r="C300" s="24"/>
@@ -4649,7 +4656,7 @@
       <c r="E300" s="24"/>
       <c r="F300" s="25"/>
     </row>
-    <row r="301" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="26"/>
       <c r="B301" s="27"/>
       <c r="C301" s="24"/>
@@ -4657,7 +4664,7 @@
       <c r="E301" s="24"/>
       <c r="F301" s="25"/>
     </row>
-    <row r="302" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="26"/>
       <c r="B302" s="27"/>
       <c r="C302" s="24"/>
@@ -4665,7 +4672,7 @@
       <c r="E302" s="24"/>
       <c r="F302" s="25"/>
     </row>
-    <row r="303" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="26"/>
       <c r="B303" s="27"/>
       <c r="C303" s="24"/>
@@ -4673,7 +4680,7 @@
       <c r="E303" s="24"/>
       <c r="F303" s="25"/>
     </row>
-    <row r="304" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="26"/>
       <c r="B304" s="27"/>
       <c r="C304" s="24"/>
@@ -4681,7 +4688,7 @@
       <c r="E304" s="24"/>
       <c r="F304" s="25"/>
     </row>
-    <row r="305" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="26"/>
       <c r="B305" s="27"/>
       <c r="C305" s="24"/>
@@ -4689,7 +4696,7 @@
       <c r="E305" s="24"/>
       <c r="F305" s="25"/>
     </row>
-    <row r="306" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="26"/>
       <c r="B306" s="27"/>
       <c r="C306" s="24"/>
@@ -4697,7 +4704,7 @@
       <c r="E306" s="24"/>
       <c r="F306" s="25"/>
     </row>
-    <row r="307" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="26"/>
       <c r="B307" s="27"/>
       <c r="C307" s="24"/>
@@ -4705,7 +4712,7 @@
       <c r="E307" s="24"/>
       <c r="F307" s="25"/>
     </row>
-    <row r="308" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="26"/>
       <c r="B308" s="27"/>
       <c r="C308" s="24"/>
@@ -4713,7 +4720,7 @@
       <c r="E308" s="24"/>
       <c r="F308" s="25"/>
     </row>
-    <row r="309" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="26"/>
       <c r="B309" s="27"/>
       <c r="C309" s="24"/>
@@ -4721,7 +4728,7 @@
       <c r="E309" s="24"/>
       <c r="F309" s="25"/>
     </row>
-    <row r="310" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="26"/>
       <c r="B310" s="27"/>
       <c r="C310" s="24"/>
@@ -4729,7 +4736,7 @@
       <c r="E310" s="24"/>
       <c r="F310" s="25"/>
     </row>
-    <row r="311" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="26"/>
       <c r="B311" s="27"/>
       <c r="C311" s="24"/>
@@ -4737,7 +4744,7 @@
       <c r="E311" s="24"/>
       <c r="F311" s="25"/>
     </row>
-    <row r="312" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="26"/>
       <c r="B312" s="27"/>
       <c r="C312" s="24"/>
@@ -4745,7 +4752,7 @@
       <c r="E312" s="24"/>
       <c r="F312" s="25"/>
     </row>
-    <row r="313" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="26"/>
       <c r="B313" s="27"/>
       <c r="C313" s="24"/>
@@ -4753,7 +4760,7 @@
       <c r="E313" s="24"/>
       <c r="F313" s="25"/>
     </row>
-    <row r="314" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="26"/>
       <c r="B314" s="27"/>
       <c r="C314" s="24"/>
@@ -4761,7 +4768,7 @@
       <c r="E314" s="24"/>
       <c r="F314" s="25"/>
     </row>
-    <row r="315" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="26"/>
       <c r="B315" s="27"/>
       <c r="C315" s="24"/>
@@ -4769,7 +4776,7 @@
       <c r="E315" s="24"/>
       <c r="F315" s="25"/>
     </row>
-    <row r="316" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="26"/>
       <c r="B316" s="27"/>
       <c r="C316" s="24"/>
@@ -4777,7 +4784,7 @@
       <c r="E316" s="24"/>
       <c r="F316" s="25"/>
     </row>
-    <row r="317" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="26"/>
       <c r="B317" s="27"/>
       <c r="C317" s="24"/>
@@ -4785,7 +4792,7 @@
       <c r="E317" s="24"/>
       <c r="F317" s="25"/>
     </row>
-    <row r="318" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="26"/>
       <c r="B318" s="27"/>
       <c r="C318" s="24"/>
@@ -4793,7 +4800,7 @@
       <c r="E318" s="24"/>
       <c r="F318" s="25"/>
     </row>
-    <row r="319" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="26"/>
       <c r="B319" s="27"/>
       <c r="C319" s="24"/>
@@ -4801,7 +4808,7 @@
       <c r="E319" s="24"/>
       <c r="F319" s="25"/>
     </row>
-    <row r="320" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="26"/>
       <c r="B320" s="27"/>
       <c r="C320" s="24"/>
@@ -4809,7 +4816,7 @@
       <c r="E320" s="24"/>
       <c r="F320" s="25"/>
     </row>
-    <row r="321" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="26"/>
       <c r="B321" s="27"/>
       <c r="C321" s="24"/>
@@ -4817,7 +4824,7 @@
       <c r="E321" s="24"/>
       <c r="F321" s="25"/>
     </row>
-    <row r="322" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="26"/>
       <c r="B322" s="27"/>
       <c r="C322" s="24"/>
@@ -4825,7 +4832,7 @@
       <c r="E322" s="24"/>
       <c r="F322" s="25"/>
     </row>
-    <row r="323" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="26"/>
       <c r="B323" s="27"/>
       <c r="C323" s="24"/>
@@ -4833,7 +4840,7 @@
       <c r="E323" s="24"/>
       <c r="F323" s="25"/>
     </row>
-    <row r="324" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="26"/>
       <c r="B324" s="27"/>
       <c r="C324" s="24"/>
@@ -4841,7 +4848,7 @@
       <c r="E324" s="24"/>
       <c r="F324" s="25"/>
     </row>
-    <row r="325" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="26"/>
       <c r="B325" s="27"/>
       <c r="C325" s="24"/>
@@ -4849,7 +4856,7 @@
       <c r="E325" s="24"/>
       <c r="F325" s="25"/>
     </row>
-    <row r="326" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="26"/>
       <c r="B326" s="27"/>
       <c r="C326" s="24"/>
@@ -4857,7 +4864,7 @@
       <c r="E326" s="24"/>
       <c r="F326" s="25"/>
     </row>
-    <row r="327" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="26"/>
       <c r="B327" s="27"/>
       <c r="C327" s="24"/>
@@ -4865,7 +4872,7 @@
       <c r="E327" s="24"/>
       <c r="F327" s="25"/>
     </row>
-    <row r="328" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="26"/>
       <c r="B328" s="27"/>
       <c r="C328" s="24"/>
@@ -4873,7 +4880,7 @@
       <c r="E328" s="24"/>
       <c r="F328" s="25"/>
     </row>
-    <row r="329" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="26"/>
       <c r="B329" s="27"/>
       <c r="C329" s="24"/>
@@ -4881,7 +4888,7 @@
       <c r="E329" s="24"/>
       <c r="F329" s="25"/>
     </row>
-    <row r="330" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="26"/>
       <c r="B330" s="27"/>
       <c r="C330" s="24"/>
@@ -4889,7 +4896,7 @@
       <c r="E330" s="24"/>
       <c r="F330" s="25"/>
     </row>
-    <row r="331" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="26"/>
       <c r="B331" s="27"/>
       <c r="C331" s="24"/>
@@ -4897,7 +4904,7 @@
       <c r="E331" s="24"/>
       <c r="F331" s="25"/>
     </row>
-    <row r="332" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="26"/>
       <c r="B332" s="27"/>
       <c r="C332" s="24"/>
@@ -4905,7 +4912,7 @@
       <c r="E332" s="24"/>
       <c r="F332" s="25"/>
     </row>
-    <row r="333" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="26"/>
       <c r="B333" s="27"/>
       <c r="C333" s="24"/>
@@ -4913,7 +4920,7 @@
       <c r="E333" s="24"/>
       <c r="F333" s="25"/>
     </row>
-    <row r="334" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="26"/>
       <c r="B334" s="27"/>
       <c r="C334" s="24"/>
@@ -4921,7 +4928,7 @@
       <c r="E334" s="24"/>
       <c r="F334" s="25"/>
     </row>
-    <row r="335" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="26"/>
       <c r="B335" s="27"/>
       <c r="C335" s="24"/>
@@ -4929,7 +4936,7 @@
       <c r="E335" s="24"/>
       <c r="F335" s="25"/>
     </row>
-    <row r="336" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="26"/>
       <c r="B336" s="27"/>
       <c r="C336" s="24"/>
@@ -4937,7 +4944,7 @@
       <c r="E336" s="24"/>
       <c r="F336" s="25"/>
     </row>
-    <row r="337" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="26"/>
       <c r="B337" s="27"/>
       <c r="C337" s="24"/>
@@ -4945,7 +4952,7 @@
       <c r="E337" s="24"/>
       <c r="F337" s="25"/>
     </row>
-    <row r="338" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="26"/>
       <c r="B338" s="27"/>
       <c r="C338" s="24"/>
@@ -4953,7 +4960,7 @@
       <c r="E338" s="24"/>
       <c r="F338" s="25"/>
     </row>
-    <row r="339" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="26"/>
       <c r="B339" s="27"/>
       <c r="C339" s="24"/>
@@ -4961,7 +4968,7 @@
       <c r="E339" s="24"/>
       <c r="F339" s="25"/>
     </row>
-    <row r="340" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="26"/>
       <c r="B340" s="27"/>
       <c r="C340" s="24"/>
@@ -4969,7 +4976,7 @@
       <c r="E340" s="24"/>
       <c r="F340" s="25"/>
     </row>
-    <row r="341" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="26"/>
       <c r="B341" s="27"/>
       <c r="C341" s="24"/>
@@ -4977,7 +4984,7 @@
       <c r="E341" s="24"/>
       <c r="F341" s="25"/>
     </row>
-    <row r="342" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="26"/>
       <c r="B342" s="27"/>
       <c r="C342" s="24"/>
@@ -4985,7 +4992,7 @@
       <c r="E342" s="24"/>
       <c r="F342" s="25"/>
     </row>
-    <row r="343" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="26"/>
       <c r="B343" s="27"/>
       <c r="C343" s="24"/>
@@ -4993,7 +5000,7 @@
       <c r="E343" s="24"/>
       <c r="F343" s="25"/>
     </row>
-    <row r="344" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="26"/>
       <c r="B344" s="27"/>
       <c r="C344" s="24"/>
@@ -5001,7 +5008,7 @@
       <c r="E344" s="24"/>
       <c r="F344" s="25"/>
     </row>
-    <row r="345" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="26"/>
       <c r="B345" s="27"/>
       <c r="C345" s="24"/>
@@ -5009,7 +5016,7 @@
       <c r="E345" s="24"/>
       <c r="F345" s="25"/>
     </row>
-    <row r="346" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="26"/>
       <c r="B346" s="27"/>
       <c r="C346" s="24"/>
@@ -5017,7 +5024,7 @@
       <c r="E346" s="24"/>
       <c r="F346" s="25"/>
     </row>
-    <row r="347" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="26"/>
       <c r="B347" s="27"/>
       <c r="C347" s="24"/>
@@ -5025,7 +5032,7 @@
       <c r="E347" s="24"/>
       <c r="F347" s="25"/>
     </row>
-    <row r="348" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="26"/>
       <c r="B348" s="27"/>
       <c r="C348" s="24"/>
@@ -5033,7 +5040,7 @@
       <c r="E348" s="24"/>
       <c r="F348" s="25"/>
     </row>
-    <row r="349" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="26"/>
       <c r="B349" s="27"/>
       <c r="C349" s="24"/>
@@ -5041,7 +5048,7 @@
       <c r="E349" s="24"/>
       <c r="F349" s="25"/>
     </row>
-    <row r="350" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="26"/>
       <c r="B350" s="27"/>
       <c r="C350" s="24"/>
@@ -5049,7 +5056,7 @@
       <c r="E350" s="24"/>
       <c r="F350" s="25"/>
     </row>
-    <row r="351" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="26"/>
       <c r="B351" s="27"/>
       <c r="C351" s="24"/>
@@ -5057,7 +5064,7 @@
       <c r="E351" s="24"/>
       <c r="F351" s="25"/>
     </row>
-    <row r="352" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="26"/>
       <c r="B352" s="27"/>
       <c r="C352" s="24"/>
@@ -5065,7 +5072,7 @@
       <c r="E352" s="24"/>
       <c r="F352" s="25"/>
     </row>
-    <row r="353" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="26"/>
       <c r="B353" s="27"/>
       <c r="C353" s="24"/>
@@ -5073,7 +5080,7 @@
       <c r="E353" s="24"/>
       <c r="F353" s="25"/>
     </row>
-    <row r="354" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="26"/>
       <c r="B354" s="27"/>
       <c r="C354" s="24"/>
@@ -5081,7 +5088,7 @@
       <c r="E354" s="24"/>
       <c r="F354" s="25"/>
     </row>
-    <row r="355" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="26"/>
       <c r="B355" s="27"/>
       <c r="C355" s="24"/>
@@ -5089,7 +5096,7 @@
       <c r="E355" s="24"/>
       <c r="F355" s="25"/>
     </row>
-    <row r="356" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="26"/>
       <c r="B356" s="27"/>
       <c r="C356" s="24"/>
@@ -5097,7 +5104,7 @@
       <c r="E356" s="24"/>
       <c r="F356" s="25"/>
     </row>
-    <row r="357" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="26"/>
       <c r="B357" s="27"/>
       <c r="C357" s="24"/>
@@ -5105,7 +5112,7 @@
       <c r="E357" s="24"/>
       <c r="F357" s="25"/>
     </row>
-    <row r="358" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="26"/>
       <c r="B358" s="27"/>
       <c r="C358" s="24"/>
@@ -5113,7 +5120,7 @@
       <c r="E358" s="24"/>
       <c r="F358" s="25"/>
     </row>
-    <row r="359" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="26"/>
       <c r="B359" s="27"/>
       <c r="C359" s="24"/>
@@ -5121,7 +5128,7 @@
       <c r="E359" s="24"/>
       <c r="F359" s="25"/>
     </row>
-    <row r="360" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="26"/>
       <c r="B360" s="27"/>
       <c r="C360" s="24"/>
@@ -5129,7 +5136,7 @@
       <c r="E360" s="24"/>
       <c r="F360" s="25"/>
     </row>
-    <row r="361" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="26"/>
       <c r="B361" s="27"/>
       <c r="C361" s="24"/>
@@ -5137,7 +5144,7 @@
       <c r="E361" s="24"/>
       <c r="F361" s="25"/>
     </row>
-    <row r="362" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="26"/>
       <c r="B362" s="27"/>
       <c r="C362" s="24"/>
@@ -5145,7 +5152,7 @@
       <c r="E362" s="24"/>
       <c r="F362" s="25"/>
     </row>
-    <row r="363" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="26"/>
       <c r="B363" s="27"/>
       <c r="C363" s="24"/>
@@ -5153,7 +5160,7 @@
       <c r="E363" s="24"/>
       <c r="F363" s="25"/>
     </row>
-    <row r="364" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="26"/>
       <c r="B364" s="27"/>
       <c r="C364" s="24"/>
@@ -5161,7 +5168,7 @@
       <c r="E364" s="24"/>
       <c r="F364" s="25"/>
     </row>
-    <row r="365" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="26"/>
       <c r="B365" s="27"/>
       <c r="C365" s="24"/>
@@ -5169,7 +5176,7 @@
       <c r="E365" s="24"/>
       <c r="F365" s="25"/>
     </row>
-    <row r="366" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="26"/>
       <c r="B366" s="27"/>
       <c r="C366" s="24"/>
@@ -5177,7 +5184,7 @@
       <c r="E366" s="24"/>
       <c r="F366" s="25"/>
     </row>
-    <row r="367" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="26"/>
       <c r="B367" s="27"/>
       <c r="C367" s="24"/>
@@ -5185,7 +5192,7 @@
       <c r="E367" s="24"/>
       <c r="F367" s="25"/>
     </row>
-    <row r="368" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="26"/>
       <c r="B368" s="27"/>
       <c r="C368" s="24"/>
@@ -5193,7 +5200,7 @@
       <c r="E368" s="24"/>
       <c r="F368" s="25"/>
     </row>
-    <row r="369" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="26"/>
       <c r="B369" s="27"/>
       <c r="C369" s="24"/>
@@ -5201,7 +5208,7 @@
       <c r="E369" s="24"/>
       <c r="F369" s="25"/>
     </row>
-    <row r="370" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="26"/>
       <c r="B370" s="27"/>
       <c r="C370" s="24"/>
@@ -5209,7 +5216,7 @@
       <c r="E370" s="24"/>
       <c r="F370" s="25"/>
     </row>
-    <row r="371" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="26"/>
       <c r="B371" s="27"/>
       <c r="C371" s="24"/>
@@ -5217,7 +5224,7 @@
       <c r="E371" s="24"/>
       <c r="F371" s="25"/>
     </row>
-    <row r="372" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="26"/>
       <c r="B372" s="27"/>
       <c r="C372" s="24"/>
@@ -5225,7 +5232,7 @@
       <c r="E372" s="24"/>
       <c r="F372" s="25"/>
     </row>
-    <row r="373" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="26"/>
       <c r="B373" s="27"/>
       <c r="C373" s="24"/>
@@ -5233,7 +5240,7 @@
       <c r="E373" s="24"/>
       <c r="F373" s="25"/>
     </row>
-    <row r="374" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="26"/>
       <c r="B374" s="27"/>
       <c r="C374" s="24"/>
@@ -5241,7 +5248,7 @@
       <c r="E374" s="24"/>
       <c r="F374" s="25"/>
     </row>
-    <row r="375" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="26"/>
       <c r="B375" s="27"/>
       <c r="C375" s="24"/>
@@ -5249,7 +5256,7 @@
       <c r="E375" s="24"/>
       <c r="F375" s="25"/>
     </row>
-    <row r="376" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="26"/>
       <c r="B376" s="27"/>
       <c r="C376" s="24"/>
@@ -5257,7 +5264,7 @@
       <c r="E376" s="24"/>
       <c r="F376" s="25"/>
     </row>
-    <row r="377" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="26"/>
       <c r="B377" s="27"/>
       <c r="C377" s="24"/>
@@ -5265,7 +5272,7 @@
       <c r="E377" s="24"/>
       <c r="F377" s="25"/>
     </row>
-    <row r="378" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="26"/>
       <c r="B378" s="27"/>
       <c r="C378" s="24"/>
@@ -5273,7 +5280,7 @@
       <c r="E378" s="24"/>
       <c r="F378" s="25"/>
     </row>
-    <row r="379" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="26"/>
       <c r="B379" s="27"/>
       <c r="C379" s="24"/>
@@ -5281,7 +5288,7 @@
       <c r="E379" s="24"/>
       <c r="F379" s="25"/>
     </row>
-    <row r="380" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="26"/>
       <c r="B380" s="27"/>
       <c r="C380" s="24"/>
@@ -5289,7 +5296,7 @@
       <c r="E380" s="24"/>
       <c r="F380" s="25"/>
     </row>
-    <row r="381" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="26"/>
       <c r="B381" s="27"/>
       <c r="C381" s="24"/>
@@ -5297,7 +5304,7 @@
       <c r="E381" s="24"/>
       <c r="F381" s="25"/>
     </row>
-    <row r="382" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="26"/>
       <c r="B382" s="27"/>
       <c r="C382" s="24"/>
@@ -5305,7 +5312,7 @@
       <c r="E382" s="24"/>
       <c r="F382" s="25"/>
     </row>
-    <row r="383" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="26"/>
       <c r="B383" s="27"/>
       <c r="C383" s="24"/>
@@ -5313,7 +5320,7 @@
       <c r="E383" s="24"/>
       <c r="F383" s="25"/>
     </row>
-    <row r="384" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="26"/>
       <c r="B384" s="27"/>
       <c r="C384" s="24"/>
@@ -5321,7 +5328,7 @@
       <c r="E384" s="24"/>
       <c r="F384" s="25"/>
     </row>
-    <row r="385" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="26"/>
       <c r="B385" s="27"/>
       <c r="C385" s="24"/>
@@ -5329,7 +5336,7 @@
       <c r="E385" s="24"/>
       <c r="F385" s="25"/>
     </row>
-    <row r="386" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="26"/>
       <c r="B386" s="27"/>
       <c r="C386" s="24"/>
@@ -5337,7 +5344,7 @@
       <c r="E386" s="24"/>
       <c r="F386" s="25"/>
     </row>
-    <row r="387" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="26"/>
       <c r="B387" s="27"/>
       <c r="C387" s="24"/>
@@ -5345,7 +5352,7 @@
       <c r="E387" s="24"/>
       <c r="F387" s="25"/>
     </row>
-    <row r="388" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="26"/>
       <c r="B388" s="27"/>
       <c r="C388" s="24"/>
@@ -5353,7 +5360,7 @@
       <c r="E388" s="24"/>
       <c r="F388" s="25"/>
     </row>
-    <row r="389" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="26"/>
       <c r="B389" s="27"/>
       <c r="C389" s="24"/>
@@ -5361,7 +5368,7 @@
       <c r="E389" s="24"/>
       <c r="F389" s="25"/>
     </row>
-    <row r="390" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="26"/>
       <c r="B390" s="27"/>
       <c r="C390" s="24"/>
@@ -5369,7 +5376,7 @@
       <c r="E390" s="24"/>
       <c r="F390" s="25"/>
     </row>
-    <row r="391" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="26"/>
       <c r="B391" s="27"/>
       <c r="C391" s="24"/>
@@ -5377,7 +5384,7 @@
       <c r="E391" s="24"/>
       <c r="F391" s="25"/>
     </row>
-    <row r="392" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="26"/>
       <c r="B392" s="27"/>
       <c r="C392" s="24"/>
@@ -5385,7 +5392,7 @@
       <c r="E392" s="24"/>
       <c r="F392" s="25"/>
     </row>
-    <row r="393" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="26"/>
       <c r="B393" s="27"/>
       <c r="C393" s="24"/>
@@ -5393,7 +5400,7 @@
       <c r="E393" s="24"/>
       <c r="F393" s="25"/>
     </row>
-    <row r="394" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="26"/>
       <c r="B394" s="27"/>
       <c r="C394" s="24"/>
@@ -5401,7 +5408,7 @@
       <c r="E394" s="24"/>
       <c r="F394" s="25"/>
     </row>
-    <row r="395" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="26"/>
       <c r="B395" s="27"/>
       <c r="C395" s="24"/>
@@ -5409,7 +5416,7 @@
       <c r="E395" s="24"/>
       <c r="F395" s="25"/>
     </row>
-    <row r="396" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="26"/>
       <c r="B396" s="27"/>
       <c r="C396" s="24"/>
@@ -5417,7 +5424,7 @@
       <c r="E396" s="24"/>
       <c r="F396" s="25"/>
     </row>
-    <row r="397" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="26"/>
       <c r="B397" s="27"/>
       <c r="C397" s="24"/>
@@ -5425,7 +5432,7 @@
       <c r="E397" s="24"/>
       <c r="F397" s="25"/>
     </row>
-    <row r="398" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="26"/>
       <c r="B398" s="27"/>
       <c r="C398" s="24"/>
@@ -5433,7 +5440,7 @@
       <c r="E398" s="24"/>
       <c r="F398" s="25"/>
     </row>
-    <row r="399" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="26"/>
       <c r="B399" s="27"/>
       <c r="C399" s="24"/>
@@ -5441,7 +5448,7 @@
       <c r="E399" s="24"/>
       <c r="F399" s="25"/>
     </row>
-    <row r="400" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="26"/>
       <c r="B400" s="27"/>
       <c r="C400" s="24"/>
@@ -5449,7 +5456,7 @@
       <c r="E400" s="24"/>
       <c r="F400" s="25"/>
     </row>
-    <row r="401" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="26"/>
       <c r="B401" s="27"/>
       <c r="C401" s="24"/>
@@ -5457,7 +5464,7 @@
       <c r="E401" s="24"/>
       <c r="F401" s="25"/>
     </row>
-    <row r="402" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="26"/>
       <c r="B402" s="27"/>
       <c r="C402" s="24"/>
@@ -5465,7 +5472,7 @@
       <c r="E402" s="24"/>
       <c r="F402" s="25"/>
     </row>
-    <row r="403" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="26"/>
       <c r="B403" s="27"/>
       <c r="C403" s="24"/>
@@ -5473,7 +5480,7 @@
       <c r="E403" s="24"/>
       <c r="F403" s="25"/>
     </row>
-    <row r="404" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="26"/>
       <c r="B404" s="27"/>
       <c r="C404" s="24"/>
@@ -5481,7 +5488,7 @@
       <c r="E404" s="24"/>
       <c r="F404" s="25"/>
     </row>
-    <row r="405" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="26"/>
       <c r="B405" s="27"/>
       <c r="C405" s="24"/>
@@ -5489,7 +5496,7 @@
       <c r="E405" s="24"/>
       <c r="F405" s="25"/>
     </row>
-    <row r="406" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="26"/>
       <c r="B406" s="27"/>
       <c r="C406" s="24"/>
@@ -5497,7 +5504,7 @@
       <c r="E406" s="24"/>
       <c r="F406" s="25"/>
     </row>
-    <row r="407" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="26"/>
       <c r="B407" s="27"/>
       <c r="C407" s="24"/>
@@ -5505,7 +5512,7 @@
       <c r="E407" s="24"/>
       <c r="F407" s="25"/>
     </row>
-    <row r="408" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="26"/>
       <c r="B408" s="27"/>
       <c r="C408" s="24"/>
@@ -5513,7 +5520,7 @@
       <c r="E408" s="24"/>
       <c r="F408" s="25"/>
     </row>
-    <row r="409" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="26"/>
       <c r="B409" s="27"/>
       <c r="C409" s="24"/>
@@ -5521,7 +5528,7 @@
       <c r="E409" s="24"/>
       <c r="F409" s="25"/>
     </row>
-    <row r="410" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="26"/>
       <c r="B410" s="27"/>
       <c r="C410" s="24"/>
@@ -5529,7 +5536,7 @@
       <c r="E410" s="24"/>
       <c r="F410" s="25"/>
     </row>
-    <row r="411" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="26"/>
       <c r="B411" s="27"/>
       <c r="C411" s="24"/>
@@ -5537,7 +5544,7 @@
       <c r="E411" s="24"/>
       <c r="F411" s="25"/>
     </row>
-    <row r="412" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="26"/>
       <c r="B412" s="27"/>
       <c r="C412" s="24"/>
@@ -5545,7 +5552,7 @@
       <c r="E412" s="24"/>
       <c r="F412" s="25"/>
     </row>
-    <row r="413" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="26"/>
       <c r="B413" s="27"/>
       <c r="C413" s="24"/>
@@ -5553,7 +5560,7 @@
       <c r="E413" s="24"/>
       <c r="F413" s="25"/>
     </row>
-    <row r="414" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="26"/>
       <c r="B414" s="27"/>
       <c r="C414" s="24"/>
@@ -5561,7 +5568,7 @@
       <c r="E414" s="24"/>
       <c r="F414" s="25"/>
     </row>
-    <row r="415" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="26"/>
       <c r="B415" s="27"/>
       <c r="C415" s="24"/>
@@ -5569,7 +5576,7 @@
       <c r="E415" s="24"/>
       <c r="F415" s="25"/>
     </row>
-    <row r="416" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="26"/>
       <c r="B416" s="27"/>
       <c r="C416" s="24"/>
@@ -5577,7 +5584,7 @@
       <c r="E416" s="24"/>
       <c r="F416" s="25"/>
     </row>
-    <row r="417" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="26"/>
       <c r="B417" s="27"/>
       <c r="C417" s="24"/>
@@ -5585,7 +5592,7 @@
       <c r="E417" s="24"/>
       <c r="F417" s="25"/>
     </row>
-    <row r="418" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="26"/>
       <c r="B418" s="27"/>
       <c r="C418" s="24"/>
@@ -5593,7 +5600,7 @@
       <c r="E418" s="24"/>
       <c r="F418" s="25"/>
     </row>
-    <row r="419" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="26"/>
       <c r="B419" s="27"/>
       <c r="C419" s="24"/>
@@ -5601,7 +5608,7 @@
       <c r="E419" s="24"/>
       <c r="F419" s="25"/>
     </row>
-    <row r="420" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="26"/>
       <c r="B420" s="27"/>
       <c r="C420" s="24"/>
@@ -5609,7 +5616,7 @@
       <c r="E420" s="24"/>
       <c r="F420" s="25"/>
     </row>
-    <row r="421" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="26"/>
       <c r="B421" s="27"/>
       <c r="C421" s="24"/>
@@ -5617,7 +5624,7 @@
       <c r="E421" s="24"/>
       <c r="F421" s="25"/>
     </row>
-    <row r="422" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="26"/>
       <c r="B422" s="27"/>
       <c r="C422" s="24"/>
@@ -5625,7 +5632,7 @@
       <c r="E422" s="24"/>
       <c r="F422" s="25"/>
     </row>
-    <row r="423" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="26"/>
       <c r="B423" s="27"/>
       <c r="C423" s="24"/>
@@ -5633,7 +5640,7 @@
       <c r="E423" s="24"/>
       <c r="F423" s="25"/>
     </row>
-    <row r="424" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="26"/>
       <c r="B424" s="27"/>
       <c r="C424" s="24"/>
@@ -5641,7 +5648,7 @@
       <c r="E424" s="24"/>
       <c r="F424" s="25"/>
     </row>
-    <row r="425" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="26"/>
       <c r="B425" s="27"/>
       <c r="C425" s="24"/>
@@ -5649,7 +5656,7 @@
       <c r="E425" s="24"/>
       <c r="F425" s="25"/>
     </row>
-    <row r="426" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="26"/>
       <c r="B426" s="27"/>
       <c r="C426" s="24"/>
@@ -5657,7 +5664,7 @@
       <c r="E426" s="24"/>
       <c r="F426" s="25"/>
     </row>
-    <row r="427" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="26"/>
       <c r="B427" s="27"/>
       <c r="C427" s="24"/>
@@ -5665,7 +5672,7 @@
       <c r="E427" s="24"/>
       <c r="F427" s="25"/>
     </row>
-    <row r="428" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="26"/>
       <c r="B428" s="27"/>
       <c r="C428" s="24"/>
@@ -5673,7 +5680,7 @@
       <c r="E428" s="24"/>
       <c r="F428" s="25"/>
     </row>
-    <row r="429" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="26"/>
       <c r="B429" s="27"/>
       <c r="C429" s="24"/>
@@ -5681,7 +5688,7 @@
       <c r="E429" s="24"/>
       <c r="F429" s="25"/>
     </row>
-    <row r="430" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="26"/>
       <c r="B430" s="27"/>
       <c r="C430" s="24"/>
@@ -5689,7 +5696,7 @@
       <c r="E430" s="24"/>
       <c r="F430" s="25"/>
     </row>
-    <row r="431" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="26"/>
       <c r="B431" s="27"/>
       <c r="C431" s="24"/>
@@ -5697,7 +5704,7 @@
       <c r="E431" s="24"/>
       <c r="F431" s="25"/>
     </row>
-    <row r="432" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="26"/>
       <c r="B432" s="27"/>
       <c r="C432" s="24"/>
@@ -5705,7 +5712,7 @@
       <c r="E432" s="24"/>
       <c r="F432" s="25"/>
     </row>
-    <row r="433" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="26"/>
       <c r="B433" s="27"/>
       <c r="C433" s="24"/>
@@ -5713,7 +5720,7 @@
       <c r="E433" s="24"/>
       <c r="F433" s="25"/>
     </row>
-    <row r="434" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="26"/>
       <c r="B434" s="27"/>
       <c r="C434" s="24"/>
@@ -5721,7 +5728,7 @@
       <c r="E434" s="24"/>
       <c r="F434" s="25"/>
     </row>
-    <row r="435" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="26"/>
       <c r="B435" s="27"/>
       <c r="C435" s="24"/>
@@ -5729,7 +5736,7 @@
       <c r="E435" s="24"/>
       <c r="F435" s="25"/>
     </row>
-    <row r="436" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="26"/>
       <c r="B436" s="27"/>
       <c r="C436" s="24"/>
@@ -5737,7 +5744,7 @@
       <c r="E436" s="24"/>
       <c r="F436" s="25"/>
     </row>
-    <row r="437" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="26"/>
       <c r="B437" s="27"/>
       <c r="C437" s="24"/>
@@ -5745,7 +5752,7 @@
       <c r="E437" s="24"/>
       <c r="F437" s="25"/>
     </row>
-    <row r="438" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="26"/>
       <c r="B438" s="27"/>
       <c r="C438" s="24"/>
@@ -5753,7 +5760,7 @@
       <c r="E438" s="24"/>
       <c r="F438" s="25"/>
     </row>
-    <row r="439" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="26"/>
       <c r="B439" s="27"/>
       <c r="C439" s="24"/>
@@ -5761,7 +5768,7 @@
       <c r="E439" s="24"/>
       <c r="F439" s="25"/>
     </row>
-    <row r="440" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="26"/>
       <c r="B440" s="27"/>
       <c r="C440" s="24"/>
@@ -5769,7 +5776,7 @@
       <c r="E440" s="24"/>
       <c r="F440" s="25"/>
     </row>
-    <row r="441" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="26"/>
       <c r="B441" s="27"/>
       <c r="C441" s="24"/>
@@ -5777,7 +5784,7 @@
       <c r="E441" s="24"/>
       <c r="F441" s="25"/>
     </row>
-    <row r="442" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="26"/>
       <c r="B442" s="27"/>
       <c r="C442" s="24"/>
@@ -5785,7 +5792,7 @@
       <c r="E442" s="24"/>
       <c r="F442" s="25"/>
     </row>
-    <row r="443" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="26"/>
       <c r="B443" s="27"/>
       <c r="C443" s="24"/>
@@ -5793,7 +5800,7 @@
       <c r="E443" s="24"/>
       <c r="F443" s="25"/>
     </row>
-    <row r="444" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="26"/>
       <c r="B444" s="27"/>
       <c r="C444" s="24"/>
@@ -5801,7 +5808,7 @@
       <c r="E444" s="24"/>
       <c r="F444" s="25"/>
     </row>
-    <row r="445" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="26"/>
       <c r="B445" s="27"/>
       <c r="C445" s="24"/>
@@ -5809,7 +5816,7 @@
       <c r="E445" s="24"/>
       <c r="F445" s="25"/>
     </row>
-    <row r="446" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="26"/>
       <c r="B446" s="27"/>
       <c r="C446" s="24"/>
@@ -5817,7 +5824,7 @@
       <c r="E446" s="24"/>
       <c r="F446" s="25"/>
     </row>
-    <row r="447" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="26"/>
       <c r="B447" s="27"/>
       <c r="C447" s="24"/>
@@ -5825,7 +5832,7 @@
       <c r="E447" s="24"/>
       <c r="F447" s="25"/>
     </row>
-    <row r="448" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="26"/>
       <c r="B448" s="27"/>
       <c r="C448" s="24"/>
@@ -5833,7 +5840,7 @@
       <c r="E448" s="24"/>
       <c r="F448" s="25"/>
     </row>
-    <row r="449" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="26"/>
       <c r="B449" s="27"/>
       <c r="C449" s="24"/>
@@ -5841,7 +5848,7 @@
       <c r="E449" s="24"/>
       <c r="F449" s="25"/>
     </row>
-    <row r="450" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="26"/>
       <c r="B450" s="27"/>
       <c r="C450" s="24"/>
@@ -5849,7 +5856,7 @@
       <c r="E450" s="24"/>
       <c r="F450" s="25"/>
     </row>
-    <row r="451" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="26"/>
       <c r="B451" s="27"/>
       <c r="C451" s="24"/>
@@ -5857,7 +5864,7 @@
       <c r="E451" s="24"/>
       <c r="F451" s="25"/>
     </row>
-    <row r="452" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="26"/>
       <c r="B452" s="27"/>
       <c r="C452" s="24"/>
@@ -5865,7 +5872,7 @@
       <c r="E452" s="24"/>
       <c r="F452" s="25"/>
     </row>
-    <row r="453" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="26"/>
       <c r="B453" s="27"/>
       <c r="C453" s="24"/>
@@ -5873,7 +5880,7 @@
       <c r="E453" s="24"/>
       <c r="F453" s="25"/>
     </row>
-    <row r="454" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="26"/>
       <c r="B454" s="27"/>
       <c r="C454" s="24"/>
@@ -5881,7 +5888,7 @@
       <c r="E454" s="24"/>
       <c r="F454" s="25"/>
     </row>
-    <row r="455" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="26"/>
       <c r="B455" s="27"/>
       <c r="C455" s="24"/>
@@ -5889,7 +5896,7 @@
       <c r="E455" s="24"/>
       <c r="F455" s="25"/>
     </row>
-    <row r="456" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="26"/>
       <c r="B456" s="27"/>
       <c r="C456" s="24"/>
@@ -5897,7 +5904,7 @@
       <c r="E456" s="24"/>
       <c r="F456" s="25"/>
     </row>
-    <row r="457" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="26"/>
       <c r="B457" s="27"/>
       <c r="C457" s="24"/>
@@ -5905,7 +5912,7 @@
       <c r="E457" s="24"/>
       <c r="F457" s="25"/>
     </row>
-    <row r="458" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="26"/>
       <c r="B458" s="27"/>
       <c r="C458" s="24"/>
@@ -5913,7 +5920,7 @@
       <c r="E458" s="24"/>
       <c r="F458" s="25"/>
     </row>
-    <row r="459" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="26"/>
       <c r="B459" s="27"/>
       <c r="C459" s="24"/>
@@ -5921,7 +5928,7 @@
       <c r="E459" s="24"/>
       <c r="F459" s="25"/>
     </row>
-    <row r="460" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="26"/>
       <c r="B460" s="27"/>
       <c r="C460" s="24"/>
@@ -5929,7 +5936,7 @@
       <c r="E460" s="24"/>
       <c r="F460" s="25"/>
     </row>
-    <row r="461" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="26"/>
       <c r="B461" s="27"/>
       <c r="C461" s="24"/>
@@ -5937,7 +5944,7 @@
       <c r="E461" s="24"/>
       <c r="F461" s="25"/>
     </row>
-    <row r="462" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="26"/>
       <c r="B462" s="27"/>
       <c r="C462" s="24"/>
@@ -5945,7 +5952,7 @@
       <c r="E462" s="24"/>
       <c r="F462" s="25"/>
     </row>
-    <row r="463" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="26"/>
       <c r="B463" s="27"/>
       <c r="C463" s="24"/>
@@ -5953,7 +5960,7 @@
       <c r="E463" s="24"/>
       <c r="F463" s="25"/>
     </row>
-    <row r="464" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="26"/>
       <c r="B464" s="27"/>
       <c r="C464" s="24"/>
@@ -5961,7 +5968,7 @@
       <c r="E464" s="24"/>
       <c r="F464" s="25"/>
     </row>
-    <row r="465" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="26"/>
       <c r="B465" s="27"/>
       <c r="C465" s="24"/>
@@ -5969,7 +5976,7 @@
       <c r="E465" s="24"/>
       <c r="F465" s="25"/>
     </row>
-    <row r="466" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="26"/>
       <c r="B466" s="27"/>
       <c r="C466" s="24"/>
@@ -5977,7 +5984,7 @@
       <c r="E466" s="24"/>
       <c r="F466" s="25"/>
     </row>
-    <row r="467" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="26"/>
       <c r="B467" s="27"/>
       <c r="C467" s="24"/>
@@ -5985,7 +5992,7 @@
       <c r="E467" s="24"/>
       <c r="F467" s="25"/>
     </row>
-    <row r="468" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="26"/>
       <c r="B468" s="27"/>
       <c r="C468" s="24"/>
@@ -5993,7 +6000,7 @@
       <c r="E468" s="24"/>
       <c r="F468" s="25"/>
     </row>
-    <row r="469" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="26"/>
       <c r="B469" s="27"/>
       <c r="C469" s="24"/>
@@ -6001,7 +6008,7 @@
       <c r="E469" s="24"/>
       <c r="F469" s="25"/>
     </row>
-    <row r="470" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="26"/>
       <c r="B470" s="27"/>
       <c r="C470" s="24"/>
@@ -6009,7 +6016,7 @@
       <c r="E470" s="24"/>
       <c r="F470" s="25"/>
     </row>
-    <row r="471" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="26"/>
       <c r="B471" s="27"/>
       <c r="C471" s="24"/>
@@ -6017,7 +6024,7 @@
       <c r="E471" s="24"/>
       <c r="F471" s="25"/>
     </row>
-    <row r="472" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="26"/>
       <c r="B472" s="27"/>
       <c r="C472" s="24"/>
@@ -6025,7 +6032,7 @@
       <c r="E472" s="24"/>
       <c r="F472" s="25"/>
     </row>
-    <row r="473" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="26"/>
       <c r="B473" s="27"/>
       <c r="C473" s="24"/>
@@ -6033,7 +6040,7 @@
       <c r="E473" s="24"/>
       <c r="F473" s="25"/>
     </row>
-    <row r="474" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="26"/>
       <c r="B474" s="27"/>
       <c r="C474" s="24"/>
@@ -6041,7 +6048,7 @@
       <c r="E474" s="24"/>
       <c r="F474" s="25"/>
     </row>
-    <row r="475" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="26"/>
       <c r="B475" s="27"/>
       <c r="C475" s="24"/>
@@ -6049,7 +6056,7 @@
       <c r="E475" s="24"/>
       <c r="F475" s="25"/>
     </row>
-    <row r="476" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="26"/>
       <c r="B476" s="27"/>
       <c r="C476" s="24"/>
@@ -6057,7 +6064,7 @@
       <c r="E476" s="24"/>
       <c r="F476" s="25"/>
     </row>
-    <row r="477" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="26"/>
       <c r="B477" s="27"/>
       <c r="C477" s="24"/>
@@ -6065,7 +6072,7 @@
       <c r="E477" s="24"/>
       <c r="F477" s="25"/>
     </row>
-    <row r="478" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="26"/>
       <c r="B478" s="27"/>
       <c r="C478" s="24"/>
@@ -6073,7 +6080,7 @@
       <c r="E478" s="24"/>
       <c r="F478" s="25"/>
     </row>
-    <row r="479" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="26"/>
       <c r="B479" s="27"/>
       <c r="C479" s="24"/>
@@ -6081,7 +6088,7 @@
       <c r="E479" s="24"/>
       <c r="F479" s="25"/>
     </row>
-    <row r="480" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="26"/>
       <c r="B480" s="27"/>
       <c r="C480" s="24"/>
@@ -6089,7 +6096,7 @@
       <c r="E480" s="24"/>
       <c r="F480" s="25"/>
     </row>
-    <row r="481" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="26"/>
       <c r="B481" s="27"/>
       <c r="C481" s="24"/>
@@ -6097,7 +6104,7 @@
       <c r="E481" s="24"/>
       <c r="F481" s="25"/>
     </row>
-    <row r="482" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="26"/>
       <c r="B482" s="27"/>
       <c r="C482" s="24"/>
@@ -6105,7 +6112,7 @@
       <c r="E482" s="24"/>
       <c r="F482" s="25"/>
     </row>
-    <row r="483" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="26"/>
       <c r="B483" s="27"/>
       <c r="C483" s="24"/>
@@ -6113,7 +6120,7 @@
       <c r="E483" s="24"/>
       <c r="F483" s="25"/>
     </row>
-    <row r="484" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="26"/>
       <c r="B484" s="27"/>
       <c r="C484" s="24"/>
@@ -6121,7 +6128,7 @@
       <c r="E484" s="24"/>
       <c r="F484" s="25"/>
     </row>
-    <row r="485" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="26"/>
       <c r="B485" s="27"/>
       <c r="C485" s="24"/>
@@ -6129,7 +6136,7 @@
       <c r="E485" s="24"/>
       <c r="F485" s="25"/>
     </row>
-    <row r="486" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="26"/>
       <c r="B486" s="27"/>
       <c r="C486" s="24"/>
@@ -6137,7 +6144,7 @@
       <c r="E486" s="24"/>
       <c r="F486" s="25"/>
     </row>
-    <row r="487" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="26"/>
       <c r="B487" s="27"/>
       <c r="C487" s="24"/>
@@ -6145,7 +6152,7 @@
       <c r="E487" s="24"/>
       <c r="F487" s="25"/>
     </row>
-    <row r="488" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="26"/>
       <c r="B488" s="27"/>
       <c r="C488" s="24"/>
@@ -6153,7 +6160,7 @@
       <c r="E488" s="24"/>
       <c r="F488" s="25"/>
     </row>
-    <row r="489" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="26"/>
       <c r="B489" s="27"/>
       <c r="C489" s="24"/>
@@ -6161,7 +6168,7 @@
       <c r="E489" s="24"/>
       <c r="F489" s="25"/>
     </row>
-    <row r="490" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="26"/>
       <c r="B490" s="27"/>
       <c r="C490" s="24"/>
@@ -6169,7 +6176,7 @@
       <c r="E490" s="24"/>
       <c r="F490" s="25"/>
     </row>
-    <row r="491" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="26"/>
       <c r="B491" s="27"/>
       <c r="C491" s="24"/>
@@ -6177,7 +6184,7 @@
       <c r="E491" s="24"/>
       <c r="F491" s="25"/>
     </row>
-    <row r="492" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="26"/>
       <c r="B492" s="27"/>
       <c r="C492" s="24"/>
@@ -6185,7 +6192,7 @@
       <c r="E492" s="24"/>
       <c r="F492" s="25"/>
     </row>
-    <row r="493" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="26"/>
       <c r="B493" s="27"/>
       <c r="C493" s="24"/>
@@ -6193,7 +6200,7 @@
       <c r="E493" s="24"/>
       <c r="F493" s="25"/>
     </row>
-    <row r="494" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="26"/>
       <c r="B494" s="27"/>
       <c r="C494" s="24"/>
@@ -6201,7 +6208,7 @@
       <c r="E494" s="24"/>
       <c r="F494" s="25"/>
     </row>
-    <row r="495" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="26"/>
       <c r="B495" s="27"/>
       <c r="C495" s="24"/>
@@ -6209,7 +6216,7 @@
       <c r="E495" s="24"/>
       <c r="F495" s="25"/>
     </row>
-    <row r="496" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="26"/>
       <c r="B496" s="27"/>
       <c r="C496" s="24"/>
@@ -6217,7 +6224,7 @@
       <c r="E496" s="24"/>
       <c r="F496" s="25"/>
     </row>
-    <row r="497" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="26"/>
       <c r="B497" s="27"/>
       <c r="C497" s="24"/>
@@ -6225,7 +6232,7 @@
       <c r="E497" s="24"/>
       <c r="F497" s="25"/>
     </row>
-    <row r="498" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="26"/>
       <c r="B498" s="27"/>
       <c r="C498" s="24"/>
@@ -6233,7 +6240,7 @@
       <c r="E498" s="24"/>
       <c r="F498" s="25"/>
     </row>
-    <row r="499" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="26"/>
       <c r="B499" s="27"/>
       <c r="C499" s="24"/>
@@ -6241,7 +6248,7 @@
       <c r="E499" s="24"/>
       <c r="F499" s="25"/>
     </row>
-    <row r="500" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="26"/>
       <c r="B500" s="27"/>
       <c r="C500" s="24"/>
@@ -6249,7 +6256,7 @@
       <c r="E500" s="24"/>
       <c r="F500" s="25"/>
     </row>
-    <row r="501" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="26"/>
       <c r="B501" s="27"/>
       <c r="C501" s="24"/>
@@ -6257,7 +6264,7 @@
       <c r="E501" s="24"/>
       <c r="F501" s="25"/>
     </row>
-    <row r="502" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="26"/>
       <c r="B502" s="27"/>
       <c r="C502" s="24"/>
@@ -6265,7 +6272,7 @@
       <c r="E502" s="24"/>
       <c r="F502" s="25"/>
     </row>
-    <row r="503" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="26"/>
       <c r="B503" s="27"/>
       <c r="C503" s="24"/>
@@ -6273,7 +6280,7 @@
       <c r="E503" s="24"/>
       <c r="F503" s="25"/>
     </row>
-    <row r="504" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="26"/>
       <c r="B504" s="27"/>
       <c r="C504" s="24"/>
@@ -6281,7 +6288,7 @@
       <c r="E504" s="24"/>
       <c r="F504" s="25"/>
     </row>
-    <row r="505" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="26"/>
       <c r="B505" s="27"/>
       <c r="C505" s="24"/>
@@ -6289,7 +6296,7 @@
       <c r="E505" s="24"/>
       <c r="F505" s="25"/>
     </row>
-    <row r="506" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="26"/>
       <c r="B506" s="27"/>
       <c r="C506" s="24"/>
@@ -6297,7 +6304,7 @@
       <c r="E506" s="24"/>
       <c r="F506" s="25"/>
     </row>
-    <row r="507" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="26"/>
       <c r="B507" s="27"/>
       <c r="C507" s="24"/>
@@ -6305,7 +6312,7 @@
       <c r="E507" s="24"/>
       <c r="F507" s="25"/>
     </row>
-    <row r="508" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="26"/>
       <c r="B508" s="27"/>
       <c r="C508" s="24"/>
@@ -6313,7 +6320,7 @@
       <c r="E508" s="24"/>
       <c r="F508" s="25"/>
     </row>
-    <row r="509" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="26"/>
       <c r="B509" s="27"/>
       <c r="C509" s="24"/>
@@ -6321,7 +6328,7 @@
       <c r="E509" s="24"/>
       <c r="F509" s="25"/>
     </row>
-    <row r="510" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="26"/>
       <c r="B510" s="27"/>
       <c r="C510" s="24"/>
@@ -6329,7 +6336,7 @@
       <c r="E510" s="24"/>
       <c r="F510" s="25"/>
     </row>
-    <row r="511" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="26"/>
       <c r="B511" s="27"/>
       <c r="C511" s="24"/>
@@ -6337,7 +6344,7 @@
       <c r="E511" s="24"/>
       <c r="F511" s="25"/>
     </row>
-    <row r="512" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="26"/>
       <c r="B512" s="27"/>
       <c r="C512" s="24"/>
@@ -6345,7 +6352,7 @@
       <c r="E512" s="24"/>
       <c r="F512" s="25"/>
     </row>
-    <row r="513" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="26"/>
       <c r="B513" s="27"/>
       <c r="C513" s="24"/>
@@ -6353,7 +6360,7 @@
       <c r="E513" s="24"/>
       <c r="F513" s="25"/>
     </row>
-    <row r="514" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="26"/>
       <c r="B514" s="27"/>
       <c r="C514" s="24"/>
@@ -6361,7 +6368,7 @@
       <c r="E514" s="24"/>
       <c r="F514" s="25"/>
     </row>
-    <row r="515" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="26"/>
       <c r="B515" s="27"/>
       <c r="C515" s="24"/>
@@ -6369,7 +6376,7 @@
       <c r="E515" s="24"/>
       <c r="F515" s="25"/>
     </row>
-    <row r="516" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="26"/>
       <c r="B516" s="27"/>
       <c r="C516" s="24"/>
@@ -6377,7 +6384,7 @@
       <c r="E516" s="24"/>
       <c r="F516" s="25"/>
     </row>
-    <row r="517" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="26"/>
       <c r="B517" s="27"/>
       <c r="C517" s="24"/>
@@ -6385,7 +6392,7 @@
       <c r="E517" s="24"/>
       <c r="F517" s="25"/>
     </row>
-    <row r="518" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="26"/>
       <c r="B518" s="27"/>
       <c r="C518" s="24"/>
@@ -6393,7 +6400,7 @@
       <c r="E518" s="24"/>
       <c r="F518" s="25"/>
     </row>
-    <row r="519" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="26"/>
       <c r="B519" s="27"/>
       <c r="C519" s="24"/>
@@ -6401,7 +6408,7 @@
       <c r="E519" s="24"/>
       <c r="F519" s="25"/>
     </row>
-    <row r="520" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="26"/>
       <c r="B520" s="27"/>
       <c r="C520" s="24"/>
@@ -6409,7 +6416,7 @@
       <c r="E520" s="24"/>
       <c r="F520" s="25"/>
     </row>
-    <row r="521" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="26"/>
       <c r="B521" s="27"/>
       <c r="C521" s="24"/>
@@ -6417,7 +6424,7 @@
       <c r="E521" s="24"/>
       <c r="F521" s="25"/>
     </row>
-    <row r="522" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="26"/>
       <c r="B522" s="27"/>
       <c r="C522" s="24"/>
@@ -6425,7 +6432,7 @@
       <c r="E522" s="24"/>
       <c r="F522" s="25"/>
     </row>
-    <row r="523" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="26"/>
       <c r="B523" s="27"/>
       <c r="C523" s="24"/>
@@ -6433,7 +6440,7 @@
       <c r="E523" s="24"/>
       <c r="F523" s="25"/>
     </row>
-    <row r="524" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="26"/>
       <c r="B524" s="27"/>
       <c r="C524" s="24"/>
@@ -6441,7 +6448,7 @@
       <c r="E524" s="24"/>
       <c r="F524" s="25"/>
     </row>
-    <row r="525" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="26"/>
       <c r="B525" s="27"/>
       <c r="C525" s="24"/>
@@ -6449,7 +6456,7 @@
       <c r="E525" s="24"/>
       <c r="F525" s="25"/>
     </row>
-    <row r="526" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="26"/>
       <c r="B526" s="27"/>
       <c r="C526" s="24"/>
@@ -6457,7 +6464,7 @@
       <c r="E526" s="24"/>
       <c r="F526" s="25"/>
     </row>
-    <row r="527" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="26"/>
       <c r="B527" s="27"/>
       <c r="C527" s="24"/>
@@ -6465,7 +6472,7 @@
       <c r="E527" s="24"/>
       <c r="F527" s="25"/>
     </row>
-    <row r="528" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="26"/>
       <c r="B528" s="27"/>
       <c r="C528" s="24"/>
@@ -6473,7 +6480,7 @@
       <c r="E528" s="24"/>
       <c r="F528" s="25"/>
     </row>
-    <row r="529" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="26"/>
       <c r="B529" s="27"/>
       <c r="C529" s="24"/>
@@ -6481,7 +6488,7 @@
       <c r="E529" s="24"/>
       <c r="F529" s="25"/>
     </row>
-    <row r="530" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="26"/>
       <c r="B530" s="27"/>
       <c r="C530" s="24"/>
@@ -6489,7 +6496,7 @@
       <c r="E530" s="24"/>
       <c r="F530" s="25"/>
     </row>
-    <row r="531" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="26"/>
       <c r="B531" s="27"/>
       <c r="C531" s="24"/>
@@ -6497,7 +6504,7 @@
       <c r="E531" s="24"/>
       <c r="F531" s="25"/>
     </row>
-    <row r="532" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="26"/>
       <c r="B532" s="27"/>
       <c r="C532" s="24"/>
@@ -6505,7 +6512,7 @@
       <c r="E532" s="24"/>
       <c r="F532" s="25"/>
     </row>
-    <row r="533" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="26"/>
       <c r="B533" s="27"/>
       <c r="C533" s="24"/>
@@ -6513,7 +6520,7 @@
       <c r="E533" s="24"/>
       <c r="F533" s="25"/>
     </row>
-    <row r="534" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="26"/>
       <c r="B534" s="27"/>
       <c r="C534" s="24"/>
@@ -6521,7 +6528,7 @@
       <c r="E534" s="24"/>
       <c r="F534" s="25"/>
     </row>
-    <row r="535" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="26"/>
       <c r="B535" s="27"/>
       <c r="C535" s="24"/>
@@ -6529,7 +6536,7 @@
       <c r="E535" s="24"/>
       <c r="F535" s="25"/>
     </row>
-    <row r="536" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="26"/>
       <c r="B536" s="27"/>
       <c r="C536" s="24"/>
@@ -6537,7 +6544,7 @@
       <c r="E536" s="24"/>
       <c r="F536" s="25"/>
     </row>
-    <row r="537" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="26"/>
       <c r="B537" s="27"/>
       <c r="C537" s="24"/>
@@ -6545,7 +6552,7 @@
       <c r="E537" s="24"/>
       <c r="F537" s="25"/>
     </row>
-    <row r="538" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="26"/>
       <c r="B538" s="27"/>
       <c r="C538" s="24"/>
@@ -6553,7 +6560,7 @@
       <c r="E538" s="24"/>
       <c r="F538" s="25"/>
     </row>
-    <row r="539" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="26"/>
       <c r="B539" s="27"/>
       <c r="C539" s="24"/>
@@ -6561,7 +6568,7 @@
       <c r="E539" s="24"/>
       <c r="F539" s="25"/>
     </row>
-    <row r="540" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="26"/>
       <c r="B540" s="27"/>
       <c r="C540" s="24"/>
@@ -6569,7 +6576,7 @@
       <c r="E540" s="24"/>
       <c r="F540" s="25"/>
     </row>
-    <row r="541" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="26"/>
       <c r="B541" s="27"/>
       <c r="C541" s="24"/>
@@ -6577,7 +6584,7 @@
       <c r="E541" s="24"/>
       <c r="F541" s="25"/>
     </row>
-    <row r="542" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="26"/>
       <c r="B542" s="27"/>
       <c r="C542" s="24"/>
@@ -6585,7 +6592,7 @@
       <c r="E542" s="24"/>
       <c r="F542" s="25"/>
     </row>
-    <row r="543" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="26"/>
       <c r="B543" s="27"/>
       <c r="C543" s="24"/>
@@ -6593,7 +6600,7 @@
       <c r="E543" s="24"/>
       <c r="F543" s="25"/>
     </row>
-    <row r="544" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="26"/>
       <c r="B544" s="27"/>
       <c r="C544" s="24"/>
@@ -6601,7 +6608,7 @@
       <c r="E544" s="24"/>
       <c r="F544" s="25"/>
     </row>
-    <row r="545" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="26"/>
       <c r="B545" s="27"/>
       <c r="C545" s="24"/>
@@ -6609,7 +6616,7 @@
       <c r="E545" s="24"/>
       <c r="F545" s="25"/>
     </row>
-    <row r="546" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="26"/>
       <c r="B546" s="27"/>
       <c r="C546" s="24"/>
@@ -6617,7 +6624,7 @@
       <c r="E546" s="24"/>
       <c r="F546" s="25"/>
     </row>
-    <row r="547" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="26"/>
       <c r="B547" s="27"/>
       <c r="C547" s="24"/>
@@ -6625,7 +6632,7 @@
       <c r="E547" s="24"/>
       <c r="F547" s="25"/>
     </row>
-    <row r="548" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="26"/>
       <c r="B548" s="27"/>
       <c r="C548" s="24"/>
@@ -6633,7 +6640,7 @@
       <c r="E548" s="24"/>
       <c r="F548" s="25"/>
     </row>
-    <row r="549" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="26"/>
       <c r="B549" s="27"/>
       <c r="C549" s="24"/>
@@ -6641,7 +6648,7 @@
       <c r="E549" s="24"/>
       <c r="F549" s="25"/>
     </row>
-    <row r="550" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="26"/>
       <c r="B550" s="27"/>
       <c r="C550" s="24"/>
@@ -6649,7 +6656,7 @@
       <c r="E550" s="24"/>
       <c r="F550" s="25"/>
     </row>
-    <row r="551" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="26"/>
       <c r="B551" s="27"/>
       <c r="C551" s="24"/>
@@ -6657,7 +6664,7 @@
       <c r="E551" s="24"/>
       <c r="F551" s="25"/>
     </row>
-    <row r="552" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="26"/>
       <c r="B552" s="27"/>
       <c r="C552" s="24"/>
@@ -6665,7 +6672,7 @@
       <c r="E552" s="24"/>
       <c r="F552" s="25"/>
     </row>
-    <row r="553" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="26"/>
       <c r="B553" s="27"/>
       <c r="C553" s="24"/>
@@ -6673,7 +6680,7 @@
       <c r="E553" s="24"/>
       <c r="F553" s="25"/>
     </row>
-    <row r="554" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="26"/>
       <c r="B554" s="27"/>
       <c r="C554" s="24"/>
@@ -6681,7 +6688,7 @@
       <c r="E554" s="24"/>
       <c r="F554" s="25"/>
     </row>
-    <row r="555" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="26"/>
       <c r="B555" s="27"/>
       <c r="C555" s="24"/>
@@ -6689,7 +6696,7 @@
       <c r="E555" s="24"/>
       <c r="F555" s="25"/>
     </row>
-    <row r="556" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="26"/>
       <c r="B556" s="27"/>
       <c r="C556" s="24"/>
@@ -6697,7 +6704,7 @@
       <c r="E556" s="24"/>
       <c r="F556" s="25"/>
     </row>
-    <row r="557" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="26"/>
       <c r="B557" s="27"/>
       <c r="C557" s="24"/>
@@ -6705,7 +6712,7 @@
       <c r="E557" s="24"/>
       <c r="F557" s="25"/>
     </row>
-    <row r="558" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="26"/>
       <c r="B558" s="27"/>
       <c r="C558" s="24"/>
@@ -6713,7 +6720,7 @@
       <c r="E558" s="24"/>
       <c r="F558" s="25"/>
     </row>
-    <row r="559" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="26"/>
       <c r="B559" s="27"/>
       <c r="C559" s="24"/>
@@ -6721,7 +6728,7 @@
       <c r="E559" s="24"/>
       <c r="F559" s="25"/>
     </row>
-    <row r="560" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="26"/>
       <c r="B560" s="27"/>
       <c r="C560" s="24"/>
@@ -6729,7 +6736,7 @@
       <c r="E560" s="24"/>
       <c r="F560" s="25"/>
     </row>
-    <row r="561" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="26"/>
       <c r="B561" s="27"/>
       <c r="C561" s="24"/>
@@ -6737,7 +6744,7 @@
       <c r="E561" s="24"/>
       <c r="F561" s="25"/>
     </row>
-    <row r="562" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="26"/>
       <c r="B562" s="27"/>
       <c r="C562" s="24"/>
@@ -6745,7 +6752,7 @@
       <c r="E562" s="24"/>
       <c r="F562" s="25"/>
     </row>
-    <row r="563" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="26"/>
       <c r="B563" s="27"/>
       <c r="C563" s="24"/>
@@ -6753,7 +6760,7 @@
       <c r="E563" s="24"/>
       <c r="F563" s="25"/>
     </row>
-    <row r="564" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="26"/>
       <c r="B564" s="27"/>
       <c r="C564" s="24"/>
@@ -6761,7 +6768,7 @@
       <c r="E564" s="24"/>
       <c r="F564" s="25"/>
     </row>
-    <row r="565" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="26"/>
       <c r="B565" s="27"/>
       <c r="C565" s="24"/>
@@ -6769,7 +6776,7 @@
       <c r="E565" s="24"/>
       <c r="F565" s="25"/>
     </row>
-    <row r="566" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="26"/>
       <c r="B566" s="27"/>
       <c r="C566" s="24"/>
@@ -6777,7 +6784,7 @@
       <c r="E566" s="24"/>
       <c r="F566" s="25"/>
     </row>
-    <row r="567" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="26"/>
       <c r="B567" s="27"/>
       <c r="C567" s="24"/>
@@ -6785,7 +6792,7 @@
       <c r="E567" s="24"/>
       <c r="F567" s="25"/>
     </row>
-    <row r="568" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="26"/>
       <c r="B568" s="27"/>
       <c r="C568" s="24"/>
@@ -6793,7 +6800,7 @@
       <c r="E568" s="24"/>
       <c r="F568" s="25"/>
     </row>
-    <row r="569" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="26"/>
       <c r="B569" s="27"/>
       <c r="C569" s="24"/>
@@ -6801,7 +6808,7 @@
       <c r="E569" s="24"/>
       <c r="F569" s="25"/>
     </row>
-    <row r="570" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="26"/>
       <c r="B570" s="27"/>
       <c r="C570" s="24"/>
@@ -6809,7 +6816,7 @@
       <c r="E570" s="24"/>
       <c r="F570" s="25"/>
     </row>
-    <row r="571" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="26"/>
       <c r="B571" s="27"/>
       <c r="C571" s="24"/>
@@ -6817,7 +6824,7 @@
       <c r="E571" s="24"/>
       <c r="F571" s="25"/>
     </row>
-    <row r="572" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="26"/>
       <c r="B572" s="27"/>
       <c r="C572" s="24"/>
@@ -6825,7 +6832,7 @@
       <c r="E572" s="24"/>
       <c r="F572" s="25"/>
     </row>
-    <row r="573" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="26"/>
       <c r="B573" s="27"/>
       <c r="C573" s="24"/>
@@ -6833,7 +6840,7 @@
       <c r="E573" s="24"/>
       <c r="F573" s="25"/>
     </row>
-    <row r="574" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="26"/>
       <c r="B574" s="27"/>
       <c r="C574" s="24"/>
@@ -6841,7 +6848,7 @@
       <c r="E574" s="24"/>
       <c r="F574" s="25"/>
     </row>
-    <row r="575" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="26"/>
       <c r="B575" s="27"/>
       <c r="C575" s="24"/>
@@ -6849,7 +6856,7 @@
       <c r="E575" s="24"/>
       <c r="F575" s="25"/>
     </row>
-    <row r="576" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="26"/>
       <c r="B576" s="27"/>
       <c r="C576" s="24"/>
@@ -6857,7 +6864,7 @@
       <c r="E576" s="24"/>
       <c r="F576" s="25"/>
     </row>
-    <row r="577" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="26"/>
       <c r="B577" s="27"/>
       <c r="C577" s="24"/>
@@ -6865,7 +6872,7 @@
       <c r="E577" s="24"/>
       <c r="F577" s="25"/>
     </row>
-    <row r="578" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="26"/>
       <c r="B578" s="27"/>
       <c r="C578" s="24"/>
@@ -6873,7 +6880,7 @@
       <c r="E578" s="24"/>
       <c r="F578" s="25"/>
     </row>
-    <row r="579" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="26"/>
       <c r="B579" s="27"/>
       <c r="C579" s="24"/>
@@ -6881,7 +6888,7 @@
       <c r="E579" s="24"/>
       <c r="F579" s="25"/>
     </row>
-    <row r="580" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="26"/>
       <c r="B580" s="27"/>
       <c r="C580" s="24"/>
@@ -6889,7 +6896,7 @@
       <c r="E580" s="24"/>
       <c r="F580" s="25"/>
     </row>
-    <row r="581" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="26"/>
       <c r="B581" s="27"/>
       <c r="C581" s="24"/>
@@ -6897,7 +6904,7 @@
       <c r="E581" s="24"/>
       <c r="F581" s="25"/>
     </row>
-    <row r="582" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="26"/>
       <c r="B582" s="27"/>
       <c r="C582" s="24"/>
@@ -6905,7 +6912,7 @@
       <c r="E582" s="24"/>
       <c r="F582" s="25"/>
     </row>
-    <row r="583" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="26"/>
       <c r="B583" s="27"/>
       <c r="C583" s="24"/>
@@ -6913,7 +6920,7 @@
       <c r="E583" s="24"/>
       <c r="F583" s="25"/>
     </row>
-    <row r="584" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="26"/>
       <c r="B584" s="27"/>
       <c r="C584" s="24"/>
@@ -6921,7 +6928,7 @@
       <c r="E584" s="24"/>
       <c r="F584" s="25"/>
     </row>
-    <row r="585" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="26"/>
       <c r="B585" s="27"/>
       <c r="C585" s="24"/>
@@ -6929,7 +6936,7 @@
       <c r="E585" s="24"/>
       <c r="F585" s="25"/>
     </row>
-    <row r="586" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="26"/>
       <c r="B586" s="27"/>
       <c r="C586" s="24"/>
@@ -6937,7 +6944,7 @@
       <c r="E586" s="24"/>
       <c r="F586" s="25"/>
     </row>
-    <row r="587" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="26"/>
       <c r="B587" s="27"/>
       <c r="C587" s="24"/>
@@ -6945,7 +6952,7 @@
       <c r="E587" s="24"/>
       <c r="F587" s="25"/>
     </row>
-    <row r="588" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="26"/>
       <c r="B588" s="27"/>
       <c r="C588" s="24"/>
@@ -6953,7 +6960,7 @@
       <c r="E588" s="24"/>
       <c r="F588" s="25"/>
     </row>
-    <row r="589" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="26"/>
       <c r="B589" s="27"/>
       <c r="C589" s="24"/>
@@ -6961,7 +6968,7 @@
       <c r="E589" s="24"/>
       <c r="F589" s="25"/>
     </row>
-    <row r="590" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="26"/>
       <c r="B590" s="27"/>
       <c r="C590" s="24"/>
@@ -6969,7 +6976,7 @@
       <c r="E590" s="24"/>
       <c r="F590" s="25"/>
     </row>
-    <row r="591" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="26"/>
       <c r="B591" s="27"/>
       <c r="C591" s="24"/>
@@ -6977,7 +6984,7 @@
       <c r="E591" s="24"/>
       <c r="F591" s="25"/>
     </row>
-    <row r="592" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="26"/>
       <c r="B592" s="27"/>
       <c r="C592" s="24"/>
@@ -6985,7 +6992,7 @@
       <c r="E592" s="24"/>
       <c r="F592" s="25"/>
     </row>
-    <row r="593" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="26"/>
       <c r="B593" s="27"/>
       <c r="C593" s="24"/>
@@ -6993,7 +7000,7 @@
       <c r="E593" s="24"/>
       <c r="F593" s="25"/>
     </row>
-    <row r="594" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="26"/>
       <c r="B594" s="27"/>
       <c r="C594" s="24"/>
@@ -7001,7 +7008,7 @@
       <c r="E594" s="24"/>
       <c r="F594" s="25"/>
     </row>
-    <row r="595" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="26"/>
       <c r="B595" s="27"/>
       <c r="C595" s="24"/>
@@ -7009,7 +7016,7 @@
       <c r="E595" s="24"/>
       <c r="F595" s="25"/>
     </row>
-    <row r="596" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="26"/>
       <c r="B596" s="27"/>
       <c r="C596" s="24"/>
@@ -7017,7 +7024,7 @@
       <c r="E596" s="24"/>
       <c r="F596" s="25"/>
     </row>
-    <row r="597" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="26"/>
       <c r="B597" s="27"/>
       <c r="C597" s="24"/>
@@ -7025,7 +7032,7 @@
       <c r="E597" s="24"/>
       <c r="F597" s="25"/>
     </row>
-    <row r="598" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="26"/>
       <c r="B598" s="27"/>
       <c r="C598" s="24"/>
@@ -7033,7 +7040,7 @@
       <c r="E598" s="24"/>
       <c r="F598" s="25"/>
     </row>
-    <row r="599" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="26"/>
       <c r="B599" s="27"/>
       <c r="C599" s="24"/>
@@ -7041,7 +7048,7 @@
       <c r="E599" s="24"/>
       <c r="F599" s="25"/>
     </row>
-    <row r="600" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="26"/>
       <c r="B600" s="27"/>
       <c r="C600" s="24"/>
@@ -7049,7 +7056,7 @@
       <c r="E600" s="24"/>
       <c r="F600" s="25"/>
     </row>
-    <row r="601" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="26"/>
       <c r="B601" s="27"/>
       <c r="C601" s="24"/>
@@ -7057,7 +7064,7 @@
       <c r="E601" s="24"/>
       <c r="F601" s="25"/>
     </row>
-    <row r="602" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="26"/>
       <c r="B602" s="27"/>
       <c r="C602" s="24"/>
@@ -7065,7 +7072,7 @@
       <c r="E602" s="24"/>
       <c r="F602" s="25"/>
     </row>
-    <row r="603" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="26"/>
       <c r="B603" s="27"/>
       <c r="C603" s="24"/>
@@ -7073,7 +7080,7 @@
       <c r="E603" s="24"/>
       <c r="F603" s="25"/>
     </row>
-    <row r="604" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="26"/>
       <c r="B604" s="27"/>
       <c r="C604" s="24"/>
@@ -7081,7 +7088,7 @@
       <c r="E604" s="24"/>
       <c r="F604" s="25"/>
     </row>
-    <row r="605" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="26"/>
       <c r="B605" s="27"/>
       <c r="C605" s="24"/>
@@ -7089,7 +7096,7 @@
       <c r="E605" s="24"/>
       <c r="F605" s="25"/>
     </row>
-    <row r="606" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="26"/>
       <c r="B606" s="27"/>
       <c r="C606" s="24"/>
@@ -7097,7 +7104,7 @@
       <c r="E606" s="24"/>
       <c r="F606" s="25"/>
     </row>
-    <row r="607" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="26"/>
       <c r="B607" s="27"/>
       <c r="C607" s="24"/>
@@ -7105,7 +7112,7 @@
       <c r="E607" s="24"/>
       <c r="F607" s="25"/>
     </row>
-    <row r="608" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="26"/>
       <c r="B608" s="27"/>
       <c r="C608" s="24"/>
@@ -7113,7 +7120,7 @@
       <c r="E608" s="24"/>
       <c r="F608" s="25"/>
     </row>
-    <row r="609" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="26"/>
       <c r="B609" s="27"/>
       <c r="C609" s="24"/>
@@ -7121,7 +7128,7 @@
       <c r="E609" s="24"/>
       <c r="F609" s="25"/>
     </row>
-    <row r="610" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="26"/>
       <c r="B610" s="27"/>
       <c r="C610" s="24"/>
@@ -7129,7 +7136,7 @@
       <c r="E610" s="24"/>
       <c r="F610" s="25"/>
     </row>
-    <row r="611" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="26"/>
       <c r="B611" s="27"/>
       <c r="C611" s="24"/>
@@ -7137,7 +7144,7 @@
       <c r="E611" s="24"/>
       <c r="F611" s="25"/>
     </row>
-    <row r="612" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="26"/>
       <c r="B612" s="27"/>
       <c r="C612" s="24"/>
@@ -7145,7 +7152,7 @@
       <c r="E612" s="24"/>
       <c r="F612" s="25"/>
     </row>
-    <row r="613" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="26"/>
       <c r="B613" s="27"/>
       <c r="C613" s="24"/>
@@ -7153,7 +7160,7 @@
       <c r="E613" s="24"/>
       <c r="F613" s="25"/>
     </row>
-    <row r="614" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="26"/>
       <c r="B614" s="27"/>
       <c r="C614" s="24"/>
@@ -7161,7 +7168,7 @@
       <c r="E614" s="24"/>
       <c r="F614" s="25"/>
     </row>
-    <row r="615" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="26"/>
       <c r="B615" s="27"/>
       <c r="C615" s="24"/>
@@ -7169,7 +7176,7 @@
       <c r="E615" s="24"/>
       <c r="F615" s="25"/>
     </row>
-    <row r="616" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="26"/>
       <c r="B616" s="27"/>
       <c r="C616" s="24"/>
@@ -7177,7 +7184,7 @@
       <c r="E616" s="24"/>
       <c r="F616" s="25"/>
     </row>
-    <row r="617" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="26"/>
       <c r="B617" s="27"/>
       <c r="C617" s="24"/>
@@ -7185,7 +7192,7 @@
       <c r="E617" s="24"/>
       <c r="F617" s="25"/>
     </row>
-    <row r="618" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="26"/>
       <c r="B618" s="27"/>
       <c r="C618" s="24"/>
@@ -7193,7 +7200,7 @@
       <c r="E618" s="24"/>
       <c r="F618" s="25"/>
     </row>
-    <row r="619" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="26"/>
       <c r="B619" s="27"/>
       <c r="C619" s="24"/>
@@ -7201,7 +7208,7 @@
       <c r="E619" s="24"/>
       <c r="F619" s="25"/>
     </row>
-    <row r="620" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="26"/>
       <c r="B620" s="27"/>
       <c r="C620" s="24"/>
@@ -7209,7 +7216,7 @@
       <c r="E620" s="24"/>
       <c r="F620" s="25"/>
     </row>
-    <row r="621" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="26"/>
       <c r="B621" s="27"/>
       <c r="C621" s="24"/>
@@ -7217,7 +7224,7 @@
       <c r="E621" s="24"/>
       <c r="F621" s="25"/>
     </row>
-    <row r="622" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="26"/>
       <c r="B622" s="27"/>
       <c r="C622" s="24"/>
@@ -7225,7 +7232,7 @@
       <c r="E622" s="24"/>
       <c r="F622" s="25"/>
     </row>
-    <row r="623" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="26"/>
       <c r="B623" s="27"/>
       <c r="C623" s="24"/>
@@ -7233,7 +7240,7 @@
       <c r="E623" s="24"/>
       <c r="F623" s="25"/>
     </row>
-    <row r="624" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="26"/>
       <c r="B624" s="27"/>
       <c r="C624" s="24"/>
@@ -7241,7 +7248,7 @@
       <c r="E624" s="24"/>
       <c r="F624" s="25"/>
     </row>
-    <row r="625" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="26"/>
       <c r="B625" s="27"/>
       <c r="C625" s="24"/>
@@ -7249,7 +7256,7 @@
       <c r="E625" s="24"/>
       <c r="F625" s="25"/>
     </row>
-    <row r="626" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="26"/>
       <c r="B626" s="27"/>
       <c r="C626" s="24"/>
@@ -7257,7 +7264,7 @@
       <c r="E626" s="24"/>
       <c r="F626" s="25"/>
     </row>
-    <row r="627" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="26"/>
       <c r="B627" s="27"/>
       <c r="C627" s="24"/>
@@ -7265,7 +7272,7 @@
       <c r="E627" s="24"/>
       <c r="F627" s="25"/>
     </row>
-    <row r="628" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="26"/>
       <c r="B628" s="27"/>
       <c r="C628" s="24"/>
@@ -7273,7 +7280,7 @@
       <c r="E628" s="24"/>
       <c r="F628" s="25"/>
     </row>
-    <row r="629" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="26"/>
       <c r="B629" s="27"/>
       <c r="C629" s="24"/>
@@ -7281,7 +7288,7 @@
       <c r="E629" s="24"/>
       <c r="F629" s="25"/>
     </row>
-    <row r="630" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="26"/>
       <c r="B630" s="27"/>
       <c r="C630" s="24"/>
@@ -7289,7 +7296,7 @@
       <c r="E630" s="24"/>
       <c r="F630" s="25"/>
     </row>
-    <row r="631" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="26"/>
       <c r="B631" s="27"/>
       <c r="C631" s="24"/>
@@ -7297,7 +7304,7 @@
       <c r="E631" s="24"/>
       <c r="F631" s="25"/>
     </row>
-    <row r="632" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="26"/>
       <c r="B632" s="27"/>
       <c r="C632" s="24"/>
@@ -7305,7 +7312,7 @@
       <c r="E632" s="24"/>
       <c r="F632" s="25"/>
     </row>
-    <row r="633" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="26"/>
       <c r="B633" s="27"/>
       <c r="C633" s="24"/>
@@ -7313,7 +7320,7 @@
       <c r="E633" s="24"/>
       <c r="F633" s="25"/>
     </row>
-    <row r="634" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="26"/>
       <c r="B634" s="27"/>
       <c r="C634" s="24"/>
@@ -7321,7 +7328,7 @@
       <c r="E634" s="24"/>
       <c r="F634" s="25"/>
     </row>
-    <row r="635" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="26"/>
       <c r="B635" s="27"/>
       <c r="C635" s="24"/>
@@ -7329,7 +7336,7 @@
       <c r="E635" s="24"/>
       <c r="F635" s="25"/>
     </row>
-    <row r="636" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="26"/>
       <c r="B636" s="27"/>
       <c r="C636" s="24"/>
@@ -7337,7 +7344,7 @@
       <c r="E636" s="24"/>
       <c r="F636" s="25"/>
     </row>
-    <row r="637" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="26"/>
       <c r="B637" s="27"/>
       <c r="C637" s="24"/>
@@ -7345,7 +7352,7 @@
       <c r="E637" s="24"/>
       <c r="F637" s="25"/>
     </row>
-    <row r="638" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="26"/>
       <c r="B638" s="27"/>
       <c r="C638" s="24"/>
@@ -7353,7 +7360,7 @@
       <c r="E638" s="24"/>
       <c r="F638" s="25"/>
     </row>
-    <row r="639" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="26"/>
       <c r="B639" s="27"/>
       <c r="C639" s="24"/>
@@ -7361,7 +7368,7 @@
       <c r="E639" s="24"/>
       <c r="F639" s="25"/>
     </row>
-    <row r="640" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="26"/>
       <c r="B640" s="27"/>
       <c r="C640" s="24"/>
@@ -7369,7 +7376,7 @@
       <c r="E640" s="24"/>
       <c r="F640" s="25"/>
     </row>
-    <row r="641" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="26"/>
       <c r="B641" s="27"/>
       <c r="C641" s="24"/>
@@ -7377,7 +7384,7 @@
       <c r="E641" s="24"/>
       <c r="F641" s="25"/>
     </row>
-    <row r="642" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="26"/>
       <c r="B642" s="27"/>
       <c r="C642" s="24"/>
@@ -7385,7 +7392,7 @@
       <c r="E642" s="24"/>
       <c r="F642" s="25"/>
     </row>
-    <row r="643" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="26"/>
       <c r="B643" s="27"/>
       <c r="C643" s="24"/>
@@ -7393,7 +7400,7 @@
       <c r="E643" s="24"/>
       <c r="F643" s="25"/>
     </row>
-    <row r="644" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="26"/>
       <c r="B644" s="27"/>
       <c r="C644" s="24"/>
@@ -7401,7 +7408,7 @@
       <c r="E644" s="24"/>
       <c r="F644" s="25"/>
     </row>
-    <row r="645" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="26"/>
       <c r="B645" s="27"/>
       <c r="C645" s="24"/>
@@ -7409,7 +7416,7 @@
       <c r="E645" s="24"/>
       <c r="F645" s="25"/>
     </row>
-    <row r="646" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="26"/>
       <c r="B646" s="27"/>
       <c r="C646" s="24"/>
@@ -7417,7 +7424,7 @@
       <c r="E646" s="24"/>
       <c r="F646" s="25"/>
     </row>
-    <row r="647" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="26"/>
       <c r="B647" s="27"/>
       <c r="C647" s="24"/>
@@ -7425,7 +7432,7 @@
       <c r="E647" s="24"/>
       <c r="F647" s="25"/>
     </row>
-    <row r="648" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="26"/>
       <c r="B648" s="27"/>
       <c r="C648" s="24"/>
@@ -7433,7 +7440,7 @@
       <c r="E648" s="24"/>
       <c r="F648" s="25"/>
     </row>
-    <row r="649" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="26"/>
       <c r="B649" s="27"/>
       <c r="C649" s="24"/>
@@ -7441,7 +7448,7 @@
       <c r="E649" s="24"/>
       <c r="F649" s="25"/>
     </row>
-    <row r="650" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="26"/>
       <c r="B650" s="27"/>
       <c r="C650" s="24"/>
@@ -7449,7 +7456,7 @@
       <c r="E650" s="24"/>
       <c r="F650" s="25"/>
     </row>
-    <row r="651" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="26"/>
       <c r="B651" s="27"/>
       <c r="C651" s="24"/>
@@ -7457,7 +7464,7 @@
       <c r="E651" s="24"/>
       <c r="F651" s="25"/>
     </row>
-    <row r="652" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="26"/>
       <c r="B652" s="27"/>
       <c r="C652" s="24"/>
@@ -7465,7 +7472,7 @@
       <c r="E652" s="24"/>
       <c r="F652" s="25"/>
     </row>
-    <row r="653" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="26"/>
       <c r="B653" s="27"/>
       <c r="C653" s="24"/>
@@ -7473,7 +7480,7 @@
       <c r="E653" s="24"/>
       <c r="F653" s="25"/>
     </row>
-    <row r="654" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="26"/>
       <c r="B654" s="27"/>
       <c r="C654" s="24"/>
@@ -7481,7 +7488,7 @@
       <c r="E654" s="24"/>
       <c r="F654" s="25"/>
     </row>
-    <row r="655" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="26"/>
       <c r="B655" s="27"/>
       <c r="C655" s="24"/>
@@ -7489,7 +7496,7 @@
       <c r="E655" s="24"/>
       <c r="F655" s="25"/>
     </row>
-    <row r="656" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="26"/>
       <c r="B656" s="27"/>
       <c r="C656" s="24"/>
@@ -7497,7 +7504,7 @@
       <c r="E656" s="24"/>
       <c r="F656" s="25"/>
     </row>
-    <row r="657" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="26"/>
       <c r="B657" s="27"/>
       <c r="C657" s="24"/>
@@ -7505,7 +7512,7 @@
       <c r="E657" s="24"/>
       <c r="F657" s="25"/>
     </row>
-    <row r="658" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="26"/>
       <c r="B658" s="27"/>
       <c r="C658" s="24"/>
@@ -7513,7 +7520,7 @@
       <c r="E658" s="24"/>
       <c r="F658" s="25"/>
     </row>
-    <row r="659" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="26"/>
       <c r="B659" s="27"/>
       <c r="C659" s="24"/>
@@ -7521,7 +7528,7 @@
       <c r="E659" s="24"/>
       <c r="F659" s="25"/>
     </row>
-    <row r="660" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="26"/>
       <c r="B660" s="27"/>
       <c r="C660" s="24"/>
@@ -7529,7 +7536,7 @@
       <c r="E660" s="24"/>
       <c r="F660" s="25"/>
     </row>
-    <row r="661" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="26"/>
       <c r="B661" s="27"/>
       <c r="C661" s="24"/>
@@ -7537,7 +7544,7 @@
       <c r="E661" s="24"/>
       <c r="F661" s="25"/>
     </row>
-    <row r="662" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="26"/>
       <c r="B662" s="27"/>
       <c r="C662" s="24"/>
@@ -7545,7 +7552,7 @@
       <c r="E662" s="24"/>
       <c r="F662" s="25"/>
     </row>
-    <row r="663" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="26"/>
       <c r="B663" s="27"/>
       <c r="C663" s="24"/>
@@ -7553,7 +7560,7 @@
       <c r="E663" s="24"/>
       <c r="F663" s="25"/>
     </row>
-    <row r="664" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="26"/>
       <c r="B664" s="27"/>
       <c r="C664" s="24"/>
@@ -7561,7 +7568,7 @@
       <c r="E664" s="24"/>
       <c r="F664" s="25"/>
     </row>
-    <row r="665" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="26"/>
       <c r="B665" s="27"/>
       <c r="C665" s="24"/>
@@ -7569,7 +7576,7 @@
       <c r="E665" s="24"/>
       <c r="F665" s="25"/>
     </row>
-    <row r="666" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="26"/>
       <c r="B666" s="27"/>
       <c r="C666" s="24"/>
@@ -7577,7 +7584,7 @@
       <c r="E666" s="24"/>
       <c r="F666" s="25"/>
     </row>
-    <row r="667" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="26"/>
       <c r="B667" s="27"/>
       <c r="C667" s="24"/>
@@ -7585,7 +7592,7 @@
       <c r="E667" s="24"/>
       <c r="F667" s="25"/>
     </row>
-    <row r="668" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="26"/>
       <c r="B668" s="27"/>
       <c r="C668" s="24"/>
@@ -7593,7 +7600,7 @@
       <c r="E668" s="24"/>
       <c r="F668" s="25"/>
     </row>
-    <row r="669" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="26"/>
       <c r="B669" s="27"/>
       <c r="C669" s="24"/>
@@ -7601,7 +7608,7 @@
       <c r="E669" s="24"/>
       <c r="F669" s="25"/>
     </row>
-    <row r="670" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="26"/>
       <c r="B670" s="27"/>
       <c r="C670" s="24"/>
@@ -7609,7 +7616,7 @@
       <c r="E670" s="24"/>
       <c r="F670" s="25"/>
     </row>
-    <row r="671" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="26"/>
       <c r="B671" s="27"/>
       <c r="C671" s="24"/>
@@ -7617,7 +7624,7 @@
       <c r="E671" s="24"/>
       <c r="F671" s="25"/>
     </row>
-    <row r="672" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="26"/>
       <c r="B672" s="27"/>
       <c r="C672" s="24"/>
@@ -7625,7 +7632,7 @@
       <c r="E672" s="24"/>
       <c r="F672" s="25"/>
     </row>
-    <row r="673" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="26"/>
       <c r="B673" s="27"/>
       <c r="C673" s="24"/>
@@ -7633,7 +7640,7 @@
       <c r="E673" s="24"/>
       <c r="F673" s="25"/>
     </row>
-    <row r="674" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="26"/>
       <c r="B674" s="27"/>
       <c r="C674" s="24"/>
@@ -7641,7 +7648,7 @@
       <c r="E674" s="24"/>
       <c r="F674" s="25"/>
     </row>
-    <row r="675" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="26"/>
       <c r="B675" s="27"/>
       <c r="C675" s="24"/>
@@ -7649,7 +7656,7 @@
       <c r="E675" s="24"/>
       <c r="F675" s="25"/>
     </row>
-    <row r="676" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="26"/>
       <c r="B676" s="27"/>
       <c r="C676" s="24"/>
@@ -7657,7 +7664,7 @@
       <c r="E676" s="24"/>
       <c r="F676" s="25"/>
     </row>
-    <row r="677" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="26"/>
       <c r="B677" s="27"/>
       <c r="C677" s="24"/>
@@ -7665,7 +7672,7 @@
       <c r="E677" s="24"/>
       <c r="F677" s="25"/>
     </row>
-    <row r="678" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="26"/>
       <c r="B678" s="27"/>
       <c r="C678" s="24"/>
@@ -7673,7 +7680,7 @@
       <c r="E678" s="24"/>
       <c r="F678" s="25"/>
     </row>
-    <row r="679" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="26"/>
       <c r="B679" s="27"/>
       <c r="C679" s="24"/>
@@ -7681,7 +7688,7 @@
       <c r="E679" s="24"/>
       <c r="F679" s="25"/>
     </row>
-    <row r="680" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="26"/>
       <c r="B680" s="27"/>
       <c r="C680" s="24"/>
@@ -7689,7 +7696,7 @@
       <c r="E680" s="24"/>
       <c r="F680" s="25"/>
     </row>
-    <row r="681" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="26"/>
       <c r="B681" s="27"/>
       <c r="C681" s="24"/>
@@ -7697,7 +7704,7 @@
       <c r="E681" s="24"/>
       <c r="F681" s="25"/>
     </row>
-    <row r="682" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="26"/>
       <c r="B682" s="27"/>
       <c r="C682" s="24"/>
@@ -7705,7 +7712,7 @@
       <c r="E682" s="24"/>
       <c r="F682" s="25"/>
     </row>
-    <row r="683" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="26"/>
       <c r="B683" s="27"/>
       <c r="C683" s="24"/>
@@ -7713,7 +7720,7 @@
       <c r="E683" s="24"/>
       <c r="F683" s="25"/>
     </row>
-    <row r="684" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="26"/>
       <c r="B684" s="27"/>
       <c r="C684" s="24"/>
@@ -7721,7 +7728,7 @@
       <c r="E684" s="24"/>
       <c r="F684" s="25"/>
     </row>
-    <row r="685" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="26"/>
       <c r="B685" s="27"/>
       <c r="C685" s="24"/>
@@ -7729,7 +7736,7 @@
       <c r="E685" s="24"/>
       <c r="F685" s="25"/>
     </row>
-    <row r="686" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="26"/>
       <c r="B686" s="27"/>
       <c r="C686" s="24"/>
@@ -7737,7 +7744,7 @@
       <c r="E686" s="24"/>
       <c r="F686" s="25"/>
     </row>
-    <row r="687" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="26"/>
       <c r="B687" s="27"/>
       <c r="C687" s="24"/>
@@ -7745,7 +7752,7 @@
       <c r="E687" s="24"/>
       <c r="F687" s="25"/>
     </row>
-    <row r="688" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="26"/>
       <c r="B688" s="27"/>
       <c r="C688" s="24"/>
@@ -7753,7 +7760,7 @@
       <c r="E688" s="24"/>
       <c r="F688" s="25"/>
     </row>
-    <row r="689" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="26"/>
       <c r="B689" s="27"/>
       <c r="C689" s="24"/>
@@ -7761,7 +7768,7 @@
       <c r="E689" s="24"/>
       <c r="F689" s="25"/>
     </row>
-    <row r="690" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="26"/>
       <c r="B690" s="27"/>
       <c r="C690" s="24"/>
@@ -7769,7 +7776,7 @@
       <c r="E690" s="24"/>
       <c r="F690" s="25"/>
     </row>
-    <row r="691" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="26"/>
       <c r="B691" s="27"/>
       <c r="C691" s="24"/>
@@ -7777,7 +7784,7 @@
       <c r="E691" s="24"/>
       <c r="F691" s="25"/>
     </row>
-    <row r="692" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="26"/>
       <c r="B692" s="27"/>
       <c r="C692" s="24"/>
@@ -7785,7 +7792,7 @@
       <c r="E692" s="24"/>
       <c r="F692" s="25"/>
     </row>
-    <row r="693" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="26"/>
       <c r="B693" s="27"/>
       <c r="C693" s="24"/>
@@ -7793,7 +7800,7 @@
       <c r="E693" s="24"/>
       <c r="F693" s="25"/>
     </row>
-    <row r="694" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="26"/>
       <c r="B694" s="27"/>
       <c r="C694" s="24"/>
@@ -7801,7 +7808,7 @@
       <c r="E694" s="24"/>
       <c r="F694" s="25"/>
     </row>
-    <row r="695" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="26"/>
       <c r="B695" s="27"/>
       <c r="C695" s="24"/>
@@ -7809,7 +7816,7 @@
       <c r="E695" s="24"/>
       <c r="F695" s="25"/>
     </row>
-    <row r="696" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="26"/>
       <c r="B696" s="27"/>
       <c r="C696" s="24"/>
@@ -7817,7 +7824,7 @@
       <c r="E696" s="24"/>
       <c r="F696" s="25"/>
     </row>
-    <row r="697" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="26"/>
       <c r="B697" s="27"/>
       <c r="C697" s="24"/>
@@ -7825,7 +7832,7 @@
       <c r="E697" s="24"/>
       <c r="F697" s="25"/>
     </row>
-    <row r="698" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="26"/>
       <c r="B698" s="27"/>
       <c r="C698" s="24"/>
@@ -7833,7 +7840,7 @@
       <c r="E698" s="24"/>
       <c r="F698" s="25"/>
     </row>
-    <row r="699" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="26"/>
       <c r="B699" s="27"/>
       <c r="C699" s="24"/>
@@ -7841,7 +7848,7 @@
       <c r="E699" s="24"/>
       <c r="F699" s="25"/>
     </row>
-    <row r="700" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="26"/>
       <c r="B700" s="27"/>
       <c r="C700" s="24"/>
@@ -7849,7 +7856,7 @@
       <c r="E700" s="24"/>
       <c r="F700" s="25"/>
     </row>
-    <row r="701" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="26"/>
       <c r="B701" s="27"/>
       <c r="C701" s="24"/>
@@ -7857,7 +7864,7 @@
       <c r="E701" s="24"/>
       <c r="F701" s="25"/>
     </row>
-    <row r="702" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="26"/>
       <c r="B702" s="27"/>
       <c r="C702" s="24"/>
@@ -7865,7 +7872,7 @@
       <c r="E702" s="24"/>
       <c r="F702" s="25"/>
     </row>
-    <row r="703" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="26"/>
       <c r="B703" s="27"/>
       <c r="C703" s="24"/>
@@ -7873,7 +7880,7 @@
       <c r="E703" s="24"/>
       <c r="F703" s="25"/>
     </row>
-    <row r="704" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="26"/>
       <c r="B704" s="27"/>
       <c r="C704" s="24"/>
@@ -7881,7 +7888,7 @@
       <c r="E704" s="24"/>
       <c r="F704" s="25"/>
     </row>
-    <row r="705" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="26"/>
       <c r="B705" s="27"/>
       <c r="C705" s="24"/>
@@ -7889,7 +7896,7 @@
       <c r="E705" s="24"/>
       <c r="F705" s="25"/>
     </row>
-    <row r="706" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="26"/>
       <c r="B706" s="27"/>
       <c r="C706" s="24"/>
@@ -7897,7 +7904,7 @@
       <c r="E706" s="24"/>
       <c r="F706" s="25"/>
     </row>
-    <row r="707" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="26"/>
       <c r="B707" s="27"/>
       <c r="C707" s="24"/>
@@ -7905,7 +7912,7 @@
       <c r="E707" s="24"/>
       <c r="F707" s="25"/>
     </row>
-    <row r="708" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="26"/>
       <c r="B708" s="27"/>
       <c r="C708" s="24"/>
@@ -7913,7 +7920,7 @@
       <c r="E708" s="24"/>
       <c r="F708" s="25"/>
     </row>
-    <row r="709" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="26"/>
       <c r="B709" s="27"/>
       <c r="C709" s="24"/>
@@ -7921,7 +7928,7 @@
       <c r="E709" s="24"/>
       <c r="F709" s="25"/>
     </row>
-    <row r="710" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="26"/>
       <c r="B710" s="27"/>
       <c r="C710" s="24"/>
@@ -7929,7 +7936,7 @@
       <c r="E710" s="24"/>
       <c r="F710" s="25"/>
     </row>
-    <row r="711" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="26"/>
       <c r="B711" s="27"/>
       <c r="C711" s="24"/>
@@ -7937,7 +7944,7 @@
       <c r="E711" s="24"/>
       <c r="F711" s="25"/>
     </row>
-    <row r="712" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="26"/>
       <c r="B712" s="27"/>
       <c r="C712" s="24"/>
@@ -7945,7 +7952,7 @@
       <c r="E712" s="24"/>
       <c r="F712" s="25"/>
     </row>
-    <row r="713" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="26"/>
       <c r="B713" s="27"/>
       <c r="C713" s="24"/>
@@ -7953,7 +7960,7 @@
       <c r="E713" s="24"/>
       <c r="F713" s="25"/>
     </row>
-    <row r="714" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="26"/>
       <c r="B714" s="27"/>
       <c r="C714" s="24"/>
@@ -7961,7 +7968,7 @@
       <c r="E714" s="24"/>
       <c r="F714" s="25"/>
     </row>
-    <row r="715" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="26"/>
       <c r="B715" s="27"/>
       <c r="C715" s="24"/>
@@ -7969,7 +7976,7 @@
       <c r="E715" s="24"/>
       <c r="F715" s="25"/>
     </row>
-    <row r="716" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="26"/>
       <c r="B716" s="27"/>
       <c r="C716" s="24"/>
@@ -7977,7 +7984,7 @@
       <c r="E716" s="24"/>
       <c r="F716" s="25"/>
     </row>
-    <row r="717" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="26"/>
       <c r="B717" s="27"/>
       <c r="C717" s="24"/>
@@ -7985,7 +7992,7 @@
       <c r="E717" s="24"/>
       <c r="F717" s="25"/>
     </row>
-    <row r="718" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="26"/>
       <c r="B718" s="27"/>
       <c r="C718" s="24"/>
@@ -7993,7 +8000,7 @@
       <c r="E718" s="24"/>
       <c r="F718" s="25"/>
     </row>
-    <row r="719" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="26"/>
       <c r="B719" s="27"/>
       <c r="C719" s="24"/>
@@ -8001,7 +8008,7 @@
       <c r="E719" s="24"/>
       <c r="F719" s="25"/>
     </row>
-    <row r="720" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="26"/>
       <c r="B720" s="27"/>
       <c r="C720" s="24"/>
@@ -8009,7 +8016,7 @@
       <c r="E720" s="24"/>
       <c r="F720" s="25"/>
     </row>
-    <row r="721" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="26"/>
       <c r="B721" s="27"/>
       <c r="C721" s="24"/>
@@ -8017,7 +8024,7 @@
       <c r="E721" s="24"/>
       <c r="F721" s="25"/>
     </row>
-    <row r="722" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="26"/>
       <c r="B722" s="27"/>
       <c r="C722" s="24"/>
@@ -8025,7 +8032,7 @@
       <c r="E722" s="24"/>
       <c r="F722" s="25"/>
     </row>
-    <row r="723" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="26"/>
       <c r="B723" s="27"/>
       <c r="C723" s="24"/>
@@ -8033,7 +8040,7 @@
       <c r="E723" s="24"/>
       <c r="F723" s="25"/>
     </row>
-    <row r="724" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="26"/>
       <c r="B724" s="27"/>
       <c r="C724" s="24"/>
@@ -8041,7 +8048,7 @@
       <c r="E724" s="24"/>
       <c r="F724" s="25"/>
     </row>
-    <row r="725" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="26"/>
       <c r="B725" s="27"/>
       <c r="C725" s="24"/>
@@ -8049,7 +8056,7 @@
       <c r="E725" s="24"/>
       <c r="F725" s="25"/>
     </row>
-    <row r="726" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="26"/>
       <c r="B726" s="27"/>
       <c r="C726" s="24"/>
@@ -8057,7 +8064,7 @@
       <c r="E726" s="24"/>
       <c r="F726" s="25"/>
     </row>
-    <row r="727" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="26"/>
       <c r="B727" s="27"/>
       <c r="C727" s="24"/>
@@ -8065,7 +8072,7 @@
       <c r="E727" s="24"/>
       <c r="F727" s="25"/>
     </row>
-    <row r="728" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="26"/>
       <c r="B728" s="27"/>
       <c r="C728" s="24"/>
@@ -8073,7 +8080,7 @@
       <c r="E728" s="24"/>
       <c r="F728" s="25"/>
     </row>
-    <row r="729" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="26"/>
       <c r="B729" s="27"/>
       <c r="C729" s="24"/>
@@ -8081,7 +8088,7 @@
       <c r="E729" s="24"/>
       <c r="F729" s="25"/>
     </row>
-    <row r="730" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="26"/>
       <c r="B730" s="27"/>
       <c r="C730" s="24"/>
@@ -8089,7 +8096,7 @@
       <c r="E730" s="24"/>
       <c r="F730" s="25"/>
     </row>
-    <row r="731" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="26"/>
       <c r="B731" s="27"/>
       <c r="C731" s="24"/>
@@ -8097,7 +8104,7 @@
       <c r="E731" s="24"/>
       <c r="F731" s="25"/>
     </row>
-    <row r="732" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="26"/>
       <c r="B732" s="27"/>
       <c r="C732" s="24"/>
@@ -8105,7 +8112,7 @@
       <c r="E732" s="24"/>
       <c r="F732" s="25"/>
     </row>
-    <row r="733" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="26"/>
       <c r="B733" s="27"/>
       <c r="C733" s="24"/>
@@ -8113,7 +8120,7 @@
       <c r="E733" s="24"/>
       <c r="F733" s="25"/>
     </row>
-    <row r="734" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="26"/>
       <c r="B734" s="27"/>
       <c r="C734" s="24"/>
@@ -8121,7 +8128,7 @@
       <c r="E734" s="24"/>
       <c r="F734" s="25"/>
     </row>
-    <row r="735" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="26"/>
       <c r="B735" s="27"/>
       <c r="C735" s="24"/>
@@ -8129,7 +8136,7 @@
       <c r="E735" s="24"/>
       <c r="F735" s="25"/>
     </row>
-    <row r="736" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="26"/>
       <c r="B736" s="27"/>
       <c r="C736" s="24"/>
@@ -8137,7 +8144,7 @@
       <c r="E736" s="24"/>
       <c r="F736" s="25"/>
     </row>
-    <row r="737" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="26"/>
       <c r="B737" s="27"/>
       <c r="C737" s="24"/>
@@ -8145,7 +8152,7 @@
       <c r="E737" s="24"/>
       <c r="F737" s="25"/>
     </row>
-    <row r="738" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="26"/>
       <c r="B738" s="27"/>
       <c r="C738" s="24"/>
@@ -8153,7 +8160,7 @@
       <c r="E738" s="24"/>
       <c r="F738" s="25"/>
     </row>
-    <row r="739" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="26"/>
       <c r="B739" s="27"/>
       <c r="C739" s="24"/>
@@ -8161,7 +8168,7 @@
       <c r="E739" s="24"/>
       <c r="F739" s="25"/>
     </row>
-    <row r="740" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="26"/>
       <c r="B740" s="27"/>
       <c r="C740" s="24"/>
@@ -8169,7 +8176,7 @@
       <c r="E740" s="24"/>
       <c r="F740" s="25"/>
     </row>
-    <row r="741" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="26"/>
       <c r="B741" s="27"/>
       <c r="C741" s="24"/>
@@ -8177,7 +8184,7 @@
       <c r="E741" s="24"/>
       <c r="F741" s="25"/>
     </row>
-    <row r="742" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="26"/>
       <c r="B742" s="27"/>
       <c r="C742" s="24"/>
@@ -8185,7 +8192,7 @@
       <c r="E742" s="24"/>
       <c r="F742" s="25"/>
     </row>
-    <row r="743" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="26"/>
       <c r="B743" s="27"/>
       <c r="C743" s="24"/>
@@ -8193,7 +8200,7 @@
       <c r="E743" s="24"/>
       <c r="F743" s="25"/>
     </row>
-    <row r="744" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="26"/>
       <c r="B744" s="27"/>
       <c r="C744" s="24"/>
@@ -8201,7 +8208,7 @@
       <c r="E744" s="24"/>
       <c r="F744" s="25"/>
     </row>
-    <row r="745" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="26"/>
       <c r="B745" s="27"/>
       <c r="C745" s="24"/>
@@ -8209,7 +8216,7 @@
       <c r="E745" s="24"/>
       <c r="F745" s="25"/>
     </row>
-    <row r="746" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="26"/>
       <c r="B746" s="27"/>
       <c r="C746" s="24"/>
@@ -8217,7 +8224,7 @@
       <c r="E746" s="24"/>
       <c r="F746" s="25"/>
     </row>
-    <row r="747" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="26"/>
       <c r="B747" s="27"/>
       <c r="C747" s="24"/>
@@ -8225,7 +8232,7 @@
       <c r="E747" s="24"/>
       <c r="F747" s="25"/>
     </row>
-    <row r="748" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="26"/>
       <c r="B748" s="27"/>
       <c r="C748" s="24"/>
@@ -8233,7 +8240,7 @@
       <c r="E748" s="24"/>
       <c r="F748" s="25"/>
     </row>
-    <row r="749" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="26"/>
       <c r="B749" s="27"/>
       <c r="C749" s="24"/>
@@ -8241,7 +8248,7 @@
       <c r="E749" s="24"/>
       <c r="F749" s="25"/>
     </row>
-    <row r="750" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="26"/>
       <c r="B750" s="27"/>
       <c r="C750" s="24"/>
@@ -8249,7 +8256,7 @@
       <c r="E750" s="24"/>
       <c r="F750" s="25"/>
     </row>
-    <row r="751" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="26"/>
       <c r="B751" s="27"/>
       <c r="C751" s="24"/>
@@ -8257,7 +8264,7 @@
       <c r="E751" s="24"/>
       <c r="F751" s="25"/>
     </row>
-    <row r="752" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="26"/>
       <c r="B752" s="27"/>
       <c r="C752" s="24"/>
@@ -8265,7 +8272,7 @@
       <c r="E752" s="24"/>
       <c r="F752" s="25"/>
     </row>
-    <row r="753" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="26"/>
       <c r="B753" s="27"/>
       <c r="C753" s="24"/>
@@ -8273,7 +8280,7 @@
       <c r="E753" s="24"/>
       <c r="F753" s="25"/>
     </row>
-    <row r="754" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="26"/>
       <c r="B754" s="27"/>
       <c r="C754" s="24"/>
@@ -8281,7 +8288,7 @@
       <c r="E754" s="24"/>
       <c r="F754" s="25"/>
     </row>
-    <row r="755" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="26"/>
       <c r="B755" s="27"/>
       <c r="C755" s="24"/>
@@ -8289,7 +8296,7 @@
       <c r="E755" s="24"/>
       <c r="F755" s="25"/>
     </row>
-    <row r="756" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="26"/>
       <c r="B756" s="27"/>
       <c r="C756" s="24"/>
@@ -8297,7 +8304,7 @@
       <c r="E756" s="24"/>
       <c r="F756" s="25"/>
     </row>
-    <row r="757" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="26"/>
       <c r="B757" s="27"/>
       <c r="C757" s="24"/>
@@ -8305,7 +8312,7 @@
       <c r="E757" s="24"/>
       <c r="F757" s="25"/>
     </row>
-    <row r="758" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="26"/>
       <c r="B758" s="27"/>
       <c r="C758" s="24"/>
@@ -8313,7 +8320,7 @@
       <c r="E758" s="24"/>
       <c r="F758" s="25"/>
     </row>
-    <row r="759" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="26"/>
       <c r="B759" s="27"/>
       <c r="C759" s="24"/>
@@ -8321,7 +8328,7 @@
       <c r="E759" s="24"/>
       <c r="F759" s="25"/>
     </row>
-    <row r="760" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="26"/>
       <c r="B760" s="27"/>
       <c r="C760" s="24"/>
@@ -8329,7 +8336,7 @@
       <c r="E760" s="24"/>
       <c r="F760" s="25"/>
     </row>
-    <row r="761" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="26"/>
       <c r="B761" s="27"/>
       <c r="C761" s="24"/>
@@ -8337,7 +8344,7 @@
       <c r="E761" s="24"/>
       <c r="F761" s="25"/>
     </row>
-    <row r="762" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="26"/>
       <c r="B762" s="27"/>
       <c r="C762" s="24"/>
@@ -8345,7 +8352,7 @@
       <c r="E762" s="24"/>
       <c r="F762" s="25"/>
     </row>
-    <row r="763" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="26"/>
       <c r="B763" s="27"/>
       <c r="C763" s="24"/>
@@ -8353,7 +8360,7 @@
       <c r="E763" s="24"/>
       <c r="F763" s="25"/>
     </row>
-    <row r="764" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="26"/>
       <c r="B764" s="27"/>
       <c r="C764" s="24"/>
@@ -8361,7 +8368,7 @@
       <c r="E764" s="24"/>
       <c r="F764" s="25"/>
     </row>
-    <row r="765" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="26"/>
       <c r="B765" s="27"/>
       <c r="C765" s="24"/>
@@ -8369,7 +8376,7 @@
       <c r="E765" s="24"/>
       <c r="F765" s="25"/>
     </row>
-    <row r="766" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="26"/>
       <c r="B766" s="27"/>
       <c r="C766" s="24"/>
@@ -8377,7 +8384,7 @@
       <c r="E766" s="24"/>
       <c r="F766" s="25"/>
     </row>
-    <row r="767" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="26"/>
       <c r="B767" s="27"/>
       <c r="C767" s="24"/>
@@ -8385,7 +8392,7 @@
       <c r="E767" s="24"/>
       <c r="F767" s="25"/>
     </row>
-    <row r="768" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="26"/>
       <c r="B768" s="27"/>
       <c r="C768" s="24"/>
@@ -8393,7 +8400,7 @@
       <c r="E768" s="24"/>
       <c r="F768" s="25"/>
     </row>
-    <row r="769" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="26"/>
       <c r="B769" s="27"/>
       <c r="C769" s="24"/>
@@ -8401,7 +8408,7 @@
       <c r="E769" s="24"/>
       <c r="F769" s="25"/>
     </row>
-    <row r="770" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="26"/>
       <c r="B770" s="27"/>
       <c r="C770" s="24"/>
@@ -8409,7 +8416,7 @@
       <c r="E770" s="24"/>
       <c r="F770" s="25"/>
     </row>
-    <row r="771" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="26"/>
       <c r="B771" s="27"/>
       <c r="C771" s="24"/>
@@ -8417,7 +8424,7 @@
       <c r="E771" s="24"/>
       <c r="F771" s="25"/>
     </row>
-    <row r="772" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="26"/>
       <c r="B772" s="27"/>
       <c r="C772" s="24"/>
@@ -8425,7 +8432,7 @@
       <c r="E772" s="24"/>
       <c r="F772" s="25"/>
     </row>
-    <row r="773" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="26"/>
       <c r="B773" s="27"/>
       <c r="C773" s="24"/>
@@ -8433,7 +8440,7 @@
       <c r="E773" s="24"/>
       <c r="F773" s="25"/>
     </row>
-    <row r="774" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="26"/>
       <c r="B774" s="27"/>
       <c r="C774" s="24"/>
@@ -8441,7 +8448,7 @@
       <c r="E774" s="24"/>
       <c r="F774" s="25"/>
     </row>
-    <row r="775" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="26"/>
       <c r="B775" s="27"/>
       <c r="C775" s="24"/>
@@ -8449,7 +8456,7 @@
       <c r="E775" s="24"/>
       <c r="F775" s="25"/>
     </row>
-    <row r="776" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="26"/>
       <c r="B776" s="27"/>
       <c r="C776" s="24"/>
@@ -8457,7 +8464,7 @@
       <c r="E776" s="24"/>
       <c r="F776" s="25"/>
     </row>
-    <row r="777" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="26"/>
       <c r="B777" s="27"/>
       <c r="C777" s="24"/>
@@ -8465,7 +8472,7 @@
       <c r="E777" s="24"/>
       <c r="F777" s="25"/>
     </row>
-    <row r="778" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="26"/>
       <c r="B778" s="27"/>
       <c r="C778" s="24"/>
@@ -8473,7 +8480,7 @@
       <c r="E778" s="24"/>
       <c r="F778" s="25"/>
     </row>
-    <row r="779" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="26"/>
       <c r="B779" s="27"/>
       <c r="C779" s="24"/>
@@ -8481,7 +8488,7 @@
       <c r="E779" s="24"/>
       <c r="F779" s="25"/>
     </row>
-    <row r="780" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="26"/>
       <c r="B780" s="27"/>
       <c r="C780" s="24"/>
@@ -8489,7 +8496,7 @@
       <c r="E780" s="24"/>
       <c r="F780" s="25"/>
     </row>
-    <row r="781" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="26"/>
       <c r="B781" s="27"/>
       <c r="C781" s="24"/>
@@ -8497,7 +8504,7 @@
       <c r="E781" s="24"/>
       <c r="F781" s="25"/>
     </row>
-    <row r="782" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="26"/>
       <c r="B782" s="27"/>
       <c r="C782" s="24"/>
@@ -8505,7 +8512,7 @@
       <c r="E782" s="24"/>
       <c r="F782" s="25"/>
     </row>
-    <row r="783" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="26"/>
       <c r="B783" s="27"/>
       <c r="C783" s="24"/>
@@ -8513,7 +8520,7 @@
       <c r="E783" s="24"/>
       <c r="F783" s="25"/>
     </row>
-    <row r="784" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="26"/>
       <c r="B784" s="27"/>
       <c r="C784" s="24"/>
@@ -8521,7 +8528,7 @@
       <c r="E784" s="24"/>
       <c r="F784" s="25"/>
     </row>
-    <row r="785" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="26"/>
       <c r="B785" s="27"/>
       <c r="C785" s="24"/>
@@ -8529,7 +8536,7 @@
       <c r="E785" s="24"/>
       <c r="F785" s="25"/>
     </row>
-    <row r="786" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="26"/>
       <c r="B786" s="27"/>
       <c r="C786" s="24"/>
@@ -8537,7 +8544,7 @@
       <c r="E786" s="24"/>
       <c r="F786" s="25"/>
     </row>
-    <row r="787" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="26"/>
       <c r="B787" s="27"/>
       <c r="C787" s="24"/>
@@ -8545,7 +8552,7 @@
       <c r="E787" s="24"/>
       <c r="F787" s="25"/>
     </row>
-    <row r="788" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="26"/>
       <c r="B788" s="27"/>
       <c r="C788" s="24"/>
@@ -8553,7 +8560,7 @@
       <c r="E788" s="24"/>
       <c r="F788" s="25"/>
     </row>
-    <row r="789" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="26"/>
       <c r="B789" s="27"/>
       <c r="C789" s="24"/>
@@ -8561,7 +8568,7 @@
       <c r="E789" s="24"/>
       <c r="F789" s="25"/>
     </row>
-    <row r="790" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="26"/>
       <c r="B790" s="27"/>
       <c r="C790" s="24"/>
@@ -8569,7 +8576,7 @@
       <c r="E790" s="24"/>
       <c r="F790" s="25"/>
     </row>
-    <row r="791" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="26"/>
       <c r="B791" s="27"/>
       <c r="C791" s="24"/>
@@ -8577,7 +8584,7 @@
       <c r="E791" s="24"/>
       <c r="F791" s="25"/>
     </row>
-    <row r="792" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="26"/>
       <c r="B792" s="27"/>
       <c r="C792" s="24"/>
@@ -8585,7 +8592,7 @@
       <c r="E792" s="24"/>
       <c r="F792" s="25"/>
     </row>
-    <row r="793" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="26"/>
       <c r="B793" s="27"/>
       <c r="C793" s="24"/>
@@ -8593,7 +8600,7 @@
       <c r="E793" s="24"/>
       <c r="F793" s="25"/>
     </row>
-    <row r="794" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="26"/>
       <c r="B794" s="27"/>
       <c r="C794" s="24"/>
@@ -8601,7 +8608,7 @@
       <c r="E794" s="24"/>
       <c r="F794" s="25"/>
     </row>
-    <row r="795" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="26"/>
       <c r="B795" s="27"/>
       <c r="C795" s="24"/>
@@ -8609,7 +8616,7 @@
       <c r="E795" s="24"/>
       <c r="F795" s="25"/>
     </row>
-    <row r="796" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="26"/>
       <c r="B796" s="27"/>
       <c r="C796" s="24"/>
@@ -8617,7 +8624,7 @@
       <c r="E796" s="24"/>
       <c r="F796" s="25"/>
     </row>
-    <row r="797" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="26"/>
       <c r="B797" s="27"/>
       <c r="C797" s="24"/>
@@ -8625,7 +8632,7 @@
       <c r="E797" s="24"/>
       <c r="F797" s="25"/>
     </row>
-    <row r="798" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="26"/>
       <c r="B798" s="27"/>
       <c r="C798" s="24"/>
@@ -8633,7 +8640,7 @@
       <c r="E798" s="24"/>
       <c r="F798" s="25"/>
     </row>
-    <row r="799" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="26"/>
       <c r="B799" s="27"/>
       <c r="C799" s="24"/>
@@ -8641,7 +8648,7 @@
       <c r="E799" s="24"/>
       <c r="F799" s="25"/>
     </row>
-    <row r="800" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="26"/>
       <c r="B800" s="27"/>
       <c r="C800" s="24"/>
@@ -8649,7 +8656,7 @@
       <c r="E800" s="24"/>
       <c r="F800" s="25"/>
     </row>
-    <row r="801" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="26"/>
       <c r="B801" s="27"/>
       <c r="C801" s="24"/>
@@ -8657,7 +8664,7 @@
       <c r="E801" s="24"/>
       <c r="F801" s="25"/>
     </row>
-    <row r="802" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="26"/>
       <c r="B802" s="27"/>
       <c r="C802" s="24"/>
@@ -8665,7 +8672,7 @@
       <c r="E802" s="24"/>
       <c r="F802" s="25"/>
     </row>
-    <row r="803" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="26"/>
       <c r="B803" s="27"/>
       <c r="C803" s="24"/>
@@ -8673,7 +8680,7 @@
       <c r="E803" s="24"/>
       <c r="F803" s="25"/>
     </row>
-    <row r="804" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="26"/>
       <c r="B804" s="27"/>
       <c r="C804" s="24"/>
@@ -8681,7 +8688,7 @@
       <c r="E804" s="24"/>
       <c r="F804" s="25"/>
     </row>
-    <row r="805" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="26"/>
       <c r="B805" s="27"/>
       <c r="C805" s="24"/>
@@ -8689,7 +8696,7 @@
       <c r="E805" s="24"/>
       <c r="F805" s="25"/>
     </row>
-    <row r="806" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="26"/>
       <c r="B806" s="27"/>
       <c r="C806" s="24"/>
@@ -8697,7 +8704,7 @@
       <c r="E806" s="24"/>
       <c r="F806" s="25"/>
     </row>
-    <row r="807" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="26"/>
       <c r="B807" s="27"/>
       <c r="C807" s="24"/>
@@ -8705,7 +8712,7 @@
       <c r="E807" s="24"/>
       <c r="F807" s="25"/>
     </row>
-    <row r="808" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="26"/>
       <c r="B808" s="27"/>
       <c r="C808" s="24"/>
@@ -8713,7 +8720,7 @@
       <c r="E808" s="24"/>
       <c r="F808" s="25"/>
     </row>
-    <row r="809" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="26"/>
       <c r="B809" s="27"/>
       <c r="C809" s="24"/>
@@ -8721,7 +8728,7 @@
       <c r="E809" s="24"/>
       <c r="F809" s="25"/>
     </row>
-    <row r="810" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="26"/>
       <c r="B810" s="27"/>
       <c r="C810" s="24"/>
@@ -8729,7 +8736,7 @@
       <c r="E810" s="24"/>
       <c r="F810" s="25"/>
     </row>
-    <row r="811" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="26"/>
       <c r="B811" s="27"/>
       <c r="C811" s="24"/>
@@ -8737,7 +8744,7 @@
       <c r="E811" s="24"/>
       <c r="F811" s="25"/>
     </row>
-    <row r="812" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="26"/>
       <c r="B812" s="27"/>
       <c r="C812" s="24"/>
@@ -8745,7 +8752,7 @@
       <c r="E812" s="24"/>
       <c r="F812" s="25"/>
     </row>
-    <row r="813" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="26"/>
       <c r="B813" s="27"/>
       <c r="C813" s="24"/>
@@ -8753,7 +8760,7 @@
       <c r="E813" s="24"/>
       <c r="F813" s="25"/>
     </row>
-    <row r="814" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="26"/>
       <c r="B814" s="27"/>
       <c r="C814" s="24"/>
@@ -8761,7 +8768,7 @@
       <c r="E814" s="24"/>
       <c r="F814" s="25"/>
     </row>
-    <row r="815" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="26"/>
       <c r="B815" s="27"/>
       <c r="C815" s="24"/>
@@ -8769,7 +8776,7 @@
       <c r="E815" s="24"/>
       <c r="F815" s="25"/>
     </row>
-    <row r="816" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="26"/>
       <c r="B816" s="27"/>
       <c r="C816" s="24"/>
@@ -8777,7 +8784,7 @@
       <c r="E816" s="24"/>
       <c r="F816" s="25"/>
     </row>
-    <row r="817" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="26"/>
       <c r="B817" s="27"/>
       <c r="C817" s="24"/>
@@ -8785,7 +8792,7 @@
       <c r="E817" s="24"/>
       <c r="F817" s="25"/>
     </row>
-    <row r="818" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="26"/>
       <c r="B818" s="27"/>
       <c r="C818" s="24"/>
@@ -8793,7 +8800,7 @@
       <c r="E818" s="24"/>
       <c r="F818" s="25"/>
     </row>
-    <row r="819" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="26"/>
       <c r="B819" s="27"/>
       <c r="C819" s="24"/>
@@ -8801,7 +8808,7 @@
       <c r="E819" s="24"/>
       <c r="F819" s="25"/>
     </row>
-    <row r="820" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="26"/>
       <c r="B820" s="27"/>
       <c r="C820" s="24"/>
@@ -8809,7 +8816,7 @@
       <c r="E820" s="24"/>
       <c r="F820" s="25"/>
     </row>
-    <row r="821" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="26"/>
       <c r="B821" s="27"/>
       <c r="C821" s="24"/>
@@ -8817,7 +8824,7 @@
       <c r="E821" s="24"/>
       <c r="F821" s="25"/>
     </row>
-    <row r="822" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="26"/>
       <c r="B822" s="27"/>
       <c r="C822" s="24"/>
@@ -8825,7 +8832,7 @@
       <c r="E822" s="24"/>
       <c r="F822" s="25"/>
     </row>
-    <row r="823" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="26"/>
       <c r="B823" s="27"/>
       <c r="C823" s="24"/>
@@ -8833,7 +8840,7 @@
       <c r="E823" s="24"/>
       <c r="F823" s="25"/>
     </row>
-    <row r="824" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="26"/>
       <c r="B824" s="27"/>
       <c r="C824" s="24"/>
@@ -8841,7 +8848,7 @@
       <c r="E824" s="24"/>
       <c r="F824" s="25"/>
     </row>
-    <row r="825" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="26"/>
       <c r="B825" s="27"/>
       <c r="C825" s="24"/>
@@ -8849,7 +8856,7 @@
       <c r="E825" s="24"/>
       <c r="F825" s="25"/>
     </row>
-    <row r="826" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="26"/>
       <c r="B826" s="27"/>
       <c r="C826" s="24"/>
@@ -8857,7 +8864,7 @@
       <c r="E826" s="24"/>
       <c r="F826" s="25"/>
     </row>
-    <row r="827" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="26"/>
       <c r="B827" s="27"/>
       <c r="C827" s="24"/>
@@ -8865,7 +8872,7 @@
       <c r="E827" s="24"/>
       <c r="F827" s="25"/>
     </row>
-    <row r="828" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="26"/>
       <c r="B828" s="27"/>
       <c r="C828" s="24"/>
@@ -8873,7 +8880,7 @@
       <c r="E828" s="24"/>
       <c r="F828" s="25"/>
     </row>
-    <row r="829" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="26"/>
       <c r="B829" s="27"/>
       <c r="C829" s="24"/>
@@ -8881,7 +8888,7 @@
       <c r="E829" s="24"/>
       <c r="F829" s="25"/>
     </row>
-    <row r="830" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="26"/>
       <c r="B830" s="27"/>
       <c r="C830" s="24"/>
@@ -8889,7 +8896,7 @@
       <c r="E830" s="24"/>
       <c r="F830" s="25"/>
     </row>
-    <row r="831" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="26"/>
       <c r="B831" s="27"/>
       <c r="C831" s="24"/>
@@ -8897,7 +8904,7 @@
       <c r="E831" s="24"/>
       <c r="F831" s="25"/>
     </row>
-    <row r="832" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="26"/>
       <c r="B832" s="27"/>
       <c r="C832" s="24"/>
@@ -8905,7 +8912,7 @@
       <c r="E832" s="24"/>
       <c r="F832" s="25"/>
     </row>
-    <row r="833" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="26"/>
       <c r="B833" s="27"/>
       <c r="C833" s="24"/>
@@ -8913,7 +8920,7 @@
       <c r="E833" s="24"/>
       <c r="F833" s="25"/>
     </row>
-    <row r="834" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="26"/>
       <c r="B834" s="27"/>
       <c r="C834" s="24"/>
@@ -8921,7 +8928,7 @@
       <c r="E834" s="24"/>
       <c r="F834" s="25"/>
     </row>
-    <row r="835" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="26"/>
       <c r="B835" s="27"/>
       <c r="C835" s="24"/>
@@ -8929,7 +8936,7 @@
       <c r="E835" s="24"/>
       <c r="F835" s="25"/>
     </row>
-    <row r="836" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="26"/>
       <c r="B836" s="27"/>
       <c r="C836" s="24"/>
@@ -8937,7 +8944,7 @@
       <c r="E836" s="24"/>
       <c r="F836" s="25"/>
     </row>
-    <row r="837" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="26"/>
       <c r="B837" s="27"/>
       <c r="C837" s="24"/>
@@ -8945,7 +8952,7 @@
       <c r="E837" s="24"/>
       <c r="F837" s="25"/>
     </row>
-    <row r="838" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="26"/>
       <c r="B838" s="27"/>
       <c r="C838" s="24"/>
@@ -8953,7 +8960,7 @@
       <c r="E838" s="24"/>
       <c r="F838" s="25"/>
     </row>
-    <row r="839" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="26"/>
       <c r="B839" s="27"/>
       <c r="C839" s="24"/>
@@ -8961,7 +8968,7 @@
       <c r="E839" s="24"/>
       <c r="F839" s="25"/>
     </row>
-    <row r="840" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="26"/>
       <c r="B840" s="27"/>
       <c r="C840" s="24"/>
@@ -8969,7 +8976,7 @@
       <c r="E840" s="24"/>
       <c r="F840" s="25"/>
     </row>
-    <row r="841" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="26"/>
       <c r="B841" s="27"/>
       <c r="C841" s="24"/>
@@ -8977,7 +8984,7 @@
       <c r="E841" s="24"/>
       <c r="F841" s="25"/>
     </row>
-    <row r="842" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="26"/>
       <c r="B842" s="27"/>
       <c r="C842" s="24"/>
@@ -8985,7 +8992,7 @@
       <c r="E842" s="24"/>
       <c r="F842" s="25"/>
     </row>
-    <row r="843" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="26"/>
       <c r="B843" s="27"/>
       <c r="C843" s="24"/>
@@ -8993,7 +9000,7 @@
       <c r="E843" s="24"/>
       <c r="F843" s="25"/>
     </row>
-    <row r="844" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="26"/>
       <c r="B844" s="27"/>
       <c r="C844" s="24"/>
@@ -9001,7 +9008,7 @@
       <c r="E844" s="24"/>
       <c r="F844" s="25"/>
     </row>
-    <row r="845" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="26"/>
       <c r="B845" s="27"/>
       <c r="C845" s="24"/>
@@ -9009,7 +9016,7 @@
       <c r="E845" s="24"/>
       <c r="F845" s="25"/>
     </row>
-    <row r="846" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="26"/>
       <c r="B846" s="27"/>
       <c r="C846" s="24"/>
@@ -9017,7 +9024,7 @@
       <c r="E846" s="24"/>
       <c r="F846" s="25"/>
     </row>
-    <row r="847" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="26"/>
       <c r="B847" s="27"/>
       <c r="C847" s="24"/>
@@ -9025,7 +9032,7 @@
       <c r="E847" s="24"/>
       <c r="F847" s="25"/>
     </row>
-    <row r="848" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="26"/>
       <c r="B848" s="27"/>
       <c r="C848" s="24"/>
@@ -9033,7 +9040,7 @@
       <c r="E848" s="24"/>
       <c r="F848" s="25"/>
     </row>
-    <row r="849" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="26"/>
       <c r="B849" s="27"/>
       <c r="C849" s="24"/>
@@ -9041,7 +9048,7 @@
       <c r="E849" s="24"/>
       <c r="F849" s="25"/>
     </row>
-    <row r="850" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="26"/>
       <c r="B850" s="27"/>
       <c r="C850" s="24"/>
@@ -9049,7 +9056,7 @@
       <c r="E850" s="24"/>
       <c r="F850" s="25"/>
     </row>
-    <row r="851" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="26"/>
       <c r="B851" s="27"/>
       <c r="C851" s="24"/>
@@ -9057,7 +9064,7 @@
       <c r="E851" s="24"/>
       <c r="F851" s="25"/>
     </row>
-    <row r="852" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="26"/>
       <c r="B852" s="27"/>
       <c r="C852" s="24"/>
@@ -9065,7 +9072,7 @@
       <c r="E852" s="24"/>
       <c r="F852" s="25"/>
     </row>
-    <row r="853" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="26"/>
       <c r="B853" s="27"/>
       <c r="C853" s="24"/>
@@ -9073,7 +9080,7 @@
       <c r="E853" s="24"/>
       <c r="F853" s="25"/>
     </row>
-    <row r="854" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="26"/>
       <c r="B854" s="27"/>
       <c r="C854" s="24"/>
@@ -9081,7 +9088,7 @@
       <c r="E854" s="24"/>
       <c r="F854" s="25"/>
     </row>
-    <row r="855" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="26"/>
       <c r="B855" s="27"/>
       <c r="C855" s="24"/>
@@ -9089,7 +9096,7 @@
       <c r="E855" s="24"/>
       <c r="F855" s="25"/>
     </row>
-    <row r="856" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="26"/>
       <c r="B856" s="27"/>
       <c r="C856" s="24"/>
@@ -9097,7 +9104,7 @@
       <c r="E856" s="24"/>
       <c r="F856" s="25"/>
     </row>
-    <row r="857" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="26"/>
       <c r="B857" s="27"/>
       <c r="C857" s="24"/>
@@ -9105,7 +9112,7 @@
       <c r="E857" s="24"/>
       <c r="F857" s="25"/>
     </row>
-    <row r="858" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="26"/>
       <c r="B858" s="27"/>
       <c r="C858" s="24"/>
@@ -9113,7 +9120,7 @@
       <c r="E858" s="24"/>
       <c r="F858" s="25"/>
     </row>
-    <row r="859" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="26"/>
       <c r="B859" s="27"/>
       <c r="C859" s="24"/>
@@ -9121,7 +9128,7 @@
       <c r="E859" s="24"/>
       <c r="F859" s="25"/>
     </row>
-    <row r="860" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="26"/>
       <c r="B860" s="27"/>
       <c r="C860" s="24"/>
@@ -9129,7 +9136,7 @@
       <c r="E860" s="24"/>
       <c r="F860" s="25"/>
     </row>
-    <row r="861" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="26"/>
       <c r="B861" s="27"/>
       <c r="C861" s="24"/>
@@ -9137,7 +9144,7 @@
       <c r="E861" s="24"/>
       <c r="F861" s="25"/>
     </row>
-    <row r="862" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="26"/>
       <c r="B862" s="27"/>
       <c r="C862" s="24"/>
@@ -9145,7 +9152,7 @@
       <c r="E862" s="24"/>
       <c r="F862" s="25"/>
     </row>
-    <row r="863" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="26"/>
       <c r="B863" s="27"/>
       <c r="C863" s="24"/>
@@ -9153,7 +9160,7 @@
       <c r="E863" s="24"/>
       <c r="F863" s="25"/>
     </row>
-    <row r="864" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="26"/>
       <c r="B864" s="27"/>
       <c r="C864" s="24"/>
@@ -9161,7 +9168,7 @@
       <c r="E864" s="24"/>
       <c r="F864" s="25"/>
     </row>
-    <row r="865" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="26"/>
       <c r="B865" s="27"/>
       <c r="C865" s="24"/>
@@ -9169,7 +9176,7 @@
       <c r="E865" s="24"/>
       <c r="F865" s="25"/>
     </row>
-    <row r="866" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="26"/>
       <c r="B866" s="27"/>
       <c r="C866" s="24"/>
@@ -9177,7 +9184,7 @@
       <c r="E866" s="24"/>
       <c r="F866" s="25"/>
     </row>
-    <row r="867" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="26"/>
       <c r="B867" s="27"/>
       <c r="C867" s="24"/>
@@ -9185,7 +9192,7 @@
       <c r="E867" s="24"/>
       <c r="F867" s="25"/>
     </row>
-    <row r="868" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="26"/>
       <c r="B868" s="27"/>
       <c r="C868" s="24"/>
@@ -9193,7 +9200,7 @@
       <c r="E868" s="24"/>
       <c r="F868" s="25"/>
     </row>
-    <row r="869" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="26"/>
       <c r="B869" s="27"/>
       <c r="C869" s="24"/>
@@ -9201,7 +9208,7 @@
       <c r="E869" s="24"/>
       <c r="F869" s="25"/>
     </row>
-    <row r="870" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="26"/>
       <c r="B870" s="27"/>
       <c r="C870" s="24"/>
@@ -9209,7 +9216,7 @@
       <c r="E870" s="24"/>
       <c r="F870" s="25"/>
     </row>
-    <row r="871" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="26"/>
       <c r="B871" s="27"/>
       <c r="C871" s="24"/>
@@ -9217,7 +9224,7 @@
       <c r="E871" s="24"/>
       <c r="F871" s="25"/>
     </row>
-    <row r="872" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="26"/>
       <c r="B872" s="27"/>
       <c r="C872" s="24"/>
@@ -9225,7 +9232,7 @@
       <c r="E872" s="24"/>
       <c r="F872" s="25"/>
     </row>
-    <row r="873" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="26"/>
       <c r="B873" s="27"/>
       <c r="C873" s="24"/>
@@ -9233,7 +9240,7 @@
       <c r="E873" s="24"/>
       <c r="F873" s="25"/>
     </row>
-    <row r="874" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="26"/>
       <c r="B874" s="27"/>
       <c r="C874" s="24"/>
@@ -9241,7 +9248,7 @@
       <c r="E874" s="24"/>
       <c r="F874" s="25"/>
     </row>
-    <row r="875" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="26"/>
       <c r="B875" s="27"/>
       <c r="C875" s="24"/>
@@ -9249,7 +9256,7 @@
       <c r="E875" s="24"/>
       <c r="F875" s="25"/>
     </row>
-    <row r="876" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="26"/>
       <c r="B876" s="27"/>
       <c r="C876" s="24"/>
@@ -9257,7 +9264,7 @@
       <c r="E876" s="24"/>
       <c r="F876" s="25"/>
     </row>
-    <row r="877" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="26"/>
       <c r="B877" s="27"/>
       <c r="C877" s="24"/>
@@ -9265,7 +9272,7 @@
       <c r="E877" s="24"/>
       <c r="F877" s="25"/>
     </row>
-    <row r="878" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="26"/>
       <c r="B878" s="27"/>
       <c r="C878" s="24"/>
@@ -9273,7 +9280,7 @@
       <c r="E878" s="24"/>
       <c r="F878" s="25"/>
     </row>
-    <row r="879" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="26"/>
       <c r="B879" s="27"/>
       <c r="C879" s="24"/>
@@ -9281,7 +9288,7 @@
       <c r="E879" s="24"/>
       <c r="F879" s="25"/>
     </row>
-    <row r="880" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="26"/>
       <c r="B880" s="27"/>
       <c r="C880" s="24"/>
@@ -9289,7 +9296,7 @@
       <c r="E880" s="24"/>
       <c r="F880" s="25"/>
     </row>
-    <row r="881" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="26"/>
       <c r="B881" s="27"/>
       <c r="C881" s="24"/>
@@ -9297,7 +9304,7 @@
       <c r="E881" s="24"/>
       <c r="F881" s="25"/>
     </row>
-    <row r="882" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="26"/>
       <c r="B882" s="27"/>
       <c r="C882" s="24"/>
@@ -9305,7 +9312,7 @@
       <c r="E882" s="24"/>
       <c r="F882" s="25"/>
     </row>
-    <row r="883" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="26"/>
       <c r="B883" s="27"/>
       <c r="C883" s="24"/>
@@ -9313,7 +9320,7 @@
       <c r="E883" s="24"/>
       <c r="F883" s="25"/>
     </row>
-    <row r="884" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="26"/>
       <c r="B884" s="27"/>
       <c r="C884" s="24"/>
@@ -9321,7 +9328,7 @@
       <c r="E884" s="24"/>
       <c r="F884" s="25"/>
     </row>
-    <row r="885" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="26"/>
       <c r="B885" s="27"/>
       <c r="C885" s="24"/>
@@ -9329,7 +9336,7 @@
       <c r="E885" s="24"/>
       <c r="F885" s="25"/>
     </row>
-    <row r="886" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="26"/>
       <c r="B886" s="27"/>
       <c r="C886" s="24"/>
@@ -9337,7 +9344,7 @@
       <c r="E886" s="24"/>
       <c r="F886" s="25"/>
     </row>
-    <row r="887" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="26"/>
       <c r="B887" s="27"/>
       <c r="C887" s="24"/>
@@ -9345,7 +9352,7 @@
       <c r="E887" s="24"/>
       <c r="F887" s="25"/>
     </row>
-    <row r="888" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="26"/>
       <c r="B888" s="27"/>
       <c r="C888" s="24"/>
@@ -9353,7 +9360,7 @@
       <c r="E888" s="24"/>
       <c r="F888" s="25"/>
     </row>
-    <row r="889" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="26"/>
       <c r="B889" s="27"/>
       <c r="C889" s="24"/>
@@ -9361,7 +9368,7 @@
       <c r="E889" s="24"/>
       <c r="F889" s="25"/>
     </row>
-    <row r="890" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="26"/>
       <c r="B890" s="27"/>
       <c r="C890" s="24"/>
@@ -9369,7 +9376,7 @@
       <c r="E890" s="24"/>
       <c r="F890" s="25"/>
     </row>
-    <row r="891" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="26"/>
       <c r="B891" s="27"/>
       <c r="C891" s="24"/>
@@ -9377,7 +9384,7 @@
       <c r="E891" s="24"/>
       <c r="F891" s="25"/>
     </row>
-    <row r="892" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="26"/>
       <c r="B892" s="27"/>
       <c r="C892" s="24"/>
@@ -9385,7 +9392,7 @@
       <c r="E892" s="24"/>
       <c r="F892" s="25"/>
     </row>
-    <row r="893" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="26"/>
       <c r="B893" s="27"/>
       <c r="C893" s="24"/>
@@ -9393,7 +9400,7 @@
       <c r="E893" s="24"/>
       <c r="F893" s="25"/>
     </row>
-    <row r="894" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="26"/>
       <c r="B894" s="27"/>
       <c r="C894" s="24"/>
@@ -9401,7 +9408,7 @@
       <c r="E894" s="24"/>
       <c r="F894" s="25"/>
     </row>
-    <row r="895" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="26"/>
       <c r="B895" s="27"/>
       <c r="C895" s="24"/>
@@ -9409,7 +9416,7 @@
       <c r="E895" s="24"/>
       <c r="F895" s="25"/>
     </row>
-    <row r="896" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="26"/>
       <c r="B896" s="27"/>
       <c r="C896" s="24"/>
@@ -9417,7 +9424,7 @@
       <c r="E896" s="24"/>
       <c r="F896" s="25"/>
     </row>
-    <row r="897" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="26"/>
       <c r="B897" s="27"/>
       <c r="C897" s="24"/>
@@ -9425,7 +9432,7 @@
       <c r="E897" s="24"/>
       <c r="F897" s="25"/>
     </row>
-    <row r="898" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="26"/>
       <c r="B898" s="27"/>
       <c r="C898" s="24"/>
@@ -9433,7 +9440,7 @@
       <c r="E898" s="24"/>
       <c r="F898" s="25"/>
     </row>
-    <row r="899" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="26"/>
       <c r="B899" s="27"/>
       <c r="C899" s="24"/>
@@ -9441,7 +9448,7 @@
       <c r="E899" s="24"/>
       <c r="F899" s="25"/>
     </row>
-    <row r="900" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="26"/>
       <c r="B900" s="27"/>
       <c r="C900" s="24"/>
@@ -9449,7 +9456,7 @@
       <c r="E900" s="24"/>
       <c r="F900" s="25"/>
     </row>
-    <row r="901" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="26"/>
       <c r="B901" s="27"/>
       <c r="C901" s="24"/>
@@ -9457,7 +9464,7 @@
       <c r="E901" s="24"/>
       <c r="F901" s="25"/>
     </row>
-    <row r="902" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="26"/>
       <c r="B902" s="27"/>
       <c r="C902" s="24"/>
@@ -9465,7 +9472,7 @@
       <c r="E902" s="24"/>
       <c r="F902" s="25"/>
     </row>
-    <row r="903" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="26"/>
       <c r="B903" s="27"/>
       <c r="C903" s="24"/>
@@ -9473,7 +9480,7 @@
       <c r="E903" s="24"/>
       <c r="F903" s="25"/>
     </row>
-    <row r="904" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="26"/>
       <c r="B904" s="27"/>
       <c r="C904" s="24"/>
@@ -9481,7 +9488,7 @@
       <c r="E904" s="24"/>
       <c r="F904" s="25"/>
     </row>
-    <row r="905" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="26"/>
       <c r="B905" s="27"/>
       <c r="C905" s="24"/>
@@ -9489,7 +9496,7 @@
       <c r="E905" s="24"/>
       <c r="F905" s="25"/>
     </row>
-    <row r="906" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="26"/>
       <c r="B906" s="27"/>
       <c r="C906" s="24"/>
@@ -9497,7 +9504,7 @@
       <c r="E906" s="24"/>
       <c r="F906" s="25"/>
     </row>
-    <row r="907" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="26"/>
       <c r="B907" s="27"/>
       <c r="C907" s="24"/>
@@ -9505,7 +9512,7 @@
       <c r="E907" s="24"/>
       <c r="F907" s="25"/>
     </row>
-    <row r="908" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="26"/>
       <c r="B908" s="27"/>
       <c r="C908" s="24"/>
@@ -9513,7 +9520,7 @@
       <c r="E908" s="24"/>
       <c r="F908" s="25"/>
     </row>
-    <row r="909" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="26"/>
       <c r="B909" s="27"/>
       <c r="C909" s="24"/>
@@ -9521,7 +9528,7 @@
       <c r="E909" s="24"/>
       <c r="F909" s="25"/>
     </row>
-    <row r="910" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="26"/>
       <c r="B910" s="27"/>
       <c r="C910" s="24"/>
@@ -9529,7 +9536,7 @@
       <c r="E910" s="24"/>
       <c r="F910" s="25"/>
     </row>
-    <row r="911" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="26"/>
       <c r="B911" s="27"/>
       <c r="C911" s="24"/>
@@ -9537,7 +9544,7 @@
       <c r="E911" s="24"/>
       <c r="F911" s="25"/>
     </row>
-    <row r="912" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="26"/>
       <c r="B912" s="27"/>
       <c r="C912" s="24"/>
@@ -9545,7 +9552,7 @@
       <c r="E912" s="24"/>
       <c r="F912" s="25"/>
     </row>
-    <row r="913" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="26"/>
       <c r="B913" s="27"/>
       <c r="C913" s="24"/>
@@ -9553,7 +9560,7 @@
       <c r="E913" s="24"/>
       <c r="F913" s="25"/>
     </row>
-    <row r="914" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="26"/>
       <c r="B914" s="27"/>
       <c r="C914" s="24"/>
@@ -9561,7 +9568,7 @@
       <c r="E914" s="24"/>
       <c r="F914" s="25"/>
     </row>
-    <row r="915" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="26"/>
       <c r="B915" s="27"/>
       <c r="C915" s="24"/>
@@ -9569,7 +9576,7 @@
       <c r="E915" s="24"/>
       <c r="F915" s="25"/>
     </row>
-    <row r="916" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="26"/>
       <c r="B916" s="27"/>
       <c r="C916" s="24"/>
@@ -9577,7 +9584,7 @@
       <c r="E916" s="24"/>
       <c r="F916" s="25"/>
     </row>
-    <row r="917" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="26"/>
       <c r="B917" s="27"/>
       <c r="C917" s="24"/>
@@ -9585,7 +9592,7 @@
       <c r="E917" s="24"/>
       <c r="F917" s="25"/>
     </row>
-    <row r="918" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="26"/>
       <c r="B918" s="27"/>
       <c r="C918" s="24"/>
@@ -9593,7 +9600,7 @@
       <c r="E918" s="24"/>
       <c r="F918" s="25"/>
     </row>
-    <row r="919" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="26"/>
       <c r="B919" s="27"/>
       <c r="C919" s="24"/>
@@ -9601,7 +9608,7 @@
       <c r="E919" s="24"/>
       <c r="F919" s="25"/>
     </row>
-    <row r="920" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="26"/>
       <c r="B920" s="27"/>
       <c r="C920" s="24"/>
@@ -9609,7 +9616,7 @@
       <c r="E920" s="24"/>
       <c r="F920" s="25"/>
     </row>
-    <row r="921" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="26"/>
       <c r="B921" s="27"/>
       <c r="C921" s="24"/>
@@ -9617,7 +9624,7 @@
       <c r="E921" s="24"/>
       <c r="F921" s="25"/>
     </row>
-    <row r="922" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="26"/>
       <c r="B922" s="27"/>
       <c r="C922" s="24"/>
@@ -9625,7 +9632,7 @@
       <c r="E922" s="24"/>
       <c r="F922" s="25"/>
     </row>
-    <row r="923" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="26"/>
       <c r="B923" s="27"/>
       <c r="C923" s="24"/>
@@ -9633,7 +9640,7 @@
       <c r="E923" s="24"/>
       <c r="F923" s="25"/>
     </row>
-    <row r="924" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="26"/>
       <c r="B924" s="27"/>
       <c r="C924" s="24"/>
@@ -9641,7 +9648,7 @@
       <c r="E924" s="24"/>
       <c r="F924" s="25"/>
     </row>
-    <row r="925" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="26"/>
       <c r="B925" s="27"/>
       <c r="C925" s="24"/>
@@ -9649,7 +9656,7 @@
       <c r="E925" s="24"/>
       <c r="F925" s="25"/>
     </row>
-    <row r="926" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="26"/>
       <c r="B926" s="27"/>
       <c r="C926" s="24"/>
@@ -9657,7 +9664,7 @@
       <c r="E926" s="24"/>
       <c r="F926" s="25"/>
     </row>
-    <row r="927" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="26"/>
       <c r="B927" s="27"/>
       <c r="C927" s="24"/>
@@ -9665,7 +9672,7 @@
       <c r="E927" s="24"/>
       <c r="F927" s="25"/>
     </row>
-    <row r="928" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="26"/>
       <c r="B928" s="27"/>
       <c r="C928" s="24"/>
@@ -9673,7 +9680,7 @@
       <c r="E928" s="24"/>
       <c r="F928" s="25"/>
     </row>
-    <row r="929" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="26"/>
       <c r="B929" s="27"/>
       <c r="C929" s="24"/>
@@ -9681,7 +9688,7 @@
       <c r="E929" s="24"/>
       <c r="F929" s="25"/>
     </row>
-    <row r="930" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="26"/>
       <c r="B930" s="27"/>
       <c r="C930" s="24"/>
@@ -9689,7 +9696,7 @@
       <c r="E930" s="24"/>
       <c r="F930" s="25"/>
     </row>
-    <row r="931" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="26"/>
       <c r="B931" s="27"/>
       <c r="C931" s="24"/>
@@ -9697,7 +9704,7 @@
       <c r="E931" s="24"/>
       <c r="F931" s="25"/>
     </row>
-    <row r="932" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="26"/>
       <c r="B932" s="27"/>
       <c r="C932" s="24"/>
@@ -9705,7 +9712,7 @@
       <c r="E932" s="24"/>
       <c r="F932" s="25"/>
     </row>
-    <row r="933" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="26"/>
       <c r="B933" s="27"/>
       <c r="C933" s="24"/>
@@ -9713,7 +9720,7 @@
       <c r="E933" s="24"/>
       <c r="F933" s="25"/>
     </row>
-    <row r="934" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="26"/>
       <c r="B934" s="27"/>
       <c r="C934" s="24"/>
@@ -9721,7 +9728,7 @@
       <c r="E934" s="24"/>
       <c r="F934" s="25"/>
     </row>
-    <row r="935" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="26"/>
       <c r="B935" s="27"/>
       <c r="C935" s="24"/>
@@ -9729,7 +9736,7 @@
       <c r="E935" s="24"/>
       <c r="F935" s="25"/>
     </row>
-    <row r="936" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="26"/>
       <c r="B936" s="27"/>
       <c r="C936" s="24"/>
@@ -9737,7 +9744,7 @@
       <c r="E936" s="24"/>
       <c r="F936" s="25"/>
     </row>
-    <row r="937" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="26"/>
       <c r="B937" s="27"/>
       <c r="C937" s="24"/>
@@ -9745,7 +9752,7 @@
       <c r="E937" s="24"/>
       <c r="F937" s="25"/>
     </row>
-    <row r="938" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="26"/>
       <c r="B938" s="27"/>
       <c r="C938" s="24"/>
@@ -9753,7 +9760,7 @@
       <c r="E938" s="24"/>
       <c r="F938" s="25"/>
     </row>
-    <row r="939" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="26"/>
       <c r="B939" s="27"/>
       <c r="C939" s="24"/>
@@ -9761,7 +9768,7 @@
       <c r="E939" s="24"/>
       <c r="F939" s="25"/>
     </row>
-    <row r="940" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="26"/>
       <c r="B940" s="27"/>
       <c r="C940" s="24"/>
@@ -9769,7 +9776,7 @@
       <c r="E940" s="24"/>
       <c r="F940" s="25"/>
     </row>
-    <row r="941" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="26"/>
       <c r="B941" s="27"/>
       <c r="C941" s="24"/>
@@ -9777,7 +9784,7 @@
       <c r="E941" s="24"/>
       <c r="F941" s="25"/>
     </row>
-    <row r="942" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="26"/>
       <c r="B942" s="27"/>
       <c r="C942" s="24"/>
@@ -9785,7 +9792,7 @@
       <c r="E942" s="24"/>
       <c r="F942" s="25"/>
     </row>
-    <row r="943" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="26"/>
       <c r="B943" s="27"/>
       <c r="C943" s="24"/>
@@ -9793,7 +9800,7 @@
       <c r="E943" s="24"/>
       <c r="F943" s="25"/>
     </row>
-    <row r="944" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="26"/>
       <c r="B944" s="27"/>
       <c r="C944" s="24"/>
@@ -9801,7 +9808,7 @@
       <c r="E944" s="24"/>
       <c r="F944" s="25"/>
     </row>
-    <row r="945" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="26"/>
       <c r="B945" s="27"/>
       <c r="C945" s="24"/>
@@ -9809,7 +9816,7 @@
       <c r="E945" s="24"/>
       <c r="F945" s="25"/>
     </row>
-    <row r="946" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="26"/>
       <c r="B946" s="27"/>
       <c r="C946" s="24"/>
@@ -9817,7 +9824,7 @@
       <c r="E946" s="24"/>
       <c r="F946" s="25"/>
     </row>
-    <row r="947" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="26"/>
       <c r="B947" s="27"/>
       <c r="C947" s="24"/>
@@ -9825,7 +9832,7 @@
       <c r="E947" s="24"/>
       <c r="F947" s="25"/>
     </row>
-    <row r="948" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="26"/>
       <c r="B948" s="27"/>
       <c r="C948" s="24"/>
@@ -9833,7 +9840,7 @@
       <c r="E948" s="24"/>
       <c r="F948" s="25"/>
     </row>
-    <row r="949" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="26"/>
       <c r="B949" s="27"/>
       <c r="C949" s="24"/>
@@ -9841,7 +9848,7 @@
       <c r="E949" s="24"/>
       <c r="F949" s="25"/>
     </row>
-    <row r="950" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="26"/>
       <c r="B950" s="27"/>
       <c r="C950" s="24"/>
@@ -9849,7 +9856,7 @@
       <c r="E950" s="24"/>
       <c r="F950" s="25"/>
     </row>
-    <row r="951" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="26"/>
       <c r="B951" s="27"/>
       <c r="C951" s="24"/>
@@ -9857,7 +9864,7 @@
       <c r="E951" s="24"/>
       <c r="F951" s="25"/>
     </row>
-    <row r="952" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="26"/>
       <c r="B952" s="27"/>
       <c r="C952" s="24"/>
@@ -9865,7 +9872,7 @@
       <c r="E952" s="24"/>
       <c r="F952" s="25"/>
     </row>
-    <row r="953" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="26"/>
       <c r="B953" s="27"/>
       <c r="C953" s="24"/>
@@ -9873,7 +9880,7 @@
       <c r="E953" s="24"/>
       <c r="F953" s="25"/>
     </row>
-    <row r="954" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="26"/>
       <c r="B954" s="27"/>
       <c r="C954" s="24"/>
@@ -9881,7 +9888,7 @@
       <c r="E954" s="24"/>
       <c r="F954" s="25"/>
     </row>
-    <row r="955" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="26"/>
       <c r="B955" s="27"/>
       <c r="C955" s="24"/>
@@ -9889,7 +9896,7 @@
       <c r="E955" s="24"/>
       <c r="F955" s="25"/>
     </row>
-    <row r="956" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="26"/>
       <c r="B956" s="27"/>
       <c r="C956" s="24"/>
@@ -9897,7 +9904,7 @@
       <c r="E956" s="24"/>
       <c r="F956" s="25"/>
     </row>
-    <row r="957" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="26"/>
       <c r="B957" s="27"/>
       <c r="C957" s="24"/>
@@ -9905,7 +9912,7 @@
       <c r="E957" s="24"/>
       <c r="F957" s="25"/>
     </row>
-    <row r="958" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="26"/>
       <c r="B958" s="27"/>
       <c r="C958" s="24"/>
@@ -9913,7 +9920,7 @@
       <c r="E958" s="24"/>
       <c r="F958" s="25"/>
     </row>
-    <row r="959" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="26"/>
       <c r="B959" s="27"/>
       <c r="C959" s="24"/>
@@ -9921,7 +9928,7 @@
       <c r="E959" s="24"/>
       <c r="F959" s="25"/>
     </row>
-    <row r="960" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="26"/>
       <c r="B960" s="27"/>
       <c r="C960" s="24"/>
@@ -9929,7 +9936,7 @@
       <c r="E960" s="24"/>
       <c r="F960" s="25"/>
     </row>
-    <row r="961" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="26"/>
       <c r="B961" s="27"/>
       <c r="C961" s="24"/>
@@ -9937,7 +9944,7 @@
       <c r="E961" s="24"/>
       <c r="F961" s="25"/>
     </row>
-    <row r="962" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="26"/>
       <c r="B962" s="27"/>
       <c r="C962" s="24"/>
@@ -9945,7 +9952,7 @@
       <c r="E962" s="24"/>
       <c r="F962" s="25"/>
     </row>
-    <row r="963" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="26"/>
       <c r="B963" s="27"/>
       <c r="C963" s="24"/>
@@ -9953,7 +9960,7 @@
       <c r="E963" s="24"/>
       <c r="F963" s="25"/>
     </row>
-    <row r="964" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="26"/>
       <c r="B964" s="27"/>
       <c r="C964" s="24"/>
@@ -9961,7 +9968,7 @@
       <c r="E964" s="24"/>
       <c r="F964" s="25"/>
     </row>
-    <row r="965" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="26"/>
       <c r="B965" s="27"/>
       <c r="C965" s="24"/>
@@ -9969,7 +9976,7 @@
       <c r="E965" s="24"/>
       <c r="F965" s="25"/>
     </row>
-    <row r="966" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="26"/>
       <c r="B966" s="27"/>
       <c r="C966" s="24"/>
@@ -9977,7 +9984,7 @@
       <c r="E966" s="24"/>
       <c r="F966" s="25"/>
     </row>
-    <row r="967" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="26"/>
       <c r="B967" s="27"/>
       <c r="C967" s="24"/>
@@ -9985,7 +9992,7 @@
       <c r="E967" s="24"/>
       <c r="F967" s="25"/>
     </row>
-    <row r="968" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="26"/>
       <c r="B968" s="27"/>
       <c r="C968" s="24"/>
@@ -9993,7 +10000,7 @@
       <c r="E968" s="24"/>
       <c r="F968" s="25"/>
     </row>
-    <row r="969" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="26"/>
       <c r="B969" s="27"/>
       <c r="C969" s="24"/>
@@ -10001,7 +10008,7 @@
       <c r="E969" s="24"/>
       <c r="F969" s="25"/>
     </row>
-    <row r="970" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="26"/>
       <c r="B970" s="27"/>
       <c r="C970" s="24"/>
@@ -10009,7 +10016,7 @@
       <c r="E970" s="24"/>
       <c r="F970" s="25"/>
     </row>
-    <row r="971" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="26"/>
       <c r="B971" s="27"/>
       <c r="C971" s="24"/>
@@ -10017,7 +10024,7 @@
       <c r="E971" s="24"/>
       <c r="F971" s="25"/>
     </row>
-    <row r="972" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="26"/>
       <c r="B972" s="27"/>
       <c r="C972" s="24"/>
@@ -10025,7 +10032,7 @@
       <c r="E972" s="24"/>
       <c r="F972" s="25"/>
     </row>
-    <row r="973" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="26"/>
       <c r="B973" s="27"/>
       <c r="C973" s="24"/>
@@ -10033,7 +10040,7 @@
       <c r="E973" s="24"/>
       <c r="F973" s="25"/>
     </row>
-    <row r="974" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="26"/>
       <c r="B974" s="27"/>
       <c r="C974" s="24"/>
@@ -10041,7 +10048,7 @@
       <c r="E974" s="24"/>
       <c r="F974" s="25"/>
     </row>
-    <row r="975" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="26"/>
       <c r="B975" s="27"/>
       <c r="C975" s="24"/>
@@ -10049,7 +10056,7 @@
       <c r="E975" s="24"/>
       <c r="F975" s="25"/>
     </row>
-    <row r="976" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="26"/>
       <c r="B976" s="27"/>
       <c r="C976" s="24"/>
@@ -10057,7 +10064,7 @@
       <c r="E976" s="24"/>
       <c r="F976" s="25"/>
     </row>
-    <row r="977" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="26"/>
       <c r="B977" s="27"/>
       <c r="C977" s="24"/>
@@ -10065,7 +10072,7 @@
       <c r="E977" s="24"/>
       <c r="F977" s="25"/>
     </row>
-    <row r="978" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="26"/>
       <c r="B978" s="27"/>
       <c r="C978" s="24"/>
@@ -10073,7 +10080,7 @@
       <c r="E978" s="24"/>
       <c r="F978" s="25"/>
     </row>
-    <row r="979" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="26"/>
       <c r="B979" s="27"/>
       <c r="C979" s="24"/>
@@ -10081,7 +10088,7 @@
       <c r="E979" s="24"/>
       <c r="F979" s="25"/>
     </row>
-    <row r="980" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="26"/>
       <c r="B980" s="27"/>
       <c r="C980" s="24"/>
@@ -10089,7 +10096,7 @@
       <c r="E980" s="24"/>
       <c r="F980" s="25"/>
     </row>
-    <row r="981" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="26"/>
       <c r="B981" s="27"/>
       <c r="C981" s="24"/>
@@ -10097,7 +10104,7 @@
       <c r="E981" s="24"/>
       <c r="F981" s="25"/>
     </row>
-    <row r="982" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="26"/>
       <c r="B982" s="27"/>
       <c r="C982" s="24"/>
@@ -10105,7 +10112,7 @@
       <c r="E982" s="24"/>
       <c r="F982" s="25"/>
     </row>
-    <row r="983" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="26"/>
       <c r="B983" s="27"/>
       <c r="C983" s="24"/>
@@ -10113,7 +10120,7 @@
       <c r="E983" s="24"/>
       <c r="F983" s="25"/>
     </row>
-    <row r="984" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="26"/>
       <c r="B984" s="27"/>
       <c r="C984" s="24"/>
@@ -10121,7 +10128,7 @@
       <c r="E984" s="24"/>
       <c r="F984" s="25"/>
     </row>
-    <row r="985" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="26"/>
       <c r="B985" s="27"/>
       <c r="C985" s="24"/>
@@ -10129,7 +10136,7 @@
       <c r="E985" s="24"/>
       <c r="F985" s="25"/>
     </row>
-    <row r="986" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="26"/>
       <c r="B986" s="27"/>
       <c r="C986" s="24"/>
@@ -10137,7 +10144,7 @@
       <c r="E986" s="24"/>
       <c r="F986" s="25"/>
     </row>
-    <row r="987" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="26"/>
       <c r="B987" s="27"/>
       <c r="C987" s="24"/>
@@ -10145,7 +10152,7 @@
       <c r="E987" s="24"/>
       <c r="F987" s="25"/>
     </row>
-    <row r="988" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="26"/>
       <c r="B988" s="27"/>
       <c r="C988" s="24"/>
@@ -10153,7 +10160,7 @@
       <c r="E988" s="24"/>
       <c r="F988" s="25"/>
     </row>
-    <row r="989" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="26"/>
       <c r="B989" s="27"/>
       <c r="C989" s="24"/>
@@ -10161,7 +10168,7 @@
       <c r="E989" s="24"/>
       <c r="F989" s="25"/>
     </row>
-    <row r="990" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="26"/>
       <c r="B990" s="27"/>
       <c r="C990" s="24"/>
@@ -10169,7 +10176,7 @@
       <c r="E990" s="24"/>
       <c r="F990" s="25"/>
     </row>
-    <row r="991" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
